--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122513561</v>
+        <v>122513469</v>
       </c>
       <c r="B2" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519272</v>
+        <v>519319</v>
       </c>
       <c r="R2" t="n">
-        <v>7055091</v>
+        <v>7055189</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,6 +753,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -761,31 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -802,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122513788</v>
+        <v>122513607</v>
       </c>
       <c r="B3" t="n">
         <v>57379</v>
@@ -820,11 +800,6 @@
       <c r="E3" t="n">
         <v>100109</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -847,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519313</v>
+        <v>519387</v>
       </c>
       <c r="R3" t="n">
-        <v>7055191</v>
+        <v>7055266</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,31 +873,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -957,11 +907,6 @@
       <c r="E4" t="n">
         <v>100136</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Lappuggla</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Strix nebulosa</t>
@@ -1050,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122513843</v>
+        <v>122513573</v>
       </c>
       <c r="B5" t="n">
-        <v>78651</v>
+        <v>90833</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,21 +1011,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>5442</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1090,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519326</v>
+        <v>519391</v>
       </c>
       <c r="R5" t="n">
-        <v>7055234</v>
+        <v>7055250</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1136,31 +1076,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1177,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122513257</v>
+        <v>122514475</v>
       </c>
       <c r="B6" t="n">
         <v>57379</v>
@@ -1195,11 +1110,6 @@
       <c r="E6" t="n">
         <v>100109</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1222,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519274</v>
+        <v>519424</v>
       </c>
       <c r="R6" t="n">
-        <v>7055087</v>
+        <v>7055785</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1289,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122513469</v>
+        <v>122513843</v>
       </c>
       <c r="B7" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1305,39 +1215,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519319</v>
+        <v>519326</v>
       </c>
       <c r="R7" t="n">
-        <v>7055189</v>
+        <v>7055234</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1372,11 +1272,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1385,6 +1280,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1401,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122514293</v>
+        <v>122513696</v>
       </c>
       <c r="B8" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1419,11 +1334,6 @@
       <c r="E8" t="n">
         <v>6425</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1441,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519526</v>
+        <v>519306</v>
       </c>
       <c r="R8" t="n">
-        <v>7055378</v>
+        <v>7055165</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1479,6 +1389,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ymnigt med långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1490,12 +1405,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -1528,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122513924</v>
+        <v>122513561</v>
       </c>
       <c r="B9" t="n">
-        <v>90826</v>
+        <v>78652</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1544,21 +1454,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1568,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519411</v>
+        <v>519272</v>
       </c>
       <c r="R9" t="n">
-        <v>7055518</v>
+        <v>7055091</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1614,6 +1519,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1630,10 +1555,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122513696</v>
+        <v>122513395</v>
       </c>
       <c r="B10" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1648,11 +1573,6 @@
       <c r="E10" t="n">
         <v>6425</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1664,16 +1584,21 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519306</v>
+        <v>519278</v>
       </c>
       <c r="R10" t="n">
-        <v>7055165</v>
+        <v>7055044</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,7 +1635,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ymnigt med långväxta bålar.</t>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,11 +1652,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK10" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -1739,12 +1659,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1762,7 +1682,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122513932</v>
+        <v>122513788</v>
       </c>
       <c r="B11" t="n">
         <v>57379</v>
@@ -1780,11 +1700,6 @@
       <c r="E11" t="n">
         <v>100109</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1807,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519417</v>
+        <v>519313</v>
       </c>
       <c r="R11" t="n">
-        <v>7055533</v>
+        <v>7055191</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1847,7 +1762,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1858,6 +1773,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1874,10 +1809,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122514475</v>
+        <v>122514485</v>
       </c>
       <c r="B12" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1890,39 +1825,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519424</v>
+        <v>519340</v>
       </c>
       <c r="R12" t="n">
-        <v>7055785</v>
+        <v>7055482</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1957,11 +1882,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1970,6 +1890,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1986,10 +1926,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122513926</v>
+        <v>122513924</v>
       </c>
       <c r="B13" t="n">
-        <v>78651</v>
+        <v>90831</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2002,21 +1942,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2026,13 +1961,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519405</v>
+        <v>519411</v>
       </c>
       <c r="R13" t="n">
-        <v>7055243</v>
+        <v>7055518</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2072,31 +2007,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2113,10 +2023,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122513395</v>
+        <v>122513932</v>
       </c>
       <c r="B14" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2129,27 +2039,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2158,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519278</v>
+        <v>519417</v>
       </c>
       <c r="R14" t="n">
-        <v>7055044</v>
+        <v>7055533</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2198,7 +2103,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2209,31 +2114,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2253,7 +2133,7 @@
         <v>122513793</v>
       </c>
       <c r="B15" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2268,11 +2148,6 @@
       <c r="E15" t="n">
         <v>6425</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2340,11 +2215,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -2377,10 +2247,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122514218</v>
+        <v>122514293</v>
       </c>
       <c r="B16" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2393,39 +2263,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519487</v>
+        <v>519526</v>
       </c>
       <c r="R16" t="n">
-        <v>7055674</v>
+        <v>7055378</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2460,11 +2320,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2473,6 +2328,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2489,7 +2364,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122513607</v>
+        <v>122514218</v>
       </c>
       <c r="B17" t="n">
         <v>57379</v>
@@ -2507,11 +2382,6 @@
       <c r="E17" t="n">
         <v>100109</v>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2534,10 +2404,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519387</v>
+        <v>519487</v>
       </c>
       <c r="R17" t="n">
-        <v>7055266</v>
+        <v>7055674</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2601,10 +2471,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122513573</v>
+        <v>122513257</v>
       </c>
       <c r="B18" t="n">
-        <v>90828</v>
+        <v>57379</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2617,34 +2487,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519391</v>
+        <v>519274</v>
       </c>
       <c r="R18" t="n">
-        <v>7055250</v>
+        <v>7055087</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2677,6 +2547,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2703,10 +2578,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122514485</v>
+        <v>122513926</v>
       </c>
       <c r="B19" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2721,11 +2596,6 @@
       <c r="E19" t="n">
         <v>6425</v>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2743,13 +2613,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519340</v>
+        <v>519405</v>
       </c>
       <c r="R19" t="n">
-        <v>7055482</v>
+        <v>7055243</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2792,12 +2662,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122513469</v>
+        <v>122513843</v>
       </c>
       <c r="B2" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519319</v>
+        <v>519326</v>
       </c>
       <c r="R2" t="n">
-        <v>7055189</v>
+        <v>7055234</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,11 +753,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -766,6 +761,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122513607</v>
+        <v>122513696</v>
       </c>
       <c r="B3" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,34 +818,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519387</v>
+        <v>519306</v>
       </c>
       <c r="R3" t="n">
-        <v>7055266</v>
+        <v>7055165</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +882,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ymnigt med långväxta bålar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -873,6 +893,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -889,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122513620</v>
+        <v>122513926</v>
       </c>
       <c r="B4" t="n">
-        <v>57348</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,45 +946,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100136</v>
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519384</v>
+        <v>519405</v>
       </c>
       <c r="R4" t="n">
-        <v>7055266</v>
+        <v>7055243</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,6 +1020,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -995,10 +1061,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122513573</v>
+        <v>122514218</v>
       </c>
       <c r="B5" t="n">
-        <v>90833</v>
+        <v>57383</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,29 +1077,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519391</v>
+        <v>519487</v>
       </c>
       <c r="R5" t="n">
-        <v>7055250</v>
+        <v>7055674</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,6 +1142,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122514475</v>
+        <v>122513395</v>
       </c>
       <c r="B6" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,22 +1189,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1132,10 +1218,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519424</v>
+        <v>519278</v>
       </c>
       <c r="R6" t="n">
-        <v>7055785</v>
+        <v>7055044</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,7 +1258,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,6 +1269,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1199,10 +1310,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122513843</v>
+        <v>122513793</v>
       </c>
       <c r="B7" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,6 +1328,11 @@
       <c r="E7" t="n">
         <v>6425</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1234,10 +1350,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519326</v>
+        <v>519310</v>
       </c>
       <c r="R7" t="n">
-        <v>7055234</v>
+        <v>7055186</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,7 +1399,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -1293,12 +1414,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1316,10 +1437,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122513696</v>
+        <v>122514485</v>
       </c>
       <c r="B8" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1334,6 +1455,11 @@
       <c r="E8" t="n">
         <v>6425</v>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1351,10 +1477,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519306</v>
+        <v>519340</v>
       </c>
       <c r="R8" t="n">
-        <v>7055165</v>
+        <v>7055482</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,11 +1515,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ymnigt med långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1405,7 +1526,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -1438,10 +1564,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122513561</v>
+        <v>122513620</v>
       </c>
       <c r="B9" t="n">
-        <v>78652</v>
+        <v>57352</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1450,33 +1576,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100136</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lappuggla</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519272</v>
+        <v>519384</v>
       </c>
       <c r="R9" t="n">
-        <v>7055091</v>
+        <v>7055266</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,26 +1659,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1555,10 +1675,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122513395</v>
+        <v>122513932</v>
       </c>
       <c r="B10" t="n">
-        <v>78652</v>
+        <v>57383</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,22 +1691,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1595,10 +1720,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519278</v>
+        <v>519417</v>
       </c>
       <c r="R10" t="n">
-        <v>7055044</v>
+        <v>7055533</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,7 +1760,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1646,26 +1771,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1682,10 +1787,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122513788</v>
+        <v>122514293</v>
       </c>
       <c r="B11" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1698,34 +1803,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519313</v>
+        <v>519526</v>
       </c>
       <c r="R11" t="n">
-        <v>7055191</v>
+        <v>7055378</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,11 +1865,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1776,7 +1876,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -1786,12 +1891,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1809,10 +1914,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122514485</v>
+        <v>122513573</v>
       </c>
       <c r="B12" t="n">
-        <v>78652</v>
+        <v>90846</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1825,16 +1930,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5442</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1844,10 +1954,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519340</v>
+        <v>519391</v>
       </c>
       <c r="R12" t="n">
-        <v>7055482</v>
+        <v>7055250</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1890,26 +2000,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1926,10 +2016,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122513924</v>
+        <v>122513561</v>
       </c>
       <c r="B13" t="n">
-        <v>90831</v>
+        <v>78656</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,16 +2032,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1961,10 +2056,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519411</v>
+        <v>519272</v>
       </c>
       <c r="R13" t="n">
-        <v>7055518</v>
+        <v>7055091</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,6 +2102,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2023,10 +2143,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122513932</v>
+        <v>122513469</v>
       </c>
       <c r="B14" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2041,6 +2161,11 @@
       <c r="E14" t="n">
         <v>100109</v>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2063,10 +2188,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519417</v>
+        <v>519319</v>
       </c>
       <c r="R14" t="n">
-        <v>7055533</v>
+        <v>7055189</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,7 +2228,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,10 +2255,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122513793</v>
+        <v>122513788</v>
       </c>
       <c r="B15" t="n">
-        <v>78652</v>
+        <v>57383</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2146,29 +2271,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519310</v>
+        <v>519313</v>
       </c>
       <c r="R15" t="n">
-        <v>7055186</v>
+        <v>7055191</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2203,6 +2338,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2217,6 +2357,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK15" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -2224,12 +2369,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2247,10 +2392,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122514293</v>
+        <v>122513924</v>
       </c>
       <c r="B16" t="n">
-        <v>78652</v>
+        <v>90844</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2263,16 +2408,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2282,10 +2432,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519526</v>
+        <v>519411</v>
       </c>
       <c r="R16" t="n">
-        <v>7055378</v>
+        <v>7055518</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2328,26 +2478,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2364,10 +2494,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122514218</v>
+        <v>122513607</v>
       </c>
       <c r="B17" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2382,6 +2512,11 @@
       <c r="E17" t="n">
         <v>100109</v>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2404,10 +2539,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519487</v>
+        <v>519387</v>
       </c>
       <c r="R17" t="n">
-        <v>7055674</v>
+        <v>7055266</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2474,7 +2609,7 @@
         <v>122513257</v>
       </c>
       <c r="B18" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2488,6 +2623,11 @@
       </c>
       <c r="E18" t="n">
         <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2578,10 +2718,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122513926</v>
+        <v>122514475</v>
       </c>
       <c r="B19" t="n">
-        <v>78652</v>
+        <v>57383</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2594,32 +2734,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519405</v>
+        <v>519424</v>
       </c>
       <c r="R19" t="n">
-        <v>7055243</v>
+        <v>7055785</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2651,6 +2801,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2659,26 +2814,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122513843</v>
+        <v>122514485</v>
       </c>
       <c r="B2" t="n">
         <v>78656</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519326</v>
+        <v>519340</v>
       </c>
       <c r="R2" t="n">
-        <v>7055234</v>
+        <v>7055482</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -779,12 +779,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122513696</v>
+        <v>122513620</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>57352</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,38 +814,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100136</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519306</v>
+        <v>519384</v>
       </c>
       <c r="R3" t="n">
-        <v>7055165</v>
+        <v>7055266</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,11 +889,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ymnigt med långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -893,31 +897,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -934,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122513926</v>
+        <v>122513788</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,37 +929,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519405</v>
+        <v>519313</v>
       </c>
       <c r="R4" t="n">
-        <v>7055243</v>
+        <v>7055191</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,6 +996,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1038,12 +1027,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1061,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122514218</v>
+        <v>122513395</v>
       </c>
       <c r="B5" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1077,27 +1066,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1106,10 +1095,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519487</v>
+        <v>519278</v>
       </c>
       <c r="R5" t="n">
-        <v>7055674</v>
+        <v>7055044</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1146,7 +1135,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,6 +1146,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1173,7 +1187,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122513395</v>
+        <v>122513696</v>
       </c>
       <c r="B6" t="n">
         <v>78656</v>
@@ -1207,21 +1221,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519278</v>
+        <v>519306</v>
       </c>
       <c r="R6" t="n">
-        <v>7055044</v>
+        <v>7055165</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1258,7 +1267,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>Ymnigt med långväxta bålar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,12 +1296,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1310,7 +1319,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122513793</v>
+        <v>122513926</v>
       </c>
       <c r="B7" t="n">
         <v>78656</v>
@@ -1350,13 +1359,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519310</v>
+        <v>519405</v>
       </c>
       <c r="R7" t="n">
-        <v>7055186</v>
+        <v>7055243</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1437,7 +1446,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122514485</v>
+        <v>122513843</v>
       </c>
       <c r="B8" t="n">
         <v>78656</v>
@@ -1477,10 +1486,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519340</v>
+        <v>519326</v>
       </c>
       <c r="R8" t="n">
-        <v>7055482</v>
+        <v>7055234</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1541,12 +1550,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1564,10 +1573,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122513620</v>
+        <v>122513573</v>
       </c>
       <c r="B9" t="n">
-        <v>57352</v>
+        <v>90859</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1576,47 +1585,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100136</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519384</v>
+        <v>519391</v>
       </c>
       <c r="R9" t="n">
-        <v>7055266</v>
+        <v>7055250</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1675,10 +1675,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122513932</v>
+        <v>122514293</v>
       </c>
       <c r="B10" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1691,39 +1691,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519417</v>
+        <v>519526</v>
       </c>
       <c r="R10" t="n">
-        <v>7055533</v>
+        <v>7055378</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1758,11 +1753,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1771,6 +1761,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1787,10 +1802,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122514293</v>
+        <v>122514218</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1803,34 +1818,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519526</v>
+        <v>519487</v>
       </c>
       <c r="R11" t="n">
-        <v>7055378</v>
+        <v>7055674</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1865,6 +1885,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1873,31 +1898,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1914,10 +1914,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122513573</v>
+        <v>122513793</v>
       </c>
       <c r="B12" t="n">
-        <v>90846</v>
+        <v>78656</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1930,21 +1930,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519391</v>
+        <v>519310</v>
       </c>
       <c r="R12" t="n">
-        <v>7055250</v>
+        <v>7055186</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2000,6 +2000,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2016,10 +2041,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122513561</v>
+        <v>122513257</v>
       </c>
       <c r="B13" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2032,34 +2057,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519272</v>
+        <v>519274</v>
       </c>
       <c r="R13" t="n">
-        <v>7055091</v>
+        <v>7055087</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2094,6 +2124,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2102,31 +2137,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2143,10 +2153,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122513469</v>
+        <v>122513561</v>
       </c>
       <c r="B14" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2159,39 +2169,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519319</v>
+        <v>519272</v>
       </c>
       <c r="R14" t="n">
-        <v>7055189</v>
+        <v>7055091</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2226,11 +2231,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2239,6 +2239,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2255,7 +2280,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122513788</v>
+        <v>122513932</v>
       </c>
       <c r="B15" t="n">
         <v>57383</v>
@@ -2300,10 +2325,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519313</v>
+        <v>519417</v>
       </c>
       <c r="R15" t="n">
-        <v>7055191</v>
+        <v>7055533</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2340,7 +2365,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2351,31 +2376,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2392,10 +2392,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122513924</v>
+        <v>122513469</v>
       </c>
       <c r="B16" t="n">
-        <v>90844</v>
+        <v>57383</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2408,34 +2408,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519411</v>
+        <v>519319</v>
       </c>
       <c r="R16" t="n">
-        <v>7055518</v>
+        <v>7055189</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2468,6 +2473,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2494,10 +2504,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122513607</v>
+        <v>122513924</v>
       </c>
       <c r="B17" t="n">
-        <v>57383</v>
+        <v>90857</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2510,39 +2520,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519387</v>
+        <v>519411</v>
       </c>
       <c r="R17" t="n">
-        <v>7055266</v>
+        <v>7055518</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2575,11 +2580,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2606,7 +2606,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122513257</v>
+        <v>122513607</v>
       </c>
       <c r="B18" t="n">
         <v>57383</v>
@@ -2651,10 +2651,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519274</v>
+        <v>519387</v>
       </c>
       <c r="R18" t="n">
-        <v>7055087</v>
+        <v>7055266</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122514485</v>
+        <v>122514293</v>
       </c>
       <c r="B2" t="n">
         <v>78656</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519340</v>
+        <v>519526</v>
       </c>
       <c r="R2" t="n">
-        <v>7055482</v>
+        <v>7055378</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122513620</v>
+        <v>122514218</v>
       </c>
       <c r="B3" t="n">
-        <v>57352</v>
+        <v>57383</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,35 +814,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100136</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -851,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519384</v>
+        <v>519487</v>
       </c>
       <c r="R3" t="n">
-        <v>7055266</v>
+        <v>7055674</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,6 +883,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1050,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122513395</v>
+        <v>122513924</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>90857</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,39 +1067,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519278</v>
+        <v>519411</v>
       </c>
       <c r="R5" t="n">
-        <v>7055044</v>
+        <v>7055518</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1133,11 +1129,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Långväxt fertil garnlav.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1146,31 +1137,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1187,7 +1153,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122513696</v>
+        <v>122513395</v>
       </c>
       <c r="B6" t="n">
         <v>78656</v>
@@ -1221,16 +1187,21 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519306</v>
+        <v>519278</v>
       </c>
       <c r="R6" t="n">
-        <v>7055165</v>
+        <v>7055044</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1267,7 +1238,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ymnigt med långväxta bålar.</t>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,12 +1267,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1446,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122513843</v>
+        <v>122513932</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1462,34 +1433,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519326</v>
+        <v>519417</v>
       </c>
       <c r="R8" t="n">
-        <v>7055234</v>
+        <v>7055533</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1524,6 +1500,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1532,31 +1513,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1573,10 +1529,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122513573</v>
+        <v>122513469</v>
       </c>
       <c r="B9" t="n">
-        <v>90859</v>
+        <v>57383</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1589,34 +1545,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519391</v>
+        <v>519319</v>
       </c>
       <c r="R9" t="n">
-        <v>7055250</v>
+        <v>7055189</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1649,6 +1610,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1675,10 +1641,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122514293</v>
+        <v>122513257</v>
       </c>
       <c r="B10" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1691,34 +1657,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519526</v>
+        <v>519274</v>
       </c>
       <c r="R10" t="n">
-        <v>7055378</v>
+        <v>7055087</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1753,6 +1724,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1761,31 +1737,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1802,10 +1753,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122514218</v>
+        <v>122513843</v>
       </c>
       <c r="B11" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1818,39 +1769,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519487</v>
+        <v>519326</v>
       </c>
       <c r="R11" t="n">
-        <v>7055674</v>
+        <v>7055234</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1885,11 +1831,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1898,6 +1839,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1914,10 +1880,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122513793</v>
+        <v>122513620</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>57352</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1926,38 +1892,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100136</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519310</v>
+        <v>519384</v>
       </c>
       <c r="R12" t="n">
-        <v>7055186</v>
+        <v>7055266</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2000,31 +1975,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2041,7 +1991,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122513257</v>
+        <v>122514475</v>
       </c>
       <c r="B13" t="n">
         <v>57383</v>
@@ -2086,10 +2036,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519274</v>
+        <v>519424</v>
       </c>
       <c r="R13" t="n">
-        <v>7055087</v>
+        <v>7055785</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2153,7 +2103,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122513561</v>
+        <v>122513696</v>
       </c>
       <c r="B14" t="n">
         <v>78656</v>
@@ -2193,10 +2143,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519272</v>
+        <v>519306</v>
       </c>
       <c r="R14" t="n">
-        <v>7055091</v>
+        <v>7055165</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2231,6 +2181,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ymnigt med långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2257,12 +2212,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2280,7 +2235,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122513932</v>
+        <v>122513607</v>
       </c>
       <c r="B15" t="n">
         <v>57383</v>
@@ -2325,10 +2280,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519417</v>
+        <v>519387</v>
       </c>
       <c r="R15" t="n">
-        <v>7055533</v>
+        <v>7055266</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2365,7 +2320,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2392,10 +2347,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122513469</v>
+        <v>122514485</v>
       </c>
       <c r="B16" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2408,39 +2363,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519319</v>
+        <v>519340</v>
       </c>
       <c r="R16" t="n">
-        <v>7055189</v>
+        <v>7055482</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2475,11 +2425,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2488,6 +2433,31 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2504,10 +2474,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122513924</v>
+        <v>122513573</v>
       </c>
       <c r="B17" t="n">
-        <v>90857</v>
+        <v>90859</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2520,21 +2490,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2544,10 +2514,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519411</v>
+        <v>519391</v>
       </c>
       <c r="R17" t="n">
-        <v>7055518</v>
+        <v>7055250</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2606,10 +2576,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122513607</v>
+        <v>122513561</v>
       </c>
       <c r="B18" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2622,39 +2592,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519387</v>
+        <v>519272</v>
       </c>
       <c r="R18" t="n">
-        <v>7055266</v>
+        <v>7055091</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2689,11 +2654,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2702,6 +2662,31 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2718,10 +2703,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122514475</v>
+        <v>122513793</v>
       </c>
       <c r="B19" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2734,39 +2719,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519424</v>
+        <v>519310</v>
       </c>
       <c r="R19" t="n">
-        <v>7055785</v>
+        <v>7055186</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2801,11 +2781,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2814,6 +2789,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122514293</v>
+        <v>122513843</v>
       </c>
       <c r="B2" t="n">
         <v>78656</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519526</v>
+        <v>519326</v>
       </c>
       <c r="R2" t="n">
-        <v>7055378</v>
+        <v>7055234</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -779,12 +779,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,7 +802,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122514218</v>
+        <v>122513257</v>
       </c>
       <c r="B3" t="n">
         <v>57383</v>
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519487</v>
+        <v>519274</v>
       </c>
       <c r="R3" t="n">
-        <v>7055674</v>
+        <v>7055087</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122513788</v>
+        <v>122513924</v>
       </c>
       <c r="B4" t="n">
-        <v>57383</v>
+        <v>90851</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,39 +930,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519313</v>
+        <v>519411</v>
       </c>
       <c r="R4" t="n">
-        <v>7055191</v>
+        <v>7055518</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,11 +992,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1010,31 +1000,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1051,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122513924</v>
+        <v>122513932</v>
       </c>
       <c r="B5" t="n">
-        <v>90857</v>
+        <v>57383</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,34 +1032,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519411</v>
+        <v>519417</v>
       </c>
       <c r="R5" t="n">
-        <v>7055518</v>
+        <v>7055533</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,6 +1097,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122513395</v>
+        <v>122513620</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>57352</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,31 +1140,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100136</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1198,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519278</v>
+        <v>519384</v>
       </c>
       <c r="R6" t="n">
-        <v>7055044</v>
+        <v>7055266</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,11 +1215,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Långväxt fertil garnlav.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1249,31 +1223,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1290,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122513926</v>
+        <v>122513788</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1306,37 +1255,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519405</v>
+        <v>519313</v>
       </c>
       <c r="R7" t="n">
-        <v>7055243</v>
+        <v>7055191</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1368,6 +1322,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1394,12 +1353,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1417,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122513932</v>
+        <v>122513573</v>
       </c>
       <c r="B8" t="n">
-        <v>57383</v>
+        <v>90853</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1433,39 +1392,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519417</v>
+        <v>519391</v>
       </c>
       <c r="R8" t="n">
-        <v>7055533</v>
+        <v>7055250</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1498,11 +1452,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1529,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122513469</v>
+        <v>122513395</v>
       </c>
       <c r="B9" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1545,27 +1494,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1574,10 +1523,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519319</v>
+        <v>519278</v>
       </c>
       <c r="R9" t="n">
-        <v>7055189</v>
+        <v>7055044</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1614,7 +1563,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1625,6 +1574,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1641,7 +1615,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122513257</v>
+        <v>122514475</v>
       </c>
       <c r="B10" t="n">
         <v>57383</v>
@@ -1686,10 +1660,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519274</v>
+        <v>519424</v>
       </c>
       <c r="R10" t="n">
-        <v>7055087</v>
+        <v>7055785</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1753,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122513843</v>
+        <v>122513607</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1769,34 +1743,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519326</v>
+        <v>519387</v>
       </c>
       <c r="R11" t="n">
-        <v>7055234</v>
+        <v>7055266</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1831,6 +1810,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1839,31 +1823,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1880,10 +1839,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122513620</v>
+        <v>122514485</v>
       </c>
       <c r="B12" t="n">
-        <v>57352</v>
+        <v>78656</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1892,47 +1851,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100136</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519384</v>
+        <v>519340</v>
       </c>
       <c r="R12" t="n">
-        <v>7055266</v>
+        <v>7055482</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1975,6 +1925,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1991,10 +1966,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122514475</v>
+        <v>122513561</v>
       </c>
       <c r="B13" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2007,39 +1982,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519424</v>
+        <v>519272</v>
       </c>
       <c r="R13" t="n">
-        <v>7055785</v>
+        <v>7055091</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2074,11 +2044,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2087,6 +2052,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2103,10 +2093,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122513696</v>
+        <v>122514218</v>
       </c>
       <c r="B14" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2119,34 +2109,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519306</v>
+        <v>519487</v>
       </c>
       <c r="R14" t="n">
-        <v>7055165</v>
+        <v>7055674</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2183,7 +2178,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ymnigt med långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2194,31 +2189,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2235,10 +2205,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122513607</v>
+        <v>122513926</v>
       </c>
       <c r="B15" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2251,42 +2221,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519387</v>
+        <v>519405</v>
       </c>
       <c r="R15" t="n">
-        <v>7055266</v>
+        <v>7055243</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2318,11 +2283,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2331,6 +2291,31 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2347,7 +2332,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122514485</v>
+        <v>122513696</v>
       </c>
       <c r="B16" t="n">
         <v>78656</v>
@@ -2387,10 +2372,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519340</v>
+        <v>519306</v>
       </c>
       <c r="R16" t="n">
-        <v>7055482</v>
+        <v>7055165</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2425,6 +2410,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ymnigt med långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2436,7 +2426,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2474,10 +2464,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122513573</v>
+        <v>122513793</v>
       </c>
       <c r="B17" t="n">
-        <v>90859</v>
+        <v>78656</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2490,21 +2480,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2514,10 +2504,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519391</v>
+        <v>519310</v>
       </c>
       <c r="R17" t="n">
-        <v>7055250</v>
+        <v>7055186</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2560,6 +2550,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2576,7 +2591,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122513561</v>
+        <v>122514293</v>
       </c>
       <c r="B18" t="n">
         <v>78656</v>
@@ -2616,10 +2631,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519272</v>
+        <v>519526</v>
       </c>
       <c r="R18" t="n">
-        <v>7055091</v>
+        <v>7055378</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2665,7 +2680,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2680,12 +2695,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2703,10 +2718,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122513793</v>
+        <v>122513469</v>
       </c>
       <c r="B19" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2719,34 +2734,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519310</v>
+        <v>519319</v>
       </c>
       <c r="R19" t="n">
-        <v>7055186</v>
+        <v>7055189</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2781,6 +2801,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2789,31 +2814,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122513843</v>
+        <v>122513620</v>
       </c>
       <c r="B2" t="n">
-        <v>78656</v>
+        <v>57352</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100136</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519326</v>
+        <v>519384</v>
       </c>
       <c r="R2" t="n">
-        <v>7055234</v>
+        <v>7055266</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,31 +770,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -802,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122513257</v>
+        <v>122513469</v>
       </c>
       <c r="B3" t="n">
         <v>57383</v>
@@ -847,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519274</v>
+        <v>519319</v>
       </c>
       <c r="R3" t="n">
-        <v>7055087</v>
+        <v>7055189</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -914,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122513924</v>
+        <v>122513926</v>
       </c>
       <c r="B4" t="n">
-        <v>90851</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,21 +914,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,13 +938,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519411</v>
+        <v>519405</v>
       </c>
       <c r="R4" t="n">
-        <v>7055518</v>
+        <v>7055243</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1000,6 +984,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1016,7 +1025,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122513932</v>
+        <v>122513607</v>
       </c>
       <c r="B5" t="n">
         <v>57383</v>
@@ -1061,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519417</v>
+        <v>519387</v>
       </c>
       <c r="R5" t="n">
-        <v>7055533</v>
+        <v>7055266</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1110,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122513620</v>
+        <v>122514293</v>
       </c>
       <c r="B6" t="n">
-        <v>57352</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,47 +1149,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100136</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519384</v>
+        <v>519526</v>
       </c>
       <c r="R6" t="n">
-        <v>7055266</v>
+        <v>7055378</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,6 +1223,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1239,7 +1264,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122513788</v>
+        <v>122513932</v>
       </c>
       <c r="B7" t="n">
         <v>57383</v>
@@ -1284,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519313</v>
+        <v>519417</v>
       </c>
       <c r="R7" t="n">
-        <v>7055191</v>
+        <v>7055533</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,7 +1349,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,31 +1360,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1376,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122513573</v>
+        <v>122513395</v>
       </c>
       <c r="B8" t="n">
-        <v>90853</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,34 +1392,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519391</v>
+        <v>519278</v>
       </c>
       <c r="R8" t="n">
-        <v>7055250</v>
+        <v>7055044</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1454,6 +1459,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Långväxt fertil garnlav.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1462,6 +1472,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1478,7 +1513,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122513395</v>
+        <v>122513793</v>
       </c>
       <c r="B9" t="n">
         <v>78656</v>
@@ -1512,21 +1547,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519278</v>
+        <v>519310</v>
       </c>
       <c r="R9" t="n">
-        <v>7055044</v>
+        <v>7055186</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,11 +1591,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Långväxt fertil garnlav.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1592,12 +1617,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1615,10 +1640,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122514475</v>
+        <v>122514485</v>
       </c>
       <c r="B10" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1631,39 +1656,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519424</v>
+        <v>519340</v>
       </c>
       <c r="R10" t="n">
-        <v>7055785</v>
+        <v>7055482</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1698,11 +1718,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1711,6 +1726,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1727,10 +1767,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122513607</v>
+        <v>122513924</v>
       </c>
       <c r="B11" t="n">
-        <v>57383</v>
+        <v>90851</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1743,39 +1783,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519387</v>
+        <v>519411</v>
       </c>
       <c r="R11" t="n">
-        <v>7055266</v>
+        <v>7055518</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1808,11 +1843,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1839,7 +1869,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122514485</v>
+        <v>122513843</v>
       </c>
       <c r="B12" t="n">
         <v>78656</v>
@@ -1879,10 +1909,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519340</v>
+        <v>519326</v>
       </c>
       <c r="R12" t="n">
-        <v>7055482</v>
+        <v>7055234</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1943,12 +1973,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1966,10 +1996,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122513561</v>
+        <v>122513257</v>
       </c>
       <c r="B13" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1982,34 +2012,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519272</v>
+        <v>519274</v>
       </c>
       <c r="R13" t="n">
-        <v>7055091</v>
+        <v>7055087</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2044,6 +2079,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2052,31 +2092,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2093,7 +2108,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122514218</v>
+        <v>122514475</v>
       </c>
       <c r="B14" t="n">
         <v>57383</v>
@@ -2138,10 +2153,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519487</v>
+        <v>519424</v>
       </c>
       <c r="R14" t="n">
-        <v>7055674</v>
+        <v>7055785</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2205,10 +2220,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122513926</v>
+        <v>122513573</v>
       </c>
       <c r="B15" t="n">
-        <v>78656</v>
+        <v>90853</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2221,21 +2236,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2245,13 +2260,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519405</v>
+        <v>519391</v>
       </c>
       <c r="R15" t="n">
-        <v>7055243</v>
+        <v>7055250</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2291,31 +2306,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2332,10 +2322,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122513696</v>
+        <v>122513788</v>
       </c>
       <c r="B16" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2348,34 +2338,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519306</v>
+        <v>519313</v>
       </c>
       <c r="R16" t="n">
-        <v>7055165</v>
+        <v>7055191</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2412,7 +2407,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ymnigt med långväxta bålar.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2441,12 +2436,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2464,7 +2459,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122513793</v>
+        <v>122513696</v>
       </c>
       <c r="B17" t="n">
         <v>78656</v>
@@ -2504,10 +2499,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519310</v>
+        <v>519306</v>
       </c>
       <c r="R17" t="n">
-        <v>7055186</v>
+        <v>7055165</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2540,6 +2535,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ymnigt med långväxta bålar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2591,10 +2591,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122514293</v>
+        <v>122514218</v>
       </c>
       <c r="B18" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2607,34 +2607,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519526</v>
+        <v>519487</v>
       </c>
       <c r="R18" t="n">
-        <v>7055378</v>
+        <v>7055674</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2669,6 +2674,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2677,31 +2687,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2718,10 +2703,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122513469</v>
+        <v>122513561</v>
       </c>
       <c r="B19" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2734,39 +2719,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519319</v>
+        <v>519272</v>
       </c>
       <c r="R19" t="n">
-        <v>7055189</v>
+        <v>7055091</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2801,11 +2781,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2814,6 +2789,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122513620</v>
+        <v>122514475</v>
       </c>
       <c r="B2" t="n">
-        <v>57352</v>
+        <v>57384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100136</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519384</v>
+        <v>519424</v>
       </c>
       <c r="R2" t="n">
-        <v>7055266</v>
+        <v>7055785</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122513469</v>
+        <v>122513843</v>
       </c>
       <c r="B3" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519319</v>
+        <v>519326</v>
       </c>
       <c r="R3" t="n">
-        <v>7055189</v>
+        <v>7055234</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,11 +865,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -882,6 +873,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -898,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122513926</v>
+        <v>122513924</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>90852</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,21 +930,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -938,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519405</v>
+        <v>519411</v>
       </c>
       <c r="R4" t="n">
-        <v>7055243</v>
+        <v>7055518</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,31 +1000,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1025,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122513607</v>
+        <v>122513561</v>
       </c>
       <c r="B5" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,39 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519387</v>
+        <v>519272</v>
       </c>
       <c r="R5" t="n">
-        <v>7055266</v>
+        <v>7055091</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,11 +1094,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1121,6 +1102,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1137,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122514293</v>
+        <v>122513926</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1177,13 +1183,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519526</v>
+        <v>519405</v>
       </c>
       <c r="R6" t="n">
-        <v>7055378</v>
+        <v>7055243</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1226,7 +1232,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1264,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122513932</v>
+        <v>122513257</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1309,10 +1315,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519417</v>
+        <v>519274</v>
       </c>
       <c r="R7" t="n">
-        <v>7055533</v>
+        <v>7055087</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,7 +1355,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122513395</v>
+        <v>122513620</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
+        <v>57353</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,31 +1394,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100136</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1421,10 +1431,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519278</v>
+        <v>519384</v>
       </c>
       <c r="R8" t="n">
-        <v>7055044</v>
+        <v>7055266</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,11 +1469,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Långväxt fertil garnlav.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1472,31 +1477,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1513,10 +1493,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122513793</v>
+        <v>122514485</v>
       </c>
       <c r="B9" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1553,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519310</v>
+        <v>519340</v>
       </c>
       <c r="R9" t="n">
-        <v>7055186</v>
+        <v>7055482</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1602,7 +1582,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1640,10 +1620,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122514485</v>
+        <v>122513469</v>
       </c>
       <c r="B10" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1656,34 +1636,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519340</v>
+        <v>519319</v>
       </c>
       <c r="R10" t="n">
-        <v>7055482</v>
+        <v>7055189</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1718,6 +1703,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1726,31 +1716,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1767,10 +1732,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122513924</v>
+        <v>122513696</v>
       </c>
       <c r="B11" t="n">
-        <v>90851</v>
+        <v>78657</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1783,21 +1748,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1807,10 +1772,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519411</v>
+        <v>519306</v>
       </c>
       <c r="R11" t="n">
-        <v>7055518</v>
+        <v>7055165</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1845,6 +1810,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ymnigt med långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1853,6 +1823,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1869,10 +1864,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122513843</v>
+        <v>122513932</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1885,34 +1880,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519326</v>
+        <v>519417</v>
       </c>
       <c r="R12" t="n">
-        <v>7055234</v>
+        <v>7055533</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1947,6 +1947,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1955,31 +1960,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1996,10 +1976,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122513257</v>
+        <v>122514218</v>
       </c>
       <c r="B13" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2041,10 +2021,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519274</v>
+        <v>519487</v>
       </c>
       <c r="R13" t="n">
-        <v>7055087</v>
+        <v>7055674</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2108,10 +2088,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122514475</v>
+        <v>122513788</v>
       </c>
       <c r="B14" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2153,10 +2133,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519424</v>
+        <v>519313</v>
       </c>
       <c r="R14" t="n">
-        <v>7055785</v>
+        <v>7055191</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2193,7 +2173,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2204,6 +2184,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2220,10 +2225,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122513573</v>
+        <v>122513793</v>
       </c>
       <c r="B15" t="n">
-        <v>90853</v>
+        <v>78657</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2236,21 +2241,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2260,10 +2265,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519391</v>
+        <v>519310</v>
       </c>
       <c r="R15" t="n">
-        <v>7055250</v>
+        <v>7055186</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2306,6 +2311,31 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2322,10 +2352,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122513788</v>
+        <v>122513395</v>
       </c>
       <c r="B16" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2338,27 +2368,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2367,10 +2397,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519313</v>
+        <v>519278</v>
       </c>
       <c r="R16" t="n">
-        <v>7055191</v>
+        <v>7055044</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2407,7 +2437,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2436,12 +2466,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2459,10 +2489,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122513696</v>
+        <v>122513607</v>
       </c>
       <c r="B17" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2475,34 +2505,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519306</v>
+        <v>519387</v>
       </c>
       <c r="R17" t="n">
-        <v>7055165</v>
+        <v>7055266</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2539,7 +2574,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ymnigt med långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2550,31 +2585,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2591,10 +2601,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122514218</v>
+        <v>122513573</v>
       </c>
       <c r="B18" t="n">
-        <v>57383</v>
+        <v>90854</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2607,39 +2617,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519487</v>
+        <v>519391</v>
       </c>
       <c r="R18" t="n">
-        <v>7055674</v>
+        <v>7055250</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2672,11 +2677,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2703,10 +2703,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122513561</v>
+        <v>122514293</v>
       </c>
       <c r="B19" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519272</v>
+        <v>519526</v>
       </c>
       <c r="R19" t="n">
-        <v>7055091</v>
+        <v>7055378</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122514475</v>
+        <v>122513843</v>
       </c>
       <c r="B2" t="n">
-        <v>57384</v>
+        <v>78657</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519424</v>
+        <v>519326</v>
       </c>
       <c r="R2" t="n">
-        <v>7055785</v>
+        <v>7055234</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,11 +753,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,6 +761,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122513843</v>
+        <v>122514475</v>
       </c>
       <c r="B3" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +818,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519326</v>
+        <v>519424</v>
       </c>
       <c r="R3" t="n">
-        <v>7055234</v>
+        <v>7055785</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,6 +885,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -873,31 +898,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -2088,10 +2088,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122513788</v>
+        <v>122513793</v>
       </c>
       <c r="B14" t="n">
-        <v>57384</v>
+        <v>78657</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2104,39 +2104,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519313</v>
+        <v>519310</v>
       </c>
       <c r="R14" t="n">
-        <v>7055191</v>
+        <v>7055186</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2171,11 +2166,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2202,12 +2192,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2225,10 +2215,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122513793</v>
+        <v>122513788</v>
       </c>
       <c r="B15" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2241,34 +2231,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519310</v>
+        <v>519313</v>
       </c>
       <c r="R15" t="n">
-        <v>7055186</v>
+        <v>7055191</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2303,6 +2298,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2329,12 +2329,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122513843</v>
+        <v>122513696</v>
       </c>
       <c r="B2" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519326</v>
+        <v>519306</v>
       </c>
       <c r="R2" t="n">
-        <v>7055234</v>
+        <v>7055165</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,6 +753,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ymnigt med långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -764,7 +769,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -779,12 +784,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122514475</v>
+        <v>122514485</v>
       </c>
       <c r="B3" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,39 +823,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519424</v>
+        <v>519340</v>
       </c>
       <c r="R3" t="n">
-        <v>7055785</v>
+        <v>7055482</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,11 +885,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -898,6 +893,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -914,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122513924</v>
+        <v>122513620</v>
       </c>
       <c r="B4" t="n">
-        <v>90852</v>
+        <v>57353</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,38 +946,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100136</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519411</v>
+        <v>519384</v>
       </c>
       <c r="R4" t="n">
-        <v>7055518</v>
+        <v>7055266</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122513561</v>
+        <v>122513469</v>
       </c>
       <c r="B5" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1061,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519272</v>
+        <v>519319</v>
       </c>
       <c r="R5" t="n">
-        <v>7055091</v>
+        <v>7055189</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,6 +1128,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1102,31 +1141,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1143,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122513926</v>
+        <v>122514475</v>
       </c>
       <c r="B6" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,37 +1173,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519405</v>
+        <v>519424</v>
       </c>
       <c r="R6" t="n">
-        <v>7055243</v>
+        <v>7055785</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,6 +1240,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1229,31 +1253,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1270,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122513257</v>
+        <v>122513926</v>
       </c>
       <c r="B7" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,42 +1285,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519274</v>
+        <v>519405</v>
       </c>
       <c r="R7" t="n">
-        <v>7055087</v>
+        <v>7055243</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1353,11 +1347,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1366,6 +1355,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1382,10 +1396,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122513620</v>
+        <v>122513788</v>
       </c>
       <c r="B8" t="n">
-        <v>57353</v>
+        <v>57384</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,35 +1408,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100136</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1431,10 +1441,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519384</v>
+        <v>519313</v>
       </c>
       <c r="R8" t="n">
-        <v>7055266</v>
+        <v>7055191</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1469,6 +1479,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1477,6 +1492,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1493,10 +1533,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122514485</v>
+        <v>122513257</v>
       </c>
       <c r="B9" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1509,34 +1549,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519340</v>
+        <v>519274</v>
       </c>
       <c r="R9" t="n">
-        <v>7055482</v>
+        <v>7055087</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,6 +1616,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1579,31 +1629,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1620,10 +1645,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122513469</v>
+        <v>122513395</v>
       </c>
       <c r="B10" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,27 +1661,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1665,10 +1690,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519319</v>
+        <v>519278</v>
       </c>
       <c r="R10" t="n">
-        <v>7055189</v>
+        <v>7055044</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1705,7 +1730,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1716,6 +1741,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1732,10 +1782,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122513696</v>
+        <v>122513607</v>
       </c>
       <c r="B11" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1748,34 +1798,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519306</v>
+        <v>519387</v>
       </c>
       <c r="R11" t="n">
-        <v>7055165</v>
+        <v>7055266</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1812,7 +1867,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ymnigt med långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1823,31 +1878,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1864,10 +1894,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122513932</v>
+        <v>122513793</v>
       </c>
       <c r="B12" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1880,39 +1910,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519417</v>
+        <v>519310</v>
       </c>
       <c r="R12" t="n">
-        <v>7055533</v>
+        <v>7055186</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1947,11 +1972,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1960,6 +1980,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1976,10 +2021,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122514218</v>
+        <v>122514293</v>
       </c>
       <c r="B13" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1992,39 +2037,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519487</v>
+        <v>519526</v>
       </c>
       <c r="R13" t="n">
-        <v>7055674</v>
+        <v>7055378</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2059,11 +2099,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2072,6 +2107,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2088,10 +2148,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122513793</v>
+        <v>122513843</v>
       </c>
       <c r="B14" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2128,10 +2188,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519310</v>
+        <v>519326</v>
       </c>
       <c r="R14" t="n">
-        <v>7055186</v>
+        <v>7055234</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2177,7 +2237,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2192,12 +2252,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2215,7 +2275,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122513788</v>
+        <v>122513932</v>
       </c>
       <c r="B15" t="n">
         <v>57384</v>
@@ -2260,10 +2320,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519313</v>
+        <v>519417</v>
       </c>
       <c r="R15" t="n">
-        <v>7055191</v>
+        <v>7055533</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2300,7 +2360,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2311,31 +2371,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2352,10 +2387,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122513395</v>
+        <v>122514218</v>
       </c>
       <c r="B16" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2368,27 +2403,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2397,10 +2432,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519278</v>
+        <v>519487</v>
       </c>
       <c r="R16" t="n">
-        <v>7055044</v>
+        <v>7055674</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2437,7 +2472,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2448,31 +2483,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2489,10 +2499,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122513607</v>
+        <v>122513924</v>
       </c>
       <c r="B17" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2505,39 +2515,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519387</v>
+        <v>519411</v>
       </c>
       <c r="R17" t="n">
-        <v>7055266</v>
+        <v>7055518</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2570,11 +2575,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2604,7 +2604,7 @@
         <v>122513573</v>
       </c>
       <c r="B18" t="n">
-        <v>90854</v>
+        <v>90857</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122514293</v>
+        <v>122513561</v>
       </c>
       <c r="B19" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519526</v>
+        <v>519272</v>
       </c>
       <c r="R19" t="n">
-        <v>7055378</v>
+        <v>7055091</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122513696</v>
+        <v>122513793</v>
       </c>
       <c r="B2" t="n">
         <v>78660</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519306</v>
+        <v>519310</v>
       </c>
       <c r="R2" t="n">
-        <v>7055165</v>
+        <v>7055186</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ymnigt med långväxta bålar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -807,7 +802,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122514485</v>
+        <v>122513395</v>
       </c>
       <c r="B3" t="n">
         <v>78660</v>
@@ -841,16 +836,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519340</v>
+        <v>519278</v>
       </c>
       <c r="R3" t="n">
-        <v>7055482</v>
+        <v>7055044</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,6 +885,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Långväxt fertil garnlav.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -896,7 +901,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -911,12 +916,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -934,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122513620</v>
+        <v>122513607</v>
       </c>
       <c r="B4" t="n">
-        <v>57353</v>
+        <v>57384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,35 +951,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100136</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -983,7 +984,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519384</v>
+        <v>519387</v>
       </c>
       <c r="R4" t="n">
         <v>7055266</v>
@@ -1019,6 +1020,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122513469</v>
+        <v>122514293</v>
       </c>
       <c r="B5" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1061,39 +1067,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519319</v>
+        <v>519526</v>
       </c>
       <c r="R5" t="n">
-        <v>7055189</v>
+        <v>7055378</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,11 +1129,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1141,6 +1137,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1157,7 +1178,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122514475</v>
+        <v>122513932</v>
       </c>
       <c r="B6" t="n">
         <v>57384</v>
@@ -1202,10 +1223,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519424</v>
+        <v>519417</v>
       </c>
       <c r="R6" t="n">
-        <v>7055785</v>
+        <v>7055533</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,7 +1263,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122513926</v>
+        <v>122514475</v>
       </c>
       <c r="B7" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,37 +1306,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519405</v>
+        <v>519424</v>
       </c>
       <c r="R7" t="n">
-        <v>7055243</v>
+        <v>7055785</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1347,6 +1373,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1355,31 +1386,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1396,7 +1402,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122513788</v>
+        <v>122513469</v>
       </c>
       <c r="B8" t="n">
         <v>57384</v>
@@ -1441,10 +1447,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519313</v>
+        <v>519319</v>
       </c>
       <c r="R8" t="n">
-        <v>7055191</v>
+        <v>7055189</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1481,7 +1487,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,31 +1498,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1533,7 +1514,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122513257</v>
+        <v>122513788</v>
       </c>
       <c r="B9" t="n">
         <v>57384</v>
@@ -1578,10 +1559,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519274</v>
+        <v>519313</v>
       </c>
       <c r="R9" t="n">
-        <v>7055087</v>
+        <v>7055191</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1618,7 +1599,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,6 +1610,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1645,7 +1651,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122513395</v>
+        <v>122513843</v>
       </c>
       <c r="B10" t="n">
         <v>78660</v>
@@ -1679,21 +1685,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519278</v>
+        <v>519326</v>
       </c>
       <c r="R10" t="n">
-        <v>7055044</v>
+        <v>7055234</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1728,11 +1729,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Långväxt fertil garnlav.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1744,7 +1740,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1782,7 +1778,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122513607</v>
+        <v>122513257</v>
       </c>
       <c r="B11" t="n">
         <v>57384</v>
@@ -1827,10 +1823,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519387</v>
+        <v>519274</v>
       </c>
       <c r="R11" t="n">
-        <v>7055266</v>
+        <v>7055087</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1894,10 +1890,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122513793</v>
+        <v>122514218</v>
       </c>
       <c r="B12" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1910,34 +1906,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519310</v>
+        <v>519487</v>
       </c>
       <c r="R12" t="n">
-        <v>7055186</v>
+        <v>7055674</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1972,6 +1973,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1980,31 +1986,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2021,7 +2002,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122514293</v>
+        <v>122513926</v>
       </c>
       <c r="B13" t="n">
         <v>78660</v>
@@ -2061,13 +2042,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519526</v>
+        <v>519405</v>
       </c>
       <c r="R13" t="n">
-        <v>7055378</v>
+        <v>7055243</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2110,7 +2091,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2148,10 +2129,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122513843</v>
+        <v>122513573</v>
       </c>
       <c r="B14" t="n">
-        <v>78660</v>
+        <v>90857</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2164,21 +2145,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2188,10 +2169,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519326</v>
+        <v>519391</v>
       </c>
       <c r="R14" t="n">
-        <v>7055234</v>
+        <v>7055250</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2234,31 +2215,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2275,10 +2231,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122513932</v>
+        <v>122513620</v>
       </c>
       <c r="B15" t="n">
-        <v>57384</v>
+        <v>57353</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2287,31 +2243,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100136</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2320,10 +2280,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519417</v>
+        <v>519384</v>
       </c>
       <c r="R15" t="n">
-        <v>7055533</v>
+        <v>7055266</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2356,11 +2316,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2387,10 +2342,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122514218</v>
+        <v>122513696</v>
       </c>
       <c r="B16" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2403,39 +2358,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519487</v>
+        <v>519306</v>
       </c>
       <c r="R16" t="n">
-        <v>7055674</v>
+        <v>7055165</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2472,7 +2422,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ymnigt med långväxta bålar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2483,6 +2433,31 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2499,10 +2474,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122513924</v>
+        <v>122514485</v>
       </c>
       <c r="B17" t="n">
-        <v>90855</v>
+        <v>78660</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2515,21 +2490,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2539,10 +2514,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519411</v>
+        <v>519340</v>
       </c>
       <c r="R17" t="n">
-        <v>7055518</v>
+        <v>7055482</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2585,6 +2560,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2601,10 +2601,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122513573</v>
+        <v>122513924</v>
       </c>
       <c r="B18" t="n">
-        <v>90857</v>
+        <v>90855</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2617,21 +2617,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2641,10 +2641,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519391</v>
+        <v>519411</v>
       </c>
       <c r="R18" t="n">
-        <v>7055250</v>
+        <v>7055518</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122514218</v>
+        <v>122513395</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>78762</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,27 +1129,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519487</v>
+        <v>519278</v>
       </c>
       <c r="R6" t="n">
-        <v>7055674</v>
+        <v>7055044</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,6 +1209,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1225,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122513395</v>
+        <v>122514218</v>
       </c>
       <c r="B7" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,27 +1266,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1270,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519278</v>
+        <v>519487</v>
       </c>
       <c r="R7" t="n">
-        <v>7055044</v>
+        <v>7055674</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1335,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,31 +1346,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122514475</v>
+        <v>122514293</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519424</v>
+        <v>519526</v>
       </c>
       <c r="R2" t="n">
-        <v>7055785</v>
+        <v>7055378</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,11 +753,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,6 +761,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122513573</v>
+        <v>122513788</v>
       </c>
       <c r="B3" t="n">
-        <v>90960</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +818,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519391</v>
+        <v>519313</v>
       </c>
       <c r="R3" t="n">
-        <v>7055250</v>
+        <v>7055191</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,6 +885,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -873,6 +898,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -889,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122513607</v>
+        <v>122514485</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,39 +955,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519387</v>
+        <v>519340</v>
       </c>
       <c r="R4" t="n">
-        <v>7055266</v>
+        <v>7055482</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,11 +1017,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -985,6 +1025,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1116,7 +1181,7 @@
         <v>122513395</v>
       </c>
       <c r="B6" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1250,10 +1315,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122514218</v>
+        <v>122513573</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>90964</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,39 +1331,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519487</v>
+        <v>519391</v>
       </c>
       <c r="R7" t="n">
-        <v>7055674</v>
+        <v>7055250</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,11 +1391,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122514293</v>
+        <v>122513469</v>
       </c>
       <c r="B8" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,34 +1433,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519526</v>
+        <v>519319</v>
       </c>
       <c r="R8" t="n">
-        <v>7055378</v>
+        <v>7055189</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,6 +1500,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1448,31 +1513,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1489,10 +1529,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122513924</v>
+        <v>122513696</v>
       </c>
       <c r="B9" t="n">
-        <v>90958</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,21 +1545,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1529,10 +1569,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519411</v>
+        <v>519306</v>
       </c>
       <c r="R9" t="n">
-        <v>7055518</v>
+        <v>7055165</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,6 +1607,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ymnigt med långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1575,6 +1620,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1591,10 +1661,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122513788</v>
+        <v>122513793</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,39 +1677,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519313</v>
+        <v>519310</v>
       </c>
       <c r="R10" t="n">
-        <v>7055191</v>
+        <v>7055186</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,11 +1739,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1705,12 +1765,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1728,10 +1788,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122513620</v>
+        <v>122513932</v>
       </c>
       <c r="B11" t="n">
-        <v>57447</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1740,35 +1800,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100136</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1777,10 +1833,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519384</v>
+        <v>519417</v>
       </c>
       <c r="R11" t="n">
-        <v>7055266</v>
+        <v>7055533</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1813,6 +1869,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1839,10 +1900,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122513696</v>
+        <v>122513607</v>
       </c>
       <c r="B12" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1855,34 +1916,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519306</v>
+        <v>519387</v>
       </c>
       <c r="R12" t="n">
-        <v>7055165</v>
+        <v>7055266</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1919,7 +1985,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ymnigt med långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1930,31 +1996,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1971,7 +2012,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122513469</v>
+        <v>122514475</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -2016,10 +2057,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519319</v>
+        <v>519424</v>
       </c>
       <c r="R13" t="n">
-        <v>7055189</v>
+        <v>7055785</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2083,10 +2124,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122513932</v>
+        <v>122513924</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2099,39 +2140,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519417</v>
+        <v>519411</v>
       </c>
       <c r="R14" t="n">
-        <v>7055533</v>
+        <v>7055518</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2164,11 +2200,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2195,10 +2226,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122513926</v>
+        <v>122513561</v>
       </c>
       <c r="B15" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2235,13 +2266,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519405</v>
+        <v>519272</v>
       </c>
       <c r="R15" t="n">
-        <v>7055243</v>
+        <v>7055091</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2299,12 +2330,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2322,10 +2353,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122513793</v>
+        <v>122513926</v>
       </c>
       <c r="B16" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2362,13 +2393,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519310</v>
+        <v>519405</v>
       </c>
       <c r="R16" t="n">
-        <v>7055186</v>
+        <v>7055243</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2449,10 +2480,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122514485</v>
+        <v>122514218</v>
       </c>
       <c r="B17" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2465,34 +2496,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519340</v>
+        <v>519487</v>
       </c>
       <c r="R17" t="n">
-        <v>7055482</v>
+        <v>7055674</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2527,6 +2563,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2535,31 +2576,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2576,10 +2592,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122513843</v>
+        <v>122513620</v>
       </c>
       <c r="B18" t="n">
-        <v>78762</v>
+        <v>57447</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2588,38 +2604,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100136</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519326</v>
+        <v>519384</v>
       </c>
       <c r="R18" t="n">
-        <v>7055234</v>
+        <v>7055266</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2662,31 +2687,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2703,10 +2703,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122513561</v>
+        <v>122513843</v>
       </c>
       <c r="B19" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519272</v>
+        <v>519326</v>
       </c>
       <c r="R19" t="n">
-        <v>7055091</v>
+        <v>7055234</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122514293</v>
+        <v>122513924</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519526</v>
+        <v>519411</v>
       </c>
       <c r="R2" t="n">
-        <v>7055378</v>
+        <v>7055518</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,31 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -802,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122513788</v>
+        <v>122513793</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519313</v>
+        <v>519310</v>
       </c>
       <c r="R3" t="n">
-        <v>7055191</v>
+        <v>7055186</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,11 +855,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -916,12 +881,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -939,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122514485</v>
+        <v>122513561</v>
       </c>
       <c r="B4" t="n">
         <v>78766</v>
@@ -979,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519340</v>
+        <v>519272</v>
       </c>
       <c r="R4" t="n">
-        <v>7055482</v>
+        <v>7055091</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1028,7 +993,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1043,12 +1008,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1066,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122513257</v>
+        <v>122513395</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1082,27 +1047,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1111,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519274</v>
+        <v>519278</v>
       </c>
       <c r="R5" t="n">
-        <v>7055087</v>
+        <v>7055044</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1151,7 +1116,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,6 +1127,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1178,7 +1168,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122513395</v>
+        <v>122513843</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1212,21 +1202,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519278</v>
+        <v>519326</v>
       </c>
       <c r="R6" t="n">
-        <v>7055044</v>
+        <v>7055234</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1261,11 +1246,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Långväxt fertil garnlav.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1277,7 +1257,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1417,10 +1397,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122513469</v>
+        <v>122514485</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1433,39 +1413,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519319</v>
+        <v>519340</v>
       </c>
       <c r="R8" t="n">
-        <v>7055189</v>
+        <v>7055482</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1500,11 +1475,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1513,6 +1483,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1529,10 +1524,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122513696</v>
+        <v>122513257</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1545,34 +1540,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519306</v>
+        <v>519274</v>
       </c>
       <c r="R9" t="n">
-        <v>7055165</v>
+        <v>7055087</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ymnigt med långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,31 +1620,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1661,7 +1636,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122513793</v>
+        <v>122513696</v>
       </c>
       <c r="B10" t="n">
         <v>78766</v>
@@ -1701,10 +1676,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519310</v>
+        <v>519306</v>
       </c>
       <c r="R10" t="n">
-        <v>7055186</v>
+        <v>7055165</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1737,6 +1712,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ymnigt med långväxta bålar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1788,10 +1768,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122513932</v>
+        <v>122513926</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1804,42 +1784,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519417</v>
+        <v>519405</v>
       </c>
       <c r="R11" t="n">
-        <v>7055533</v>
+        <v>7055243</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1871,11 +1846,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1884,6 +1854,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1900,7 +1895,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122513607</v>
+        <v>122514475</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1945,10 +1940,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519387</v>
+        <v>519424</v>
       </c>
       <c r="R12" t="n">
-        <v>7055266</v>
+        <v>7055785</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2012,7 +2007,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122514475</v>
+        <v>122513788</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -2057,10 +2052,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519424</v>
+        <v>519313</v>
       </c>
       <c r="R13" t="n">
-        <v>7055785</v>
+        <v>7055191</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2097,7 +2092,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2108,6 +2103,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2124,10 +2144,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122513924</v>
+        <v>122513932</v>
       </c>
       <c r="B14" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2140,34 +2160,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519411</v>
+        <v>519417</v>
       </c>
       <c r="R14" t="n">
-        <v>7055518</v>
+        <v>7055533</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2200,6 +2225,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2226,10 +2256,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122513561</v>
+        <v>122513620</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>57447</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2238,38 +2268,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100136</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519272</v>
+        <v>519384</v>
       </c>
       <c r="R15" t="n">
-        <v>7055091</v>
+        <v>7055266</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2312,31 +2351,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2353,10 +2367,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122513926</v>
+        <v>122514218</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2369,37 +2383,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519405</v>
+        <v>519487</v>
       </c>
       <c r="R16" t="n">
-        <v>7055243</v>
+        <v>7055674</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2431,6 +2450,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2439,31 +2463,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2480,10 +2479,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122514218</v>
+        <v>122514293</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2496,39 +2495,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519487</v>
+        <v>519526</v>
       </c>
       <c r="R17" t="n">
-        <v>7055674</v>
+        <v>7055378</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2563,11 +2557,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2576,6 +2565,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2592,10 +2606,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122513620</v>
+        <v>122513469</v>
       </c>
       <c r="B18" t="n">
-        <v>57447</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2604,35 +2618,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100136</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2641,10 +2651,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519384</v>
+        <v>519319</v>
       </c>
       <c r="R18" t="n">
-        <v>7055266</v>
+        <v>7055189</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2677,6 +2687,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2703,10 +2718,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122513843</v>
+        <v>122513607</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2719,34 +2734,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519326</v>
+        <v>519387</v>
       </c>
       <c r="R19" t="n">
-        <v>7055234</v>
+        <v>7055266</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2781,6 +2801,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2789,31 +2814,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122513924</v>
+        <v>122513607</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519411</v>
+        <v>519387</v>
       </c>
       <c r="R2" t="n">
-        <v>7055518</v>
+        <v>7055266</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122513793</v>
+        <v>122514485</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -817,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519310</v>
+        <v>519340</v>
       </c>
       <c r="R3" t="n">
-        <v>7055186</v>
+        <v>7055482</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +876,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -904,7 +914,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122513561</v>
+        <v>122513843</v>
       </c>
       <c r="B4" t="n">
         <v>78766</v>
@@ -944,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519272</v>
+        <v>519326</v>
       </c>
       <c r="R4" t="n">
-        <v>7055091</v>
+        <v>7055234</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +1003,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1031,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122513395</v>
+        <v>122513788</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,27 +1057,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1076,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519278</v>
+        <v>519313</v>
       </c>
       <c r="R5" t="n">
-        <v>7055044</v>
+        <v>7055191</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,7 +1126,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,12 +1155,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1168,10 +1178,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122513843</v>
+        <v>122513257</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1184,34 +1194,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519326</v>
+        <v>519274</v>
       </c>
       <c r="R6" t="n">
-        <v>7055234</v>
+        <v>7055087</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1246,6 +1261,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1254,31 +1274,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1295,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122513573</v>
+        <v>122513561</v>
       </c>
       <c r="B7" t="n">
-        <v>90964</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1311,21 +1306,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1335,10 +1330,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519391</v>
+        <v>519272</v>
       </c>
       <c r="R7" t="n">
-        <v>7055250</v>
+        <v>7055091</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1381,6 +1376,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1397,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122514485</v>
+        <v>122514475</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1413,34 +1433,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519340</v>
+        <v>519424</v>
       </c>
       <c r="R8" t="n">
-        <v>7055482</v>
+        <v>7055785</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1475,6 +1500,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1483,31 +1513,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1524,10 +1529,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122513257</v>
+        <v>122513696</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1540,39 +1545,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519274</v>
+        <v>519306</v>
       </c>
       <c r="R9" t="n">
-        <v>7055087</v>
+        <v>7055165</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ymnigt med långväxta bålar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,6 +1620,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1636,7 +1661,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122513696</v>
+        <v>122513395</v>
       </c>
       <c r="B10" t="n">
         <v>78766</v>
@@ -1670,16 +1695,21 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519306</v>
+        <v>519278</v>
       </c>
       <c r="R10" t="n">
-        <v>7055165</v>
+        <v>7055044</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1716,7 +1746,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ymnigt med långväxta bålar.</t>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1745,12 +1775,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1768,7 +1798,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122513926</v>
+        <v>122514293</v>
       </c>
       <c r="B11" t="n">
         <v>78766</v>
@@ -1808,13 +1838,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519405</v>
+        <v>519526</v>
       </c>
       <c r="R11" t="n">
-        <v>7055243</v>
+        <v>7055378</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1857,7 +1887,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1895,10 +1925,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122514475</v>
+        <v>122513573</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>90964</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1911,39 +1941,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519424</v>
+        <v>519391</v>
       </c>
       <c r="R12" t="n">
-        <v>7055785</v>
+        <v>7055250</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1976,11 +2001,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2007,10 +2027,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122513788</v>
+        <v>122513620</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>57447</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2019,31 +2039,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100136</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2052,10 +2076,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519313</v>
+        <v>519384</v>
       </c>
       <c r="R13" t="n">
-        <v>7055191</v>
+        <v>7055266</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2090,11 +2114,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2103,31 +2122,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2144,10 +2138,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122513932</v>
+        <v>122513924</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2160,39 +2154,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519417</v>
+        <v>519411</v>
       </c>
       <c r="R14" t="n">
-        <v>7055533</v>
+        <v>7055518</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2225,11 +2214,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2256,10 +2240,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122513620</v>
+        <v>122513932</v>
       </c>
       <c r="B15" t="n">
-        <v>57447</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2268,35 +2252,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100136</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2305,10 +2285,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519384</v>
+        <v>519417</v>
       </c>
       <c r="R15" t="n">
-        <v>7055266</v>
+        <v>7055533</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2341,6 +2321,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2479,10 +2464,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122514293</v>
+        <v>122513469</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2495,34 +2480,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519526</v>
+        <v>519319</v>
       </c>
       <c r="R17" t="n">
-        <v>7055378</v>
+        <v>7055189</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2557,6 +2547,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2565,31 +2560,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2606,10 +2576,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122513469</v>
+        <v>122513793</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2622,39 +2592,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519319</v>
+        <v>519310</v>
       </c>
       <c r="R18" t="n">
-        <v>7055189</v>
+        <v>7055186</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2689,11 +2654,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2702,6 +2662,31 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2718,10 +2703,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122513607</v>
+        <v>122513926</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2734,42 +2719,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519387</v>
+        <v>519405</v>
       </c>
       <c r="R19" t="n">
-        <v>7055266</v>
+        <v>7055243</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2801,11 +2781,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2814,6 +2789,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122513607</v>
+        <v>122514485</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519387</v>
+        <v>519340</v>
       </c>
       <c r="R2" t="n">
-        <v>7055266</v>
+        <v>7055482</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,11 +753,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,6 +761,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122514485</v>
+        <v>122513607</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +818,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519340</v>
+        <v>519387</v>
       </c>
       <c r="R3" t="n">
-        <v>7055482</v>
+        <v>7055266</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,6 +885,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -873,31 +898,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122513843</v>
+        <v>122513788</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,34 +930,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519326</v>
+        <v>519313</v>
       </c>
       <c r="R4" t="n">
-        <v>7055234</v>
+        <v>7055191</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,6 +997,11 @@
           <t>2025-02-08</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1003,7 +1013,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1018,12 +1028,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1041,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122513788</v>
+        <v>122513843</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,39 +1067,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519313</v>
+        <v>519326</v>
       </c>
       <c r="R5" t="n">
-        <v>7055191</v>
+        <v>7055234</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,11 +1129,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -2034,7 +2034,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -2030,7 +2030,7 @@
         <v>122513620</v>
       </c>
       <c r="B13" t="n">
-        <v>57447</v>
+        <v>57450</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -2030,7 +2030,7 @@
         <v>122513620</v>
       </c>
       <c r="B13" t="n">
-        <v>57450</v>
+        <v>57456</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -2030,7 +2030,7 @@
         <v>122513620</v>
       </c>
       <c r="B13" t="n">
-        <v>57456</v>
+        <v>57459</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -2030,7 +2030,7 @@
         <v>122513620</v>
       </c>
       <c r="B13" t="n">
-        <v>57459</v>
+        <v>57460</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2828,6 +2828,113 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>123543627</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Öjån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>519406</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7055512</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack färska. Även flertal äldre ringhack förekommer i området.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Linda  Höglund</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Linda  Höglund</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -2830,7 +2830,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123543627</v>
+        <v>123542918</v>
       </c>
       <c r="B20" t="n">
         <v>57491</v>
@@ -2864,6 +2864,10 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Öjån, Jmt</t>
@@ -2903,14 +2907,19 @@
           <t>2025-03-28</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-28</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack färska. Även flertal äldre ringhack förekommer i området.</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -2830,7 +2830,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123542918</v>
+        <v>123543627</v>
       </c>
       <c r="B20" t="n">
         <v>57491</v>
@@ -2864,10 +2864,6 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Öjån, Jmt</t>
@@ -2907,19 +2903,14 @@
           <t>2025-03-28</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-28</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:44</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack färska. Även flertal äldre ringhack förekommer i området.</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2944,6 +2944,4150 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129310773</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92857</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>519497</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7055506</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129313853</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92257</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>519415</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7055795</v>
+      </c>
+      <c r="S22" t="n">
+        <v>8</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129313937</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91536</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>519405</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7055762</v>
+      </c>
+      <c r="S23" t="n">
+        <v>7</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129313980</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>519421</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7055771</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i en gran.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129311450</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>519497</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7055786</v>
+      </c>
+      <c r="S25" t="n">
+        <v>11</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, längs flera meter på en gran vid åkanten.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129310852</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92494</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>519479</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7055528</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129309748</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92857</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>519381</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7055220</v>
+      </c>
+      <c r="S27" t="n">
+        <v>8</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129307091</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98610</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>504</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>519283</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7055063</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>8 vissna plantor av guckusko i en liten sänka.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129314194</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>519427</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7055741</v>
+      </c>
+      <c r="S29" t="n">
+        <v>9</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129309922</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98608</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>519372</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7055266</v>
+      </c>
+      <c r="S30" t="n">
+        <v>9</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 1 fröställning inom 0,2 m2 yta.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129310410</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>519532</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7055358</v>
+      </c>
+      <c r="S31" t="n">
+        <v>8</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129310986</v>
+      </c>
+      <c r="B32" t="n">
+        <v>92494</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>519482</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7055550</v>
+      </c>
+      <c r="S32" t="n">
+        <v>11</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129307276</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91313</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>519259</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7055075</v>
+      </c>
+      <c r="S33" t="n">
+        <v>8</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Våtmark med barrträd</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129313884</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91536</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>519404</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7055773</v>
+      </c>
+      <c r="S34" t="n">
+        <v>7</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129313586</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>519436</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7055806</v>
+      </c>
+      <c r="S35" t="n">
+        <v>8</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129311001</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91558</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>519493</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7055555</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129308557</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>519390</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7055229</v>
+      </c>
+      <c r="S37" t="n">
+        <v>9</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Synobservation av 4 livliga talltitor som nyfiket dök upp på nära håll.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129310923</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>519476</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7055536</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Minst 1 talltita i flerskiktad gammal granskog och gransumpskog.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129316798</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>519455</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7055533</v>
+      </c>
+      <c r="S39" t="n">
+        <v>11</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gränsen till färska, på stambasen av en gran.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129308765</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91558</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>519386</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7055265</v>
+      </c>
+      <c r="S40" t="n">
+        <v>8</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Växer i en stubbe av en gran som knäckts i stambasen.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129306797</v>
+      </c>
+      <c r="B41" t="n">
+        <v>92494</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>519293</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7055067</v>
+      </c>
+      <c r="S41" t="n">
+        <v>12</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129308971</v>
+      </c>
+      <c r="B42" t="n">
+        <v>80182</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>519353</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7055274</v>
+      </c>
+      <c r="S42" t="n">
+        <v>9</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129310002</v>
+      </c>
+      <c r="B43" t="n">
+        <v>80181</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>519344</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7055261</v>
+      </c>
+      <c r="S43" t="n">
+        <v>11</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På en lutande död sälg.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129306721</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>519304</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7055061</v>
+      </c>
+      <c r="S44" t="n">
+        <v>8</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, påtagligt och tydligt på stambasen av en gammal gran.</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129309053</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>519383</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7055292</v>
+      </c>
+      <c r="S45" t="n">
+        <v>9</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129309958</v>
+      </c>
+      <c r="B46" t="n">
+        <v>80147</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>519366</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7055274</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På en lutande död sälg.</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129307918</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>519302</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7055219</v>
+      </c>
+      <c r="S47" t="n">
+        <v>9</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129309664</v>
+      </c>
+      <c r="B48" t="n">
+        <v>97581</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>519401</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7055248</v>
+      </c>
+      <c r="S48" t="n">
+        <v>9</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129316769</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>519455</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7055526</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gränsen till färska, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129310040</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>519359</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7055281</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129313241</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>519454</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7055805</v>
+      </c>
+      <c r="S51" t="n">
+        <v>11</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gränsen till färska, längs flera meter på en gran.</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -2949,7 +2949,7 @@
         <v>129310773</v>
       </c>
       <c r="B21" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>129313853</v>
       </c>
       <c r="B22" t="n">
-        <v>92257</v>
+        <v>92258</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>129310852</v>
       </c>
       <c r="B26" t="n">
-        <v>92494</v>
+        <v>92495</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3743,10 +3743,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129309748</v>
+        <v>129307091</v>
       </c>
       <c r="B27" t="n">
-        <v>92857</v>
+        <v>98611</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3754,27 +3754,41 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5964</v>
+        <v>504</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3783,13 +3797,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519381</v>
+        <v>519283</v>
       </c>
       <c r="R27" t="n">
-        <v>7055220</v>
+        <v>7055063</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3818,7 +3832,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3828,7 +3842,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>8 vissna plantor av guckusko i en liten sänka.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3860,10 +3879,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129307091</v>
+        <v>129309748</v>
       </c>
       <c r="B28" t="n">
-        <v>98610</v>
+        <v>92858</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3871,41 +3890,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>504</v>
+        <v>5964</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3914,13 +3919,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519283</v>
+        <v>519381</v>
       </c>
       <c r="R28" t="n">
-        <v>7055063</v>
+        <v>7055220</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3949,7 +3954,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3959,12 +3964,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:36</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>8 vissna plantor av guckusko i en liten sänka.</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3996,45 +3996,55 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129314194</v>
+        <v>129309922</v>
       </c>
       <c r="B29" t="n">
-        <v>79041</v>
+        <v>98609</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519427</v>
+        <v>519372</v>
       </c>
       <c r="R29" t="n">
-        <v>7055741</v>
+        <v>7055266</v>
       </c>
       <c r="S29" t="n">
         <v>9</v>
@@ -4066,7 +4076,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4076,7 +4086,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Minst 1 fröställning inom 0,2 m2 yta.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4090,27 +4105,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4128,55 +4123,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129309922</v>
+        <v>129314194</v>
       </c>
       <c r="B30" t="n">
-        <v>98608</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519372</v>
+        <v>519427</v>
       </c>
       <c r="R30" t="n">
-        <v>7055266</v>
+        <v>7055741</v>
       </c>
       <c r="S30" t="n">
         <v>9</v>
@@ -4208,7 +4193,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4218,12 +4203,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minst 1 fröställning inom 0,2 m2 yta.</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4237,7 +4217,27 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4255,43 +4255,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129310410</v>
+        <v>129310986</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>92495</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4300,13 +4295,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519532</v>
+        <v>519482</v>
       </c>
       <c r="R31" t="n">
-        <v>7055358</v>
+        <v>7055550</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4335,7 +4330,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4345,12 +4340,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4364,27 +4354,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4402,38 +4372,43 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129310986</v>
+        <v>129310410</v>
       </c>
       <c r="B32" t="n">
-        <v>92494</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4442,13 +4417,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519482</v>
+        <v>519532</v>
       </c>
       <c r="R32" t="n">
-        <v>7055550</v>
+        <v>7055358</v>
       </c>
       <c r="S32" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4477,7 +4452,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4487,7 +4462,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4501,7 +4481,27 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4908,7 +4908,7 @@
         <v>129311001</v>
       </c>
       <c r="B36" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4925,14 +4925,10 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
@@ -5309,43 +5305,38 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129316798</v>
+        <v>129306797</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>92495</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5354,13 +5345,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519455</v>
+        <v>519293</v>
       </c>
       <c r="R39" t="n">
-        <v>7055533</v>
+        <v>7055067</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5389,7 +5380,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5399,12 +5390,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:37</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gränsen till färska, på stambasen av en gran.</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5419,26 +5405,6 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5459,7 +5425,7 @@
         <v>129308765</v>
       </c>
       <c r="B40" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5476,14 +5442,10 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
@@ -5598,38 +5560,43 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129306797</v>
+        <v>129316798</v>
       </c>
       <c r="B41" t="n">
-        <v>92494</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5638,13 +5605,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>519293</v>
+        <v>519455</v>
       </c>
       <c r="R41" t="n">
-        <v>7055067</v>
+        <v>7055533</v>
       </c>
       <c r="S41" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5673,7 +5640,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5683,7 +5650,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gränsen till färska, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5698,6 +5670,26 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5857,32 +5849,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129310002</v>
+        <v>129309958</v>
       </c>
       <c r="B43" t="n">
-        <v>80181</v>
+        <v>80147</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5897,13 +5889,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519344</v>
+        <v>519366</v>
       </c>
       <c r="R43" t="n">
-        <v>7055261</v>
+        <v>7055274</v>
       </c>
       <c r="S43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5932,7 +5924,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5942,7 +5934,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -5999,43 +5991,38 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129306721</v>
+        <v>129310002</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>80181</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6044,13 +6031,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519304</v>
+        <v>519344</v>
       </c>
       <c r="R44" t="n">
-        <v>7055061</v>
+        <v>7055261</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6079,7 +6066,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6089,12 +6076,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, påtagligt och tydligt på stambasen av en gammal gran.</t>
+          <t>På en lutande död sälg.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6113,22 +6100,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6278,10 +6265,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129309958</v>
+        <v>129306721</v>
       </c>
       <c r="B46" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6289,27 +6276,32 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6318,13 +6310,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519366</v>
+        <v>519304</v>
       </c>
       <c r="R46" t="n">
-        <v>7055274</v>
+        <v>7055061</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6353,7 +6345,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6363,12 +6355,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På en lutande död sälg.</t>
+          <t>Ringhack, äldre, påtagligt och tydligt på stambasen av en gammal gran.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6387,22 +6379,22 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6555,7 +6547,7 @@
         <v>129309664</v>
       </c>
       <c r="B48" t="n">
-        <v>97581</v>
+        <v>97582</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6664,10 +6656,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129316769</v>
+        <v>129310040</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6675,44 +6667,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519455</v>
+        <v>519359</v>
       </c>
       <c r="R49" t="n">
-        <v>7055526</v>
+        <v>7055281</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6744,7 +6726,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6754,12 +6736,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:35</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gränsen till färska, på en gran.</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6788,12 +6765,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6811,10 +6788,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129310040</v>
+        <v>129316769</v>
       </c>
       <c r="B50" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6822,34 +6799,44 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>519359</v>
+        <v>519455</v>
       </c>
       <c r="R50" t="n">
-        <v>7055281</v>
+        <v>7055526</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6881,7 +6868,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6891,7 +6878,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gränsen till färska, på en gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6920,12 +6912,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -3337,10 +3337,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129313980</v>
+        <v>129311450</v>
       </c>
       <c r="B24" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,16 +3348,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3371,19 +3371,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>519421</v>
+        <v>519497</v>
       </c>
       <c r="R24" t="n">
-        <v>7055771</v>
+        <v>7055786</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3412,7 +3417,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3422,12 +3427,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i en gran.</t>
+          <t>Ringhack, äldre, längs flera meter på en gran vid åkanten.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3479,10 +3484,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129311450</v>
+        <v>129313980</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3490,16 +3495,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3513,24 +3518,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519497</v>
+        <v>519421</v>
       </c>
       <c r="R25" t="n">
-        <v>7055786</v>
+        <v>7055771</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3569,12 +3569,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs flera meter på en gran vid åkanten.</t>
+          <t>Rejäla hackspår i en gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3743,10 +3743,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129307091</v>
+        <v>129309748</v>
       </c>
       <c r="B27" t="n">
-        <v>98611</v>
+        <v>92858</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3754,41 +3754,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>504</v>
+        <v>5964</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3797,13 +3783,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519283</v>
+        <v>519381</v>
       </c>
       <c r="R27" t="n">
-        <v>7055063</v>
+        <v>7055220</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3832,7 +3818,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3842,12 +3828,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:36</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>8 vissna plantor av guckusko i en liten sänka.</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3879,53 +3860,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129309748</v>
+        <v>129314194</v>
       </c>
       <c r="B28" t="n">
-        <v>92858</v>
+        <v>79041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519381</v>
+        <v>519427</v>
       </c>
       <c r="R28" t="n">
-        <v>7055220</v>
+        <v>7055741</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3954,7 +3930,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3964,7 +3940,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3978,7 +3954,27 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3996,10 +3992,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129309922</v>
+        <v>129307091</v>
       </c>
       <c r="B29" t="n">
-        <v>98609</v>
+        <v>98612</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4007,27 +4003,36 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220093</v>
+        <v>504</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4041,13 +4046,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519372</v>
+        <v>519283</v>
       </c>
       <c r="R29" t="n">
-        <v>7055266</v>
+        <v>7055063</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4076,7 +4081,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4086,12 +4091,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Minst 1 fröställning inom 0,2 m2 yta.</t>
+          <t>8 vissna plantor av guckusko i en liten sänka.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4123,45 +4128,55 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129314194</v>
+        <v>129309922</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>98610</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519427</v>
+        <v>519372</v>
       </c>
       <c r="R30" t="n">
-        <v>7055741</v>
+        <v>7055266</v>
       </c>
       <c r="S30" t="n">
         <v>9</v>
@@ -4193,7 +4208,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4203,7 +4218,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 1 fröställning inom 0,2 m2 yta.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4217,27 +4237,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4519,32 +4519,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129307276</v>
+        <v>129313884</v>
       </c>
       <c r="B33" t="n">
-        <v>91313</v>
+        <v>91536</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3215</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4559,13 +4559,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519259</v>
+        <v>519404</v>
       </c>
       <c r="R33" t="n">
-        <v>7055075</v>
+        <v>7055773</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4618,7 +4618,27 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Våtmark med barrträd</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4636,32 +4656,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129313884</v>
+        <v>129307276</v>
       </c>
       <c r="B34" t="n">
-        <v>91536</v>
+        <v>91313</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>3215</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4676,13 +4696,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>519404</v>
+        <v>519259</v>
       </c>
       <c r="R34" t="n">
-        <v>7055773</v>
+        <v>7055075</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4711,7 +4731,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4721,7 +4741,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4735,27 +4755,7 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Våtmark med barrträd</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5305,38 +5305,43 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129306797</v>
+        <v>129316798</v>
       </c>
       <c r="B39" t="n">
-        <v>92495</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5345,13 +5350,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519293</v>
+        <v>519455</v>
       </c>
       <c r="R39" t="n">
-        <v>7055067</v>
+        <v>7055533</v>
       </c>
       <c r="S39" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5380,7 +5385,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5390,7 +5395,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gränsen till färska, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5405,6 +5415,26 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5560,43 +5590,38 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129316798</v>
+        <v>129306797</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>92495</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5605,13 +5630,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>519455</v>
+        <v>519293</v>
       </c>
       <c r="R41" t="n">
-        <v>7055533</v>
+        <v>7055067</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5640,7 +5665,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5650,12 +5675,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:37</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gränsen till färska, på stambasen av en gran.</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5670,26 +5690,6 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5849,32 +5849,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129309958</v>
+        <v>129310002</v>
       </c>
       <c r="B43" t="n">
-        <v>80147</v>
+        <v>80181</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5889,13 +5889,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519366</v>
+        <v>519344</v>
       </c>
       <c r="R43" t="n">
-        <v>7055274</v>
+        <v>7055261</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -5991,32 +5991,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129310002</v>
+        <v>129309958</v>
       </c>
       <c r="B44" t="n">
-        <v>80181</v>
+        <v>80147</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6031,13 +6031,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519344</v>
+        <v>519366</v>
       </c>
       <c r="R44" t="n">
-        <v>7055261</v>
+        <v>7055274</v>
       </c>
       <c r="S44" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -6133,10 +6133,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129309053</v>
+        <v>129306721</v>
       </c>
       <c r="B45" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6144,37 +6144,47 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519383</v>
+        <v>519304</v>
       </c>
       <c r="R45" t="n">
-        <v>7055292</v>
+        <v>7055061</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6203,7 +6213,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6213,7 +6223,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, påtagligt och tydligt på stambasen av en gammal gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6242,12 +6257,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6265,10 +6280,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129306721</v>
+        <v>129309053</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6276,47 +6291,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519304</v>
+        <v>519383</v>
       </c>
       <c r="R46" t="n">
-        <v>7055061</v>
+        <v>7055292</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6345,7 +6350,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6355,12 +6360,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, påtagligt och tydligt på stambasen av en gammal gran.</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6389,12 +6389,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6547,7 +6547,7 @@
         <v>129309664</v>
       </c>
       <c r="B48" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -2949,7 +2949,7 @@
         <v>129310773</v>
       </c>
       <c r="B21" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>129313853</v>
       </c>
       <c r="B22" t="n">
-        <v>92258</v>
+        <v>92261</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>129313937</v>
       </c>
       <c r="B23" t="n">
-        <v>91536</v>
+        <v>91539</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3337,10 +3337,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129311450</v>
+        <v>129313980</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,16 +3348,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3371,24 +3371,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>519497</v>
+        <v>519421</v>
       </c>
       <c r="R24" t="n">
-        <v>7055786</v>
+        <v>7055771</v>
       </c>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3417,7 +3412,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3427,12 +3422,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs flera meter på en gran vid åkanten.</t>
+          <t>Rejäla hackspår i en gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3484,10 +3479,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129313980</v>
+        <v>129311450</v>
       </c>
       <c r="B25" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3495,16 +3490,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3518,19 +3513,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519421</v>
+        <v>519497</v>
       </c>
       <c r="R25" t="n">
-        <v>7055771</v>
+        <v>7055786</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3569,12 +3569,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i en gran.</t>
+          <t>Ringhack, äldre, längs flera meter på en gran vid åkanten.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3629,7 +3629,7 @@
         <v>129310852</v>
       </c>
       <c r="B26" t="n">
-        <v>92495</v>
+        <v>92498</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3743,10 +3743,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129309748</v>
+        <v>129307091</v>
       </c>
       <c r="B27" t="n">
-        <v>92858</v>
+        <v>98616</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3754,27 +3754,41 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5964</v>
+        <v>504</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3783,13 +3797,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519381</v>
+        <v>519283</v>
       </c>
       <c r="R27" t="n">
-        <v>7055220</v>
+        <v>7055063</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3818,7 +3832,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3828,7 +3842,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>8 vissna plantor av guckusko i en liten sänka.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3860,48 +3879,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129314194</v>
+        <v>129309748</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>92861</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519427</v>
+        <v>519381</v>
       </c>
       <c r="R28" t="n">
-        <v>7055741</v>
+        <v>7055220</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3930,7 +3954,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3940,7 +3964,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3954,27 +3978,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3992,67 +3996,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129307091</v>
+        <v>129314194</v>
       </c>
       <c r="B29" t="n">
-        <v>98612</v>
+        <v>79043</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>504</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519283</v>
+        <v>519427</v>
       </c>
       <c r="R29" t="n">
-        <v>7055063</v>
+        <v>7055741</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4081,7 +4066,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4091,12 +4076,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:36</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>8 vissna plantor av guckusko i en liten sänka.</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4110,7 +4090,27 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4131,7 +4131,7 @@
         <v>129309922</v>
       </c>
       <c r="B30" t="n">
-        <v>98610</v>
+        <v>98614</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>129310986</v>
       </c>
       <c r="B31" t="n">
-        <v>92495</v>
+        <v>92498</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>129313884</v>
       </c>
       <c r="B33" t="n">
-        <v>91536</v>
+        <v>91539</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>129307276</v>
       </c>
       <c r="B34" t="n">
-        <v>91313</v>
+        <v>91316</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>129313586</v>
       </c>
       <c r="B35" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>129311001</v>
       </c>
       <c r="B36" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129308557</v>
+        <v>129310923</v>
       </c>
       <c r="B37" t="n">
         <v>57887</v>
@@ -5068,12 +5068,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -5092,13 +5087,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519390</v>
+        <v>519476</v>
       </c>
       <c r="R37" t="n">
-        <v>7055229</v>
+        <v>7055536</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5127,7 +5122,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5137,12 +5132,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Synobservation av 4 livliga talltitor som nyfiket dök upp på nära håll.</t>
+          <t>Minst 1 talltita i flerskiktad gammal granskog och gransumpskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5174,7 +5169,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129310923</v>
+        <v>129308557</v>
       </c>
       <c r="B38" t="n">
         <v>57887</v>
@@ -5204,7 +5199,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -5223,13 +5223,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519476</v>
+        <v>519390</v>
       </c>
       <c r="R38" t="n">
-        <v>7055536</v>
+        <v>7055229</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Minst 1 talltita i flerskiktad gammal granskog och gransumpskog.</t>
+          <t>Synobservation av 4 livliga talltitor som nyfiket dök upp på nära håll.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5305,10 +5305,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129316798</v>
+        <v>129308765</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>91563</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5316,32 +5316,23 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5350,13 +5341,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519455</v>
+        <v>519386</v>
       </c>
       <c r="R39" t="n">
-        <v>7055533</v>
+        <v>7055265</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5385,7 +5376,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5395,12 +5386,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska, på stambasen av en gran.</t>
+          <t>Växer i en stubbe av en gran som knäckts i stambasen.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5429,12 +5420,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5452,30 +5443,34 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129308765</v>
+        <v>129306797</v>
       </c>
       <c r="B40" t="n">
-        <v>91560</v>
+        <v>92498</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>4769</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
@@ -5488,13 +5483,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519386</v>
+        <v>519293</v>
       </c>
       <c r="R40" t="n">
-        <v>7055265</v>
+        <v>7055067</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5523,7 +5518,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5533,12 +5528,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Växer i en stubbe av en gran som knäckts i stambasen.</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5553,26 +5543,6 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5590,38 +5560,43 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129306797</v>
+        <v>129316798</v>
       </c>
       <c r="B41" t="n">
-        <v>92495</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5630,13 +5605,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>519293</v>
+        <v>519455</v>
       </c>
       <c r="R41" t="n">
-        <v>7055067</v>
+        <v>7055533</v>
       </c>
       <c r="S41" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5665,7 +5640,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5675,7 +5650,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gränsen till färska, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5690,6 +5670,26 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5710,7 +5710,7 @@
         <v>129308971</v>
       </c>
       <c r="B42" t="n">
-        <v>80182</v>
+        <v>80184</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5849,27 +5849,27 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129310002</v>
+        <v>129307918</v>
       </c>
       <c r="B43" t="n">
-        <v>80181</v>
+        <v>79043</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5878,24 +5878,19 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519344</v>
+        <v>519302</v>
       </c>
       <c r="R43" t="n">
-        <v>7055261</v>
+        <v>7055219</v>
       </c>
       <c r="S43" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5924,7 +5919,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5934,12 +5929,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På en lutande död sälg.</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5958,22 +5948,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5991,10 +5981,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129309958</v>
+        <v>129309053</v>
       </c>
       <c r="B44" t="n">
-        <v>80147</v>
+        <v>79043</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6002,42 +5992,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519366</v>
+        <v>519383</v>
       </c>
       <c r="R44" t="n">
-        <v>7055274</v>
+        <v>7055292</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6066,7 +6051,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6076,12 +6061,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På en lutande död sälg.</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6100,22 +6080,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6280,10 +6260,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129309053</v>
+        <v>129309958</v>
       </c>
       <c r="B46" t="n">
-        <v>79041</v>
+        <v>80149</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6291,37 +6271,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519383</v>
+        <v>519366</v>
       </c>
       <c r="R46" t="n">
-        <v>7055292</v>
+        <v>7055274</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6350,7 +6335,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6360,7 +6345,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På en lutande död sälg.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6379,22 +6369,22 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6412,27 +6402,27 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129307918</v>
+        <v>129310002</v>
       </c>
       <c r="B47" t="n">
-        <v>79041</v>
+        <v>80183</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -6441,19 +6431,24 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519302</v>
+        <v>519344</v>
       </c>
       <c r="R47" t="n">
-        <v>7055219</v>
+        <v>7055261</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6482,7 +6477,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6492,7 +6487,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På en lutande död sälg.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6511,22 +6511,22 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6547,7 +6547,7 @@
         <v>129309664</v>
       </c>
       <c r="B48" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6656,10 +6656,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129310040</v>
+        <v>129316769</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6667,34 +6667,44 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519359</v>
+        <v>519455</v>
       </c>
       <c r="R49" t="n">
-        <v>7055281</v>
+        <v>7055526</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6726,7 +6736,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6736,7 +6746,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gränsen till färska, på en gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6765,12 +6780,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6788,7 +6803,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129316769</v>
+        <v>129313241</v>
       </c>
       <c r="B50" t="n">
         <v>57727</v>
@@ -6833,13 +6848,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>519455</v>
+        <v>519454</v>
       </c>
       <c r="R50" t="n">
-        <v>7055526</v>
+        <v>7055805</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6868,7 +6883,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6878,12 +6893,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska, på en gran.</t>
+          <t>Ringhack, äldre, på gränsen till färska, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6897,7 +6912,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -6935,10 +6950,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129313241</v>
+        <v>129310040</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6946,47 +6961,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519454</v>
+        <v>519359</v>
       </c>
       <c r="R51" t="n">
-        <v>7055805</v>
+        <v>7055281</v>
       </c>
       <c r="S51" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7015,7 +7020,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7025,12 +7030,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:40</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gränsen till färska, längs flera meter på en gran.</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -3743,67 +3743,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129307091</v>
+        <v>129314194</v>
       </c>
       <c r="B27" t="n">
-        <v>98616</v>
+        <v>79043</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>504</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519283</v>
+        <v>519427</v>
       </c>
       <c r="R27" t="n">
-        <v>7055063</v>
+        <v>7055741</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3832,7 +3813,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3842,12 +3823,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:36</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>8 vissna plantor av guckusko i en liten sänka.</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3861,7 +3837,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3879,10 +3875,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129309748</v>
+        <v>129307091</v>
       </c>
       <c r="B28" t="n">
-        <v>92861</v>
+        <v>98616</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3890,27 +3886,41 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5964</v>
+        <v>504</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3919,13 +3929,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519381</v>
+        <v>519283</v>
       </c>
       <c r="R28" t="n">
-        <v>7055220</v>
+        <v>7055063</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3954,7 +3964,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3964,7 +3974,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>8 vissna plantor av guckusko i en liten sänka.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3996,48 +4011,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129314194</v>
+        <v>129309748</v>
       </c>
       <c r="B29" t="n">
-        <v>79043</v>
+        <v>92861</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519427</v>
+        <v>519381</v>
       </c>
       <c r="R29" t="n">
-        <v>7055741</v>
+        <v>7055220</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4066,7 +4086,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4076,7 +4096,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4090,27 +4110,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -6656,10 +6656,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129316769</v>
+        <v>129310040</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6667,44 +6667,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519455</v>
+        <v>519359</v>
       </c>
       <c r="R49" t="n">
-        <v>7055526</v>
+        <v>7055281</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6736,7 +6726,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6746,12 +6736,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:35</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gränsen till färska, på en gran.</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6780,12 +6765,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6803,7 +6788,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129313241</v>
+        <v>129316769</v>
       </c>
       <c r="B50" t="n">
         <v>57727</v>
@@ -6848,13 +6833,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>519454</v>
+        <v>519455</v>
       </c>
       <c r="R50" t="n">
-        <v>7055805</v>
+        <v>7055526</v>
       </c>
       <c r="S50" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6883,7 +6868,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6893,12 +6878,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska, längs flera meter på en gran.</t>
+          <t>Ringhack, äldre, på gränsen till färska, på en gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6912,7 +6897,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -6950,10 +6935,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129310040</v>
+        <v>129313241</v>
       </c>
       <c r="B51" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6961,37 +6946,47 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519359</v>
+        <v>519454</v>
       </c>
       <c r="R51" t="n">
-        <v>7055281</v>
+        <v>7055805</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7020,7 +7015,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7030,7 +7025,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gränsen till färska, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -2949,7 +2949,7 @@
         <v>129310773</v>
       </c>
       <c r="B21" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>129313853</v>
       </c>
       <c r="B22" t="n">
-        <v>92261</v>
+        <v>92263</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>129313937</v>
       </c>
       <c r="B23" t="n">
-        <v>91539</v>
+        <v>91541</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3337,10 +3337,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129313980</v>
+        <v>129311450</v>
       </c>
       <c r="B24" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,16 +3348,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3371,19 +3371,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>519421</v>
+        <v>519497</v>
       </c>
       <c r="R24" t="n">
-        <v>7055771</v>
+        <v>7055786</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3412,7 +3417,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3422,12 +3427,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i en gran.</t>
+          <t>Ringhack, äldre, längs flera meter på en gran vid åkanten.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3479,10 +3484,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129311450</v>
+        <v>129313980</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3490,16 +3495,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3513,24 +3518,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519497</v>
+        <v>519421</v>
       </c>
       <c r="R25" t="n">
-        <v>7055786</v>
+        <v>7055771</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3569,12 +3569,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs flera meter på en gran vid åkanten.</t>
+          <t>Rejäla hackspår i en gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3629,7 +3629,7 @@
         <v>129310852</v>
       </c>
       <c r="B26" t="n">
-        <v>92498</v>
+        <v>92500</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3743,48 +3743,67 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129314194</v>
+        <v>129307091</v>
       </c>
       <c r="B27" t="n">
-        <v>79043</v>
+        <v>98618</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>504</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519427</v>
+        <v>519283</v>
       </c>
       <c r="R27" t="n">
-        <v>7055741</v>
+        <v>7055063</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3813,7 +3832,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3823,7 +3842,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>8 vissna plantor av guckusko i en liten sänka.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3837,27 +3861,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3875,10 +3879,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129307091</v>
+        <v>129309748</v>
       </c>
       <c r="B28" t="n">
-        <v>98616</v>
+        <v>92863</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3886,41 +3890,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>504</v>
+        <v>5964</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3929,13 +3919,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519283</v>
+        <v>519381</v>
       </c>
       <c r="R28" t="n">
-        <v>7055063</v>
+        <v>7055220</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3964,7 +3954,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3974,12 +3964,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:36</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>8 vissna plantor av guckusko i en liten sänka.</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4011,53 +3996,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129309748</v>
+        <v>129314194</v>
       </c>
       <c r="B29" t="n">
-        <v>92861</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519381</v>
+        <v>519427</v>
       </c>
       <c r="R29" t="n">
-        <v>7055220</v>
+        <v>7055741</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4086,7 +4066,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4096,7 +4076,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4110,7 +4090,27 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4131,7 +4131,7 @@
         <v>129309922</v>
       </c>
       <c r="B30" t="n">
-        <v>98614</v>
+        <v>98616</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>129310986</v>
       </c>
       <c r="B31" t="n">
-        <v>92498</v>
+        <v>92500</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>129313884</v>
       </c>
       <c r="B33" t="n">
-        <v>91539</v>
+        <v>91541</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>129307276</v>
       </c>
       <c r="B34" t="n">
-        <v>91316</v>
+        <v>91318</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>129313586</v>
       </c>
       <c r="B35" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>129311001</v>
       </c>
       <c r="B36" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129310923</v>
+        <v>129308557</v>
       </c>
       <c r="B37" t="n">
         <v>57887</v>
@@ -5068,7 +5068,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -5087,13 +5092,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519476</v>
+        <v>519390</v>
       </c>
       <c r="R37" t="n">
-        <v>7055536</v>
+        <v>7055229</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5122,7 +5127,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5132,12 +5137,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Minst 1 talltita i flerskiktad gammal granskog och gransumpskog.</t>
+          <t>Synobservation av 4 livliga talltitor som nyfiket dök upp på nära håll.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5169,7 +5174,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129308557</v>
+        <v>129310923</v>
       </c>
       <c r="B38" t="n">
         <v>57887</v>
@@ -5199,12 +5204,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -5223,13 +5223,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519390</v>
+        <v>519476</v>
       </c>
       <c r="R38" t="n">
-        <v>7055229</v>
+        <v>7055536</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Synobservation av 4 livliga talltitor som nyfiket dök upp på nära håll.</t>
+          <t>Minst 1 talltita i flerskiktad gammal granskog och gransumpskog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5308,7 +5308,7 @@
         <v>129308765</v>
       </c>
       <c r="B39" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>129306797</v>
       </c>
       <c r="B40" t="n">
-        <v>92498</v>
+        <v>92500</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>129308971</v>
       </c>
       <c r="B42" t="n">
-        <v>80184</v>
+        <v>80185</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5849,10 +5849,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129307918</v>
+        <v>129309053</v>
       </c>
       <c r="B43" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5884,10 +5884,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519302</v>
+        <v>519383</v>
       </c>
       <c r="R43" t="n">
-        <v>7055219</v>
+        <v>7055292</v>
       </c>
       <c r="S43" t="n">
         <v>9</v>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5981,10 +5981,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129309053</v>
+        <v>129307918</v>
       </c>
       <c r="B44" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519383</v>
+        <v>519302</v>
       </c>
       <c r="R44" t="n">
-        <v>7055292</v>
+        <v>7055219</v>
       </c>
       <c r="S44" t="n">
         <v>9</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6113,43 +6113,38 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129306721</v>
+        <v>129310002</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>80184</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6158,13 +6153,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519304</v>
+        <v>519344</v>
       </c>
       <c r="R45" t="n">
-        <v>7055061</v>
+        <v>7055261</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6193,7 +6188,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6203,12 +6198,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, påtagligt och tydligt på stambasen av en gammal gran.</t>
+          <t>På en lutande död sälg.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6227,22 +6222,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6263,7 +6258,7 @@
         <v>129309958</v>
       </c>
       <c r="B46" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6402,38 +6397,43 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129310002</v>
+        <v>129306721</v>
       </c>
       <c r="B47" t="n">
-        <v>80183</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6442,13 +6442,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519344</v>
+        <v>519304</v>
       </c>
       <c r="R47" t="n">
-        <v>7055261</v>
+        <v>7055061</v>
       </c>
       <c r="S47" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På en lutande död sälg.</t>
+          <t>Ringhack, äldre, påtagligt och tydligt på stambasen av en gammal gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6511,22 +6511,22 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6547,7 +6547,7 @@
         <v>129309664</v>
       </c>
       <c r="B48" t="n">
-        <v>97587</v>
+        <v>97589</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>129310040</v>
       </c>
       <c r="B49" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129316769</v>
+        <v>129313241</v>
       </c>
       <c r="B50" t="n">
         <v>57727</v>
@@ -6833,13 +6833,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>519455</v>
+        <v>519454</v>
       </c>
       <c r="R50" t="n">
-        <v>7055526</v>
+        <v>7055805</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6878,12 +6878,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska, på en gran.</t>
+          <t>Ringhack, äldre, på gränsen till färska, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -6935,7 +6935,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129313241</v>
+        <v>129316769</v>
       </c>
       <c r="B51" t="n">
         <v>57727</v>
@@ -6980,13 +6980,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519454</v>
+        <v>519455</v>
       </c>
       <c r="R51" t="n">
-        <v>7055805</v>
+        <v>7055526</v>
       </c>
       <c r="S51" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska, längs flera meter på en gran.</t>
+          <t>Ringhack, äldre, på gränsen till färska, på en gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -2949,7 +2949,7 @@
         <v>129310773</v>
       </c>
       <c r="B21" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>129313853</v>
       </c>
       <c r="B22" t="n">
-        <v>92263</v>
+        <v>92267</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>129313937</v>
       </c>
       <c r="B23" t="n">
-        <v>91541</v>
+        <v>91545</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3337,10 +3337,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129311450</v>
+        <v>129313980</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,16 +3348,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3371,24 +3371,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>519497</v>
+        <v>519421</v>
       </c>
       <c r="R24" t="n">
-        <v>7055786</v>
+        <v>7055771</v>
       </c>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3417,7 +3412,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3427,12 +3422,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs flera meter på en gran vid åkanten.</t>
+          <t>Rejäla hackspår i en gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3484,10 +3479,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129313980</v>
+        <v>129311450</v>
       </c>
       <c r="B25" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3495,16 +3490,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3518,19 +3513,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519421</v>
+        <v>519497</v>
       </c>
       <c r="R25" t="n">
-        <v>7055771</v>
+        <v>7055786</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3569,12 +3569,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i en gran.</t>
+          <t>Ringhack, äldre, längs flera meter på en gran vid åkanten.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3629,7 +3629,7 @@
         <v>129310852</v>
       </c>
       <c r="B26" t="n">
-        <v>92500</v>
+        <v>92504</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3743,67 +3743,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129307091</v>
+        <v>129314194</v>
       </c>
       <c r="B27" t="n">
-        <v>98618</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>504</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519283</v>
+        <v>519427</v>
       </c>
       <c r="R27" t="n">
-        <v>7055063</v>
+        <v>7055741</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3832,7 +3813,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3842,12 +3823,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:36</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>8 vissna plantor av guckusko i en liten sänka.</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3861,7 +3837,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3879,10 +3875,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129309748</v>
+        <v>129307091</v>
       </c>
       <c r="B28" t="n">
-        <v>92863</v>
+        <v>98622</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3890,27 +3886,41 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5964</v>
+        <v>504</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3919,13 +3929,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519381</v>
+        <v>519283</v>
       </c>
       <c r="R28" t="n">
-        <v>7055220</v>
+        <v>7055063</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3954,7 +3964,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3964,7 +3974,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>8 vissna plantor av guckusko i en liten sänka.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3996,48 +4011,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129314194</v>
+        <v>129309748</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>92867</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519427</v>
+        <v>519381</v>
       </c>
       <c r="R29" t="n">
-        <v>7055741</v>
+        <v>7055220</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4066,7 +4086,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4076,7 +4096,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4090,27 +4110,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4131,7 +4131,7 @@
         <v>129309922</v>
       </c>
       <c r="B30" t="n">
-        <v>98616</v>
+        <v>98620</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>129310986</v>
       </c>
       <c r="B31" t="n">
-        <v>92500</v>
+        <v>92504</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>129313884</v>
       </c>
       <c r="B33" t="n">
-        <v>91541</v>
+        <v>91545</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>129307276</v>
       </c>
       <c r="B34" t="n">
-        <v>91318</v>
+        <v>91322</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>129311001</v>
       </c>
       <c r="B36" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>129308765</v>
       </c>
       <c r="B39" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>129306797</v>
       </c>
       <c r="B40" t="n">
-        <v>92500</v>
+        <v>92504</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5849,10 +5849,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129309053</v>
+        <v>129309958</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5860,37 +5860,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519383</v>
+        <v>519366</v>
       </c>
       <c r="R43" t="n">
-        <v>7055292</v>
+        <v>7055274</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5919,7 +5924,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5929,7 +5934,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På en lutande död sälg.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5948,22 +5958,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5981,27 +5991,27 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129307918</v>
+        <v>129310002</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>80184</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -6010,19 +6020,24 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519302</v>
+        <v>519344</v>
       </c>
       <c r="R44" t="n">
-        <v>7055219</v>
+        <v>7055261</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6051,7 +6066,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6061,7 +6076,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På en lutande död sälg.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6080,22 +6100,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6113,27 +6133,27 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129310002</v>
+        <v>129309053</v>
       </c>
       <c r="B45" t="n">
-        <v>80184</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -6142,24 +6162,19 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519344</v>
+        <v>519383</v>
       </c>
       <c r="R45" t="n">
-        <v>7055261</v>
+        <v>7055292</v>
       </c>
       <c r="S45" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6188,7 +6203,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6198,12 +6213,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På en lutande död sälg.</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6222,22 +6232,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6255,10 +6265,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129309958</v>
+        <v>129307918</v>
       </c>
       <c r="B46" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6266,42 +6276,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519366</v>
+        <v>519302</v>
       </c>
       <c r="R46" t="n">
-        <v>7055274</v>
+        <v>7055219</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6330,7 +6335,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6340,12 +6345,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På en lutande död sälg.</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6364,22 +6364,22 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6547,7 +6547,7 @@
         <v>129309664</v>
       </c>
       <c r="B48" t="n">
-        <v>97589</v>
+        <v>97593</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129313241</v>
+        <v>129316769</v>
       </c>
       <c r="B50" t="n">
         <v>57727</v>
@@ -6833,13 +6833,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>519454</v>
+        <v>519455</v>
       </c>
       <c r="R50" t="n">
-        <v>7055805</v>
+        <v>7055526</v>
       </c>
       <c r="S50" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6878,12 +6878,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska, längs flera meter på en gran.</t>
+          <t>Ringhack, äldre, på gränsen till färska, på en gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -6935,7 +6935,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129316769</v>
+        <v>129313241</v>
       </c>
       <c r="B51" t="n">
         <v>57727</v>
@@ -6980,13 +6980,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519455</v>
+        <v>519454</v>
       </c>
       <c r="R51" t="n">
-        <v>7055526</v>
+        <v>7055805</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska, på en gran.</t>
+          <t>Ringhack, äldre, på gränsen till färska, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -2949,7 +2949,7 @@
         <v>129310773</v>
       </c>
       <c r="B21" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>129313853</v>
       </c>
       <c r="B22" t="n">
-        <v>92267</v>
+        <v>92268</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>129313937</v>
       </c>
       <c r="B23" t="n">
-        <v>91545</v>
+        <v>91546</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>129310852</v>
       </c>
       <c r="B26" t="n">
-        <v>92504</v>
+        <v>92505</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3743,48 +3743,67 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129314194</v>
+        <v>129307091</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>98630</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>504</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519427</v>
+        <v>519283</v>
       </c>
       <c r="R27" t="n">
-        <v>7055741</v>
+        <v>7055063</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3813,7 +3832,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3823,7 +3842,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>8 vissna plantor av guckusko i en liten sänka.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3837,27 +3861,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3875,67 +3879,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129307091</v>
+        <v>129314194</v>
       </c>
       <c r="B28" t="n">
-        <v>98622</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>504</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519283</v>
+        <v>519427</v>
       </c>
       <c r="R28" t="n">
-        <v>7055063</v>
+        <v>7055741</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3964,7 +3949,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3974,12 +3959,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:36</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>8 vissna plantor av guckusko i en liten sänka.</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3993,7 +3973,27 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4014,7 +4014,7 @@
         <v>129309748</v>
       </c>
       <c r="B29" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>129309922</v>
       </c>
       <c r="B30" t="n">
-        <v>98620</v>
+        <v>98628</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>129310986</v>
       </c>
       <c r="B31" t="n">
-        <v>92504</v>
+        <v>92505</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4519,32 +4519,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129313884</v>
+        <v>129307276</v>
       </c>
       <c r="B33" t="n">
-        <v>91545</v>
+        <v>91323</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>3215</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4559,13 +4559,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519404</v>
+        <v>519259</v>
       </c>
       <c r="R33" t="n">
-        <v>7055773</v>
+        <v>7055075</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4618,27 +4618,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Våtmark med barrträd</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4656,32 +4636,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129307276</v>
+        <v>129313884</v>
       </c>
       <c r="B34" t="n">
-        <v>91322</v>
+        <v>91546</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3215</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4696,13 +4676,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>519259</v>
+        <v>519404</v>
       </c>
       <c r="R34" t="n">
-        <v>7055075</v>
+        <v>7055773</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4731,7 +4711,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4741,7 +4721,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4755,7 +4735,27 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Våtmark med barrträd</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4908,7 +4908,7 @@
         <v>129311001</v>
       </c>
       <c r="B36" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>129308765</v>
       </c>
       <c r="B39" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>129306797</v>
       </c>
       <c r="B40" t="n">
-        <v>92504</v>
+        <v>92505</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5849,32 +5849,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129309958</v>
+        <v>129310002</v>
       </c>
       <c r="B43" t="n">
-        <v>80150</v>
+        <v>80184</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5889,13 +5889,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519366</v>
+        <v>519344</v>
       </c>
       <c r="R43" t="n">
-        <v>7055274</v>
+        <v>7055261</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -5991,27 +5991,27 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129310002</v>
+        <v>129309053</v>
       </c>
       <c r="B44" t="n">
-        <v>80184</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -6020,24 +6020,19 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519344</v>
+        <v>519383</v>
       </c>
       <c r="R44" t="n">
-        <v>7055261</v>
+        <v>7055292</v>
       </c>
       <c r="S44" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6066,7 +6061,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6076,12 +6071,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På en lutande död sälg.</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6100,22 +6090,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6133,7 +6123,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129309053</v>
+        <v>129307918</v>
       </c>
       <c r="B45" t="n">
         <v>79044</v>
@@ -6168,10 +6158,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519383</v>
+        <v>519302</v>
       </c>
       <c r="R45" t="n">
-        <v>7055292</v>
+        <v>7055219</v>
       </c>
       <c r="S45" t="n">
         <v>9</v>
@@ -6203,7 +6193,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6213,7 +6203,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6265,10 +6255,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129307918</v>
+        <v>129306721</v>
       </c>
       <c r="B46" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6276,37 +6266,47 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519302</v>
+        <v>519304</v>
       </c>
       <c r="R46" t="n">
-        <v>7055219</v>
+        <v>7055061</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6345,7 +6345,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, påtagligt och tydligt på stambasen av en gammal gran.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6374,12 +6379,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6397,10 +6402,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129306721</v>
+        <v>129309958</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6408,32 +6413,27 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6442,13 +6442,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519304</v>
+        <v>519366</v>
       </c>
       <c r="R47" t="n">
-        <v>7055061</v>
+        <v>7055274</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, påtagligt och tydligt på stambasen av en gammal gran.</t>
+          <t>På en lutande död sälg.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6511,22 +6511,22 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6547,7 +6547,7 @@
         <v>129309664</v>
       </c>
       <c r="B48" t="n">
-        <v>97593</v>
+        <v>97601</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -2243,12 +2243,7 @@
         <v>122513932</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2274,11 +2269,14 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
@@ -2325,7 +2323,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack, äldre, på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2336,6 +2334,31 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -3743,67 +3766,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129307091</v>
+        <v>129314194</v>
       </c>
       <c r="B27" t="n">
-        <v>98630</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>504</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519283</v>
+        <v>519427</v>
       </c>
       <c r="R27" t="n">
-        <v>7055063</v>
+        <v>7055741</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3832,7 +3836,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3842,12 +3846,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:36</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>8 vissna plantor av guckusko i en liten sänka.</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3861,7 +3860,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3879,45 +3898,55 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129314194</v>
+        <v>129309922</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>98628</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519427</v>
+        <v>519372</v>
       </c>
       <c r="R28" t="n">
-        <v>7055741</v>
+        <v>7055266</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -3949,7 +3978,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3959,7 +3988,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Minst 1 fröställning inom 0,2 m2 yta.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3973,27 +4007,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4128,10 +4142,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129309922</v>
+        <v>129310986</v>
       </c>
       <c r="B30" t="n">
-        <v>98628</v>
+        <v>92505</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4139,32 +4153,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220093</v>
+        <v>4769</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4173,13 +4182,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519372</v>
+        <v>519482</v>
       </c>
       <c r="R30" t="n">
-        <v>7055266</v>
+        <v>7055550</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4208,7 +4217,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4218,12 +4227,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minst 1 fröställning inom 0,2 m2 yta.</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4237,7 +4241,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4255,38 +4259,43 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129310986</v>
+        <v>129310410</v>
       </c>
       <c r="B31" t="n">
-        <v>92505</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4295,13 +4304,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519482</v>
+        <v>519532</v>
       </c>
       <c r="R31" t="n">
-        <v>7055550</v>
+        <v>7055358</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4330,7 +4339,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4340,7 +4349,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4354,7 +4368,27 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4372,10 +4406,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129310410</v>
+        <v>129313884</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>91546</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4383,32 +4417,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4417,13 +4446,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519532</v>
+        <v>519404</v>
       </c>
       <c r="R32" t="n">
-        <v>7055358</v>
+        <v>7055773</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4452,7 +4481,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4462,12 +4491,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4481,7 +4505,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -4636,10 +4660,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129313884</v>
+        <v>129313586</v>
       </c>
       <c r="B34" t="n">
-        <v>91546</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4647,42 +4671,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>519404</v>
+        <v>519436</v>
       </c>
       <c r="R34" t="n">
-        <v>7055773</v>
+        <v>7055806</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4711,7 +4730,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4721,7 +4740,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4750,12 +4769,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4773,10 +4792,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129313586</v>
+        <v>129311001</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>91570</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4784,37 +4803,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>519436</v>
+        <v>519493</v>
       </c>
       <c r="R35" t="n">
-        <v>7055806</v>
+        <v>7055555</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4843,7 +4863,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4853,7 +4873,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4882,12 +4902,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4905,10 +4925,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129311001</v>
+        <v>129308557</v>
       </c>
       <c r="B36" t="n">
-        <v>91570</v>
+        <v>57887</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4916,23 +4936,41 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4941,13 +4979,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>519493</v>
+        <v>519390</v>
       </c>
       <c r="R36" t="n">
-        <v>7055555</v>
+        <v>7055229</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4976,7 +5014,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4986,7 +5024,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Synobservation av 4 livliga talltitor som nyfiket dök upp på nära håll.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5001,26 +5044,6 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5038,7 +5061,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129308557</v>
+        <v>129310923</v>
       </c>
       <c r="B37" t="n">
         <v>57887</v>
@@ -5068,12 +5091,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -5092,13 +5110,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519390</v>
+        <v>519476</v>
       </c>
       <c r="R37" t="n">
-        <v>7055229</v>
+        <v>7055536</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5127,7 +5145,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5137,12 +5155,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Synobservation av 4 livliga talltitor som nyfiket dök upp på nära håll.</t>
+          <t>Minst 1 talltita i flerskiktad gammal granskog och gransumpskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5174,47 +5192,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129310923</v>
+        <v>129306797</v>
       </c>
       <c r="B38" t="n">
-        <v>57887</v>
+        <v>92505</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>4769</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5223,13 +5232,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519476</v>
+        <v>519293</v>
       </c>
       <c r="R38" t="n">
-        <v>7055536</v>
+        <v>7055067</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5258,7 +5267,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5268,12 +5277,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Minst 1 talltita i flerskiktad gammal granskog och gransumpskog.</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5287,7 +5291,7 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5443,38 +5447,43 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129306797</v>
+        <v>129316798</v>
       </c>
       <c r="B40" t="n">
-        <v>92505</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5483,13 +5492,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519293</v>
+        <v>519455</v>
       </c>
       <c r="R40" t="n">
-        <v>7055067</v>
+        <v>7055533</v>
       </c>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5518,7 +5527,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5528,7 +5537,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gränsen till färska, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5543,6 +5557,26 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5560,43 +5594,38 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129316798</v>
+        <v>129308971</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>80185</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5605,13 +5634,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>519455</v>
+        <v>519353</v>
       </c>
       <c r="R41" t="n">
-        <v>7055533</v>
+        <v>7055274</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5640,7 +5669,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5650,12 +5679,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska, på stambasen av en gran.</t>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5674,22 +5703,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5707,50 +5736,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129308971</v>
+        <v>129307918</v>
       </c>
       <c r="B42" t="n">
-        <v>80185</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519353</v>
+        <v>519302</v>
       </c>
       <c r="R42" t="n">
-        <v>7055274</v>
+        <v>7055219</v>
       </c>
       <c r="S42" t="n">
         <v>9</v>
@@ -5782,7 +5806,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5792,12 +5816,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5816,22 +5835,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5849,27 +5868,27 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129310002</v>
+        <v>129309053</v>
       </c>
       <c r="B43" t="n">
-        <v>80184</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5878,24 +5897,19 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519344</v>
+        <v>519383</v>
       </c>
       <c r="R43" t="n">
-        <v>7055261</v>
+        <v>7055292</v>
       </c>
       <c r="S43" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5924,7 +5938,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5934,12 +5948,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På en lutande död sälg.</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5958,22 +5967,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5991,27 +6000,27 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129309053</v>
+        <v>129310002</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>80184</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -6020,19 +6029,24 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519383</v>
+        <v>519344</v>
       </c>
       <c r="R44" t="n">
-        <v>7055292</v>
+        <v>7055261</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6061,7 +6075,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6071,7 +6085,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På en lutande död sälg.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6090,22 +6109,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6123,10 +6142,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129307918</v>
+        <v>129309958</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6134,37 +6153,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519302</v>
+        <v>519366</v>
       </c>
       <c r="R45" t="n">
-        <v>7055219</v>
+        <v>7055274</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6193,7 +6217,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6203,7 +6227,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På en lutande död sälg.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6222,22 +6251,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6255,58 +6284,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129306721</v>
+        <v>129309664</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>97601</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519304</v>
+        <v>519401</v>
       </c>
       <c r="R46" t="n">
-        <v>7055061</v>
+        <v>7055248</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6335,7 +6354,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6345,12 +6364,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, påtagligt och tydligt på stambasen av en gammal gran.</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6365,26 +6379,6 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6402,10 +6396,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129309958</v>
+        <v>129310040</v>
       </c>
       <c r="B47" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6413,39 +6407,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519366</v>
+        <v>519359</v>
       </c>
       <c r="R47" t="n">
-        <v>7055274</v>
+        <v>7055281</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6477,7 +6466,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6487,12 +6476,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På en lutande död sälg.</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6511,22 +6495,22 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6544,10 +6528,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129309664</v>
+        <v>129307091</v>
       </c>
       <c r="B48" t="n">
-        <v>97601</v>
+        <v>98630</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6555,16 +6539,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221941</v>
+        <v>504</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -6572,20 +6556,39 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519401</v>
+        <v>519283</v>
       </c>
       <c r="R48" t="n">
-        <v>7055248</v>
+        <v>7055063</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6614,7 +6617,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6624,7 +6627,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>8 vissna plantor av guckusko i en liten sänka.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6656,10 +6664,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129310040</v>
+        <v>129306721</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6667,37 +6675,47 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519359</v>
+        <v>519304</v>
       </c>
       <c r="R49" t="n">
-        <v>7055281</v>
+        <v>7055061</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6726,7 +6744,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6736,7 +6754,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, påtagligt och tydligt på stambasen av en gammal gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6765,12 +6788,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -4142,38 +4142,43 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129310986</v>
+        <v>129310410</v>
       </c>
       <c r="B30" t="n">
-        <v>92505</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4182,13 +4187,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519482</v>
+        <v>519532</v>
       </c>
       <c r="R30" t="n">
-        <v>7055550</v>
+        <v>7055358</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4217,7 +4222,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4227,7 +4232,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4241,7 +4251,27 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4259,43 +4289,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129310410</v>
+        <v>129310986</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>92505</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4304,13 +4329,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519532</v>
+        <v>519482</v>
       </c>
       <c r="R31" t="n">
-        <v>7055358</v>
+        <v>7055550</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4339,7 +4364,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4349,12 +4374,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4368,27 +4388,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -5736,10 +5736,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129307918</v>
+        <v>129309958</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5747,37 +5747,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519302</v>
+        <v>519366</v>
       </c>
       <c r="R42" t="n">
-        <v>7055219</v>
+        <v>7055274</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5806,7 +5811,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5816,7 +5821,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På en lutande död sälg.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5835,22 +5845,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5868,7 +5878,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129309053</v>
+        <v>129307918</v>
       </c>
       <c r="B43" t="n">
         <v>79044</v>
@@ -5903,10 +5913,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519383</v>
+        <v>519302</v>
       </c>
       <c r="R43" t="n">
-        <v>7055292</v>
+        <v>7055219</v>
       </c>
       <c r="S43" t="n">
         <v>9</v>
@@ -5938,7 +5948,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5948,7 +5958,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6000,27 +6010,27 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129310002</v>
+        <v>129309053</v>
       </c>
       <c r="B44" t="n">
-        <v>80184</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -6029,24 +6039,19 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519344</v>
+        <v>519383</v>
       </c>
       <c r="R44" t="n">
-        <v>7055261</v>
+        <v>7055292</v>
       </c>
       <c r="S44" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6075,7 +6080,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6085,12 +6090,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På en lutande död sälg.</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6109,22 +6109,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6142,32 +6142,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129309958</v>
+        <v>129310002</v>
       </c>
       <c r="B45" t="n">
-        <v>80150</v>
+        <v>80184</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6182,13 +6182,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519366</v>
+        <v>519344</v>
       </c>
       <c r="R45" t="n">
-        <v>7055274</v>
+        <v>7055261</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -2972,7 +2972,7 @@
         <v>129310773</v>
       </c>
       <c r="B21" t="n">
-        <v>92868</v>
+        <v>92871</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>129313853</v>
       </c>
       <c r="B22" t="n">
-        <v>92268</v>
+        <v>92271</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>129313937</v>
       </c>
       <c r="B23" t="n">
-        <v>91546</v>
+        <v>91549</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>129310852</v>
       </c>
       <c r="B26" t="n">
-        <v>92505</v>
+        <v>92508</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3766,48 +3766,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129314194</v>
+        <v>129309748</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>92871</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519427</v>
+        <v>519381</v>
       </c>
       <c r="R27" t="n">
-        <v>7055741</v>
+        <v>7055220</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3836,7 +3841,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3846,7 +3851,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3860,27 +3865,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3898,55 +3883,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129309922</v>
+        <v>129314194</v>
       </c>
       <c r="B28" t="n">
-        <v>98628</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519372</v>
+        <v>519427</v>
       </c>
       <c r="R28" t="n">
-        <v>7055266</v>
+        <v>7055741</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -3978,7 +3953,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3988,12 +3963,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Minst 1 fröställning inom 0,2 m2 yta.</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4007,7 +3977,27 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4025,10 +4015,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129309748</v>
+        <v>129309922</v>
       </c>
       <c r="B29" t="n">
-        <v>92868</v>
+        <v>98631</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4036,27 +4026,32 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5964</v>
+        <v>220093</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4065,13 +4060,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519381</v>
+        <v>519372</v>
       </c>
       <c r="R29" t="n">
-        <v>7055220</v>
+        <v>7055266</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4100,7 +4095,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4110,7 +4105,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Minst 1 fröställning inom 0,2 m2 yta.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4142,43 +4142,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129310410</v>
+        <v>129310986</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>92508</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4187,13 +4182,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519532</v>
+        <v>519482</v>
       </c>
       <c r="R30" t="n">
-        <v>7055358</v>
+        <v>7055550</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4222,7 +4217,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4232,12 +4227,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4251,27 +4241,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4289,38 +4259,43 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129310986</v>
+        <v>129310410</v>
       </c>
       <c r="B31" t="n">
-        <v>92505</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4329,13 +4304,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519482</v>
+        <v>519532</v>
       </c>
       <c r="R31" t="n">
-        <v>7055550</v>
+        <v>7055358</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4364,7 +4339,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4374,7 +4349,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4388,7 +4368,27 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4409,7 +4409,7 @@
         <v>129313884</v>
       </c>
       <c r="B32" t="n">
-        <v>91546</v>
+        <v>91549</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>129307276</v>
       </c>
       <c r="B33" t="n">
-        <v>91323</v>
+        <v>91326</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>129311001</v>
       </c>
       <c r="B35" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5192,34 +5192,30 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129306797</v>
+        <v>129308765</v>
       </c>
       <c r="B38" t="n">
-        <v>92505</v>
+        <v>91573</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4769</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
@@ -5232,13 +5228,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519293</v>
+        <v>519386</v>
       </c>
       <c r="R38" t="n">
-        <v>7055067</v>
+        <v>7055265</v>
       </c>
       <c r="S38" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5267,7 +5263,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5277,7 +5273,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Växer i en stubbe av en gran som knäckts i stambasen.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5292,6 +5293,26 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5309,30 +5330,34 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129308765</v>
+        <v>129306797</v>
       </c>
       <c r="B39" t="n">
-        <v>91570</v>
+        <v>92508</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>4769</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
@@ -5345,13 +5370,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519386</v>
+        <v>519293</v>
       </c>
       <c r="R39" t="n">
-        <v>7055265</v>
+        <v>7055067</v>
       </c>
       <c r="S39" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5380,7 +5405,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5390,12 +5415,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Växer i en stubbe av en gran som knäckts i stambasen.</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5410,26 +5430,6 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5736,32 +5736,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129309958</v>
+        <v>129310002</v>
       </c>
       <c r="B42" t="n">
-        <v>80150</v>
+        <v>80184</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519366</v>
+        <v>519344</v>
       </c>
       <c r="R42" t="n">
-        <v>7055274</v>
+        <v>7055261</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -5878,7 +5878,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129307918</v>
+        <v>129309053</v>
       </c>
       <c r="B43" t="n">
         <v>79044</v>
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519302</v>
+        <v>519383</v>
       </c>
       <c r="R43" t="n">
-        <v>7055219</v>
+        <v>7055292</v>
       </c>
       <c r="S43" t="n">
         <v>9</v>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6010,7 +6010,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129309053</v>
+        <v>129307918</v>
       </c>
       <c r="B44" t="n">
         <v>79044</v>
@@ -6045,10 +6045,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519383</v>
+        <v>519302</v>
       </c>
       <c r="R44" t="n">
-        <v>7055292</v>
+        <v>7055219</v>
       </c>
       <c r="S44" t="n">
         <v>9</v>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6142,32 +6142,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129310002</v>
+        <v>129309958</v>
       </c>
       <c r="B45" t="n">
-        <v>80184</v>
+        <v>80150</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6182,13 +6182,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519344</v>
+        <v>519366</v>
       </c>
       <c r="R45" t="n">
-        <v>7055261</v>
+        <v>7055274</v>
       </c>
       <c r="S45" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -6287,7 +6287,7 @@
         <v>129309664</v>
       </c>
       <c r="B46" t="n">
-        <v>97601</v>
+        <v>97604</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>129307091</v>
       </c>
       <c r="B48" t="n">
-        <v>98630</v>
+        <v>98633</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -4142,38 +4142,43 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129310986</v>
+        <v>129310410</v>
       </c>
       <c r="B30" t="n">
-        <v>92508</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4182,13 +4187,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519482</v>
+        <v>519532</v>
       </c>
       <c r="R30" t="n">
-        <v>7055550</v>
+        <v>7055358</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4217,7 +4222,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4227,7 +4232,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4241,7 +4251,27 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4259,43 +4289,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129310410</v>
+        <v>129310986</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>92508</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4304,13 +4329,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519532</v>
+        <v>519482</v>
       </c>
       <c r="R31" t="n">
-        <v>7055358</v>
+        <v>7055550</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4339,7 +4364,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4349,12 +4374,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4368,27 +4388,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4406,32 +4406,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129313884</v>
+        <v>129307276</v>
       </c>
       <c r="B32" t="n">
-        <v>91549</v>
+        <v>91326</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>3215</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4446,13 +4446,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519404</v>
+        <v>519259</v>
       </c>
       <c r="R32" t="n">
-        <v>7055773</v>
+        <v>7055075</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4505,27 +4505,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Våtmark med barrträd</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4543,32 +4523,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129307276</v>
+        <v>129313884</v>
       </c>
       <c r="B33" t="n">
-        <v>91326</v>
+        <v>91549</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3215</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4583,13 +4563,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519259</v>
+        <v>519404</v>
       </c>
       <c r="R33" t="n">
-        <v>7055075</v>
+        <v>7055773</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4618,7 +4598,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4628,7 +4608,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4642,7 +4622,27 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Våtmark med barrträd</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4925,7 +4925,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129308557</v>
+        <v>129310923</v>
       </c>
       <c r="B36" t="n">
         <v>57887</v>
@@ -4955,12 +4955,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4979,13 +4974,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>519390</v>
+        <v>519476</v>
       </c>
       <c r="R36" t="n">
-        <v>7055229</v>
+        <v>7055536</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5014,7 +5009,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5024,12 +5019,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Synobservation av 4 livliga talltitor som nyfiket dök upp på nära håll.</t>
+          <t>Minst 1 talltita i flerskiktad gammal granskog och gransumpskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5061,7 +5056,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129310923</v>
+        <v>129308557</v>
       </c>
       <c r="B37" t="n">
         <v>57887</v>
@@ -5091,7 +5086,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -5110,13 +5110,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519476</v>
+        <v>519390</v>
       </c>
       <c r="R37" t="n">
-        <v>7055536</v>
+        <v>7055229</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Minst 1 talltita i flerskiktad gammal granskog och gransumpskog.</t>
+          <t>Synobservation av 4 livliga talltitor som nyfiket dök upp på nära håll.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5736,32 +5736,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129310002</v>
+        <v>129309958</v>
       </c>
       <c r="B42" t="n">
-        <v>80184</v>
+        <v>80150</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519344</v>
+        <v>519366</v>
       </c>
       <c r="R42" t="n">
-        <v>7055261</v>
+        <v>7055274</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6142,32 +6142,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129309958</v>
+        <v>129310002</v>
       </c>
       <c r="B45" t="n">
-        <v>80150</v>
+        <v>80184</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6182,13 +6182,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519366</v>
+        <v>519344</v>
       </c>
       <c r="R45" t="n">
-        <v>7055274</v>
+        <v>7055261</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -3766,53 +3766,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129309748</v>
+        <v>129314194</v>
       </c>
       <c r="B27" t="n">
-        <v>92871</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519381</v>
+        <v>519427</v>
       </c>
       <c r="R27" t="n">
-        <v>7055220</v>
+        <v>7055741</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3841,7 +3836,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3851,7 +3846,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3865,7 +3860,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3883,48 +3898,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129314194</v>
+        <v>129309748</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>92871</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519427</v>
+        <v>519381</v>
       </c>
       <c r="R28" t="n">
-        <v>7055741</v>
+        <v>7055220</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3953,7 +3973,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3963,7 +3983,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3977,27 +3997,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4142,43 +4142,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129310410</v>
+        <v>129310986</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>92508</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4187,13 +4182,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519532</v>
+        <v>519482</v>
       </c>
       <c r="R30" t="n">
-        <v>7055358</v>
+        <v>7055550</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4222,7 +4217,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4232,12 +4227,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4251,27 +4241,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4289,38 +4259,43 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129310986</v>
+        <v>129310410</v>
       </c>
       <c r="B31" t="n">
-        <v>92508</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4329,13 +4304,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519482</v>
+        <v>519532</v>
       </c>
       <c r="R31" t="n">
-        <v>7055550</v>
+        <v>7055358</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4364,7 +4339,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4374,7 +4349,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4388,7 +4368,27 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4406,32 +4406,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129307276</v>
+        <v>129313884</v>
       </c>
       <c r="B32" t="n">
-        <v>91326</v>
+        <v>91549</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3215</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4446,13 +4446,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519259</v>
+        <v>519404</v>
       </c>
       <c r="R32" t="n">
-        <v>7055075</v>
+        <v>7055773</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4505,7 +4505,27 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Våtmark med barrträd</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4523,32 +4543,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129313884</v>
+        <v>129307276</v>
       </c>
       <c r="B33" t="n">
-        <v>91549</v>
+        <v>91326</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>3215</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4563,13 +4583,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519404</v>
+        <v>519259</v>
       </c>
       <c r="R33" t="n">
-        <v>7055773</v>
+        <v>7055075</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4598,7 +4618,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4608,7 +4628,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4622,27 +4642,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Våtmark med barrträd</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4925,7 +4925,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129310923</v>
+        <v>129308557</v>
       </c>
       <c r="B36" t="n">
         <v>57887</v>
@@ -4955,7 +4955,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4974,13 +4979,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>519476</v>
+        <v>519390</v>
       </c>
       <c r="R36" t="n">
-        <v>7055536</v>
+        <v>7055229</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5009,7 +5014,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5019,12 +5024,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Minst 1 talltita i flerskiktad gammal granskog och gransumpskog.</t>
+          <t>Synobservation av 4 livliga talltitor som nyfiket dök upp på nära håll.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5056,7 +5061,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129308557</v>
+        <v>129310923</v>
       </c>
       <c r="B37" t="n">
         <v>57887</v>
@@ -5086,12 +5091,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -5110,13 +5110,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519390</v>
+        <v>519476</v>
       </c>
       <c r="R37" t="n">
-        <v>7055229</v>
+        <v>7055536</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Synobservation av 4 livliga talltitor som nyfiket dök upp på nära håll.</t>
+          <t>Minst 1 talltita i flerskiktad gammal granskog och gransumpskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5192,10 +5192,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129308765</v>
+        <v>129316798</v>
       </c>
       <c r="B38" t="n">
-        <v>91573</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5203,23 +5203,32 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5228,13 +5237,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519386</v>
+        <v>519455</v>
       </c>
       <c r="R38" t="n">
-        <v>7055265</v>
+        <v>7055533</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5263,7 +5272,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5273,12 +5282,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Växer i en stubbe av en gran som knäckts i stambasen.</t>
+          <t>Ringhack, äldre, på gränsen till färska, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5307,12 +5316,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5330,34 +5339,30 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129306797</v>
+        <v>129308765</v>
       </c>
       <c r="B39" t="n">
-        <v>92508</v>
+        <v>91573</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4769</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
@@ -5370,13 +5375,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519293</v>
+        <v>519386</v>
       </c>
       <c r="R39" t="n">
-        <v>7055067</v>
+        <v>7055265</v>
       </c>
       <c r="S39" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5405,7 +5410,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5415,7 +5420,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Växer i en stubbe av en gran som knäckts i stambasen.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5430,6 +5440,26 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5447,43 +5477,38 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129316798</v>
+        <v>129306797</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>92508</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5492,13 +5517,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519455</v>
+        <v>519293</v>
       </c>
       <c r="R40" t="n">
-        <v>7055533</v>
+        <v>7055067</v>
       </c>
       <c r="S40" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5527,7 +5552,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5537,12 +5562,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:37</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gränsen till färska, på stambasen av en gran.</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5557,26 +5577,6 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -3360,10 +3360,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129313980</v>
+        <v>129311450</v>
       </c>
       <c r="B24" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3371,16 +3371,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3394,19 +3394,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>519421</v>
+        <v>519497</v>
       </c>
       <c r="R24" t="n">
-        <v>7055771</v>
+        <v>7055786</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3435,7 +3440,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3445,12 +3450,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i en gran.</t>
+          <t>Ringhack, äldre, längs flera meter på en gran vid åkanten.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3502,10 +3507,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129311450</v>
+        <v>129313980</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3513,16 +3518,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3536,24 +3541,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519497</v>
+        <v>519421</v>
       </c>
       <c r="R25" t="n">
-        <v>7055786</v>
+        <v>7055771</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs flera meter på en gran vid åkanten.</t>
+          <t>Rejäla hackspår i en gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3766,45 +3766,55 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129314194</v>
+        <v>129309922</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>98631</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519427</v>
+        <v>519372</v>
       </c>
       <c r="R27" t="n">
-        <v>7055741</v>
+        <v>7055266</v>
       </c>
       <c r="S27" t="n">
         <v>9</v>
@@ -3836,7 +3846,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3846,7 +3856,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Minst 1 fröställning inom 0,2 m2 yta.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3860,27 +3875,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4015,55 +4010,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129309922</v>
+        <v>129314194</v>
       </c>
       <c r="B29" t="n">
-        <v>98631</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519372</v>
+        <v>519427</v>
       </c>
       <c r="R29" t="n">
-        <v>7055266</v>
+        <v>7055741</v>
       </c>
       <c r="S29" t="n">
         <v>9</v>
@@ -4095,7 +4080,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4105,12 +4090,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Minst 1 fröställning inom 0,2 m2 yta.</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4124,7 +4104,27 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -5736,10 +5736,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129309958</v>
+        <v>129309053</v>
       </c>
       <c r="B42" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5747,42 +5747,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519366</v>
+        <v>519383</v>
       </c>
       <c r="R42" t="n">
-        <v>7055274</v>
+        <v>7055292</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5811,7 +5806,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5821,12 +5816,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På en lutande död sälg.</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5845,22 +5835,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5878,7 +5868,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129309053</v>
+        <v>129307918</v>
       </c>
       <c r="B43" t="n">
         <v>79044</v>
@@ -5913,10 +5903,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519383</v>
+        <v>519302</v>
       </c>
       <c r="R43" t="n">
-        <v>7055292</v>
+        <v>7055219</v>
       </c>
       <c r="S43" t="n">
         <v>9</v>
@@ -5948,7 +5938,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5958,7 +5948,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6010,10 +6000,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129307918</v>
+        <v>129309958</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6021,37 +6011,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519302</v>
+        <v>519366</v>
       </c>
       <c r="R44" t="n">
-        <v>7055219</v>
+        <v>7055274</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6080,7 +6075,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6090,7 +6085,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På en lutande död sälg.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6109,22 +6109,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -3360,10 +3360,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129311450</v>
+        <v>129313980</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3371,16 +3371,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3394,24 +3394,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>519497</v>
+        <v>519421</v>
       </c>
       <c r="R24" t="n">
-        <v>7055786</v>
+        <v>7055771</v>
       </c>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3440,7 +3435,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3450,12 +3445,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs flera meter på en gran vid åkanten.</t>
+          <t>Rejäla hackspår i en gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3507,10 +3502,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129313980</v>
+        <v>129311450</v>
       </c>
       <c r="B25" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3518,16 +3513,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3541,19 +3536,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519421</v>
+        <v>519497</v>
       </c>
       <c r="R25" t="n">
-        <v>7055771</v>
+        <v>7055786</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i en gran.</t>
+          <t>Ringhack, äldre, längs flera meter på en gran vid åkanten.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4142,38 +4142,43 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129310986</v>
+        <v>129310410</v>
       </c>
       <c r="B30" t="n">
-        <v>92508</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4182,13 +4187,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519482</v>
+        <v>519532</v>
       </c>
       <c r="R30" t="n">
-        <v>7055550</v>
+        <v>7055358</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4217,7 +4222,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4227,7 +4232,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4241,7 +4251,27 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4259,43 +4289,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129310410</v>
+        <v>129310986</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>92508</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4304,13 +4329,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519532</v>
+        <v>519482</v>
       </c>
       <c r="R31" t="n">
-        <v>7055358</v>
+        <v>7055550</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4339,7 +4364,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4349,12 +4374,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4368,27 +4388,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4406,32 +4406,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129313884</v>
+        <v>129307276</v>
       </c>
       <c r="B32" t="n">
-        <v>91549</v>
+        <v>91326</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>3215</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4446,13 +4446,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519404</v>
+        <v>519259</v>
       </c>
       <c r="R32" t="n">
-        <v>7055773</v>
+        <v>7055075</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4505,27 +4505,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Våtmark med barrträd</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4543,32 +4523,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129307276</v>
+        <v>129313884</v>
       </c>
       <c r="B33" t="n">
-        <v>91326</v>
+        <v>91549</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3215</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4583,13 +4563,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519259</v>
+        <v>519404</v>
       </c>
       <c r="R33" t="n">
-        <v>7055075</v>
+        <v>7055773</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4618,7 +4598,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4628,7 +4608,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4642,7 +4622,27 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Våtmark med barrträd</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5736,10 +5736,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129309053</v>
+        <v>129309958</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5747,37 +5747,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519383</v>
+        <v>519366</v>
       </c>
       <c r="R42" t="n">
-        <v>7055292</v>
+        <v>7055274</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5806,7 +5811,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5816,7 +5821,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På en lutande död sälg.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5835,22 +5845,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6000,32 +6010,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129309958</v>
+        <v>129310002</v>
       </c>
       <c r="B44" t="n">
-        <v>80150</v>
+        <v>80184</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6040,13 +6050,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519366</v>
+        <v>519344</v>
       </c>
       <c r="R44" t="n">
-        <v>7055274</v>
+        <v>7055261</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6075,7 +6085,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6085,7 +6095,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -6142,27 +6152,27 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129310002</v>
+        <v>129309053</v>
       </c>
       <c r="B45" t="n">
-        <v>80184</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -6171,24 +6181,19 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519344</v>
+        <v>519383</v>
       </c>
       <c r="R45" t="n">
-        <v>7055261</v>
+        <v>7055292</v>
       </c>
       <c r="S45" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6217,7 +6222,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6227,12 +6232,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På en lutande död sälg.</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6251,22 +6251,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -3766,10 +3766,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129309922</v>
+        <v>129309748</v>
       </c>
       <c r="B27" t="n">
-        <v>98631</v>
+        <v>92871</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3777,32 +3777,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220093</v>
+        <v>5964</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3811,13 +3806,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519372</v>
+        <v>519381</v>
       </c>
       <c r="R27" t="n">
-        <v>7055266</v>
+        <v>7055220</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3846,7 +3841,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3856,12 +3851,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Minst 1 fröställning inom 0,2 m2 yta.</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3893,53 +3883,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129309748</v>
+        <v>129314194</v>
       </c>
       <c r="B28" t="n">
-        <v>92871</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519381</v>
+        <v>519427</v>
       </c>
       <c r="R28" t="n">
-        <v>7055220</v>
+        <v>7055741</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3968,7 +3953,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3978,7 +3963,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3992,7 +3977,27 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4010,45 +4015,55 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129314194</v>
+        <v>129309922</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>98631</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519427</v>
+        <v>519372</v>
       </c>
       <c r="R29" t="n">
-        <v>7055741</v>
+        <v>7055266</v>
       </c>
       <c r="S29" t="n">
         <v>9</v>
@@ -4080,7 +4095,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4090,7 +4105,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Minst 1 fröställning inom 0,2 m2 yta.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4104,27 +4124,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4142,43 +4142,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129310410</v>
+        <v>129310986</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>92508</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4187,13 +4182,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519532</v>
+        <v>519482</v>
       </c>
       <c r="R30" t="n">
-        <v>7055358</v>
+        <v>7055550</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4222,7 +4217,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4232,12 +4227,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4251,27 +4241,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4289,38 +4259,43 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129310986</v>
+        <v>129310410</v>
       </c>
       <c r="B31" t="n">
-        <v>92508</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4329,13 +4304,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519482</v>
+        <v>519532</v>
       </c>
       <c r="R31" t="n">
-        <v>7055550</v>
+        <v>7055358</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4364,7 +4339,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4374,7 +4349,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4388,7 +4368,27 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -5878,27 +5878,27 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129307918</v>
+        <v>129310002</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>80184</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5907,19 +5907,24 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519302</v>
+        <v>519344</v>
       </c>
       <c r="R43" t="n">
-        <v>7055219</v>
+        <v>7055261</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5948,7 +5953,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5958,7 +5963,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På en lutande död sälg.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5977,22 +5987,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6010,27 +6020,27 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129310002</v>
+        <v>129309053</v>
       </c>
       <c r="B44" t="n">
-        <v>80184</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -6039,24 +6049,19 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519344</v>
+        <v>519383</v>
       </c>
       <c r="R44" t="n">
-        <v>7055261</v>
+        <v>7055292</v>
       </c>
       <c r="S44" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6085,7 +6090,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6095,12 +6100,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På en lutande död sälg.</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6119,22 +6119,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6152,7 +6152,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129309053</v>
+        <v>129307918</v>
       </c>
       <c r="B45" t="n">
         <v>79044</v>
@@ -6187,10 +6187,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519383</v>
+        <v>519302</v>
       </c>
       <c r="R45" t="n">
-        <v>7055292</v>
+        <v>7055219</v>
       </c>
       <c r="S45" t="n">
         <v>9</v>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6232,7 +6232,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -2243,7 +2243,7 @@
         <v>122513932</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>129310773</v>
       </c>
       <c r="B21" t="n">
-        <v>92871</v>
+        <v>92899</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>129313853</v>
       </c>
       <c r="B22" t="n">
-        <v>92271</v>
+        <v>92299</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>129313937</v>
       </c>
       <c r="B23" t="n">
-        <v>91549</v>
+        <v>91577</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>129313980</v>
       </c>
       <c r="B24" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>129311450</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>129310852</v>
       </c>
       <c r="B26" t="n">
-        <v>92508</v>
+        <v>92536</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>129309748</v>
       </c>
       <c r="B27" t="n">
-        <v>92871</v>
+        <v>92899</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>129314194</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>129309922</v>
       </c>
       <c r="B29" t="n">
-        <v>98631</v>
+        <v>98660</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>129310986</v>
       </c>
       <c r="B30" t="n">
-        <v>92508</v>
+        <v>92536</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         <v>129310410</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4406,32 +4406,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129307276</v>
+        <v>129313884</v>
       </c>
       <c r="B32" t="n">
-        <v>91326</v>
+        <v>91577</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3215</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4446,13 +4446,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519259</v>
+        <v>519404</v>
       </c>
       <c r="R32" t="n">
-        <v>7055075</v>
+        <v>7055773</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4505,7 +4505,27 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Våtmark med barrträd</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4523,32 +4543,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129313884</v>
+        <v>129307276</v>
       </c>
       <c r="B33" t="n">
-        <v>91549</v>
+        <v>91354</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>3215</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4563,13 +4583,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519404</v>
+        <v>519259</v>
       </c>
       <c r="R33" t="n">
-        <v>7055773</v>
+        <v>7055075</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4598,7 +4618,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4608,7 +4628,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4622,27 +4642,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Våtmark med barrträd</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4663,7 +4663,7 @@
         <v>129313586</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>129311001</v>
       </c>
       <c r="B35" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>129308557</v>
       </c>
       <c r="B36" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>129310923</v>
       </c>
       <c r="B37" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5192,10 +5192,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129316798</v>
+        <v>129308765</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>91601</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5203,32 +5203,23 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5237,13 +5228,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519455</v>
+        <v>519386</v>
       </c>
       <c r="R38" t="n">
-        <v>7055533</v>
+        <v>7055265</v>
       </c>
       <c r="S38" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5272,7 +5263,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5282,12 +5273,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska, på stambasen av en gran.</t>
+          <t>Växer i en stubbe av en gran som knäckts i stambasen.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5316,12 +5307,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5339,10 +5330,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129308765</v>
+        <v>129316798</v>
       </c>
       <c r="B39" t="n">
-        <v>91573</v>
+        <v>57730</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5350,23 +5341,32 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5375,13 +5375,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519386</v>
+        <v>519455</v>
       </c>
       <c r="R39" t="n">
-        <v>7055265</v>
+        <v>7055533</v>
       </c>
       <c r="S39" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5420,12 +5420,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Växer i en stubbe av en gran som knäckts i stambasen.</t>
+          <t>Ringhack, äldre, på gränsen till färska, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5454,12 +5454,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5480,7 +5480,7 @@
         <v>129306797</v>
       </c>
       <c r="B40" t="n">
-        <v>92508</v>
+        <v>92536</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         <v>129308971</v>
       </c>
       <c r="B41" t="n">
-        <v>80185</v>
+        <v>80211</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>129309958</v>
       </c>
       <c r="B42" t="n">
-        <v>80150</v>
+        <v>80176</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5878,27 +5878,27 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129310002</v>
+        <v>129309053</v>
       </c>
       <c r="B43" t="n">
-        <v>80184</v>
+        <v>79070</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5907,24 +5907,19 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519344</v>
+        <v>519383</v>
       </c>
       <c r="R43" t="n">
-        <v>7055261</v>
+        <v>7055292</v>
       </c>
       <c r="S43" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5953,7 +5948,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5963,12 +5958,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På en lutande död sälg.</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5987,22 +5977,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6020,10 +6010,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129309053</v>
+        <v>129307918</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6055,10 +6045,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519383</v>
+        <v>519302</v>
       </c>
       <c r="R44" t="n">
-        <v>7055292</v>
+        <v>7055219</v>
       </c>
       <c r="S44" t="n">
         <v>9</v>
@@ -6090,7 +6080,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6100,7 +6090,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6152,27 +6142,27 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129307918</v>
+        <v>129310002</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>80210</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -6181,19 +6171,24 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519302</v>
+        <v>519344</v>
       </c>
       <c r="R45" t="n">
-        <v>7055219</v>
+        <v>7055261</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6222,7 +6217,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6232,7 +6227,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På en lutande död sälg.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6251,22 +6251,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6287,7 +6287,7 @@
         <v>129309664</v>
       </c>
       <c r="B46" t="n">
-        <v>97604</v>
+        <v>97633</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>129310040</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>129307091</v>
       </c>
       <c r="B48" t="n">
-        <v>98633</v>
+        <v>98662</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>129306721</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>129316769</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         <v>129313241</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -5878,27 +5878,27 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129309053</v>
+        <v>129310002</v>
       </c>
       <c r="B43" t="n">
-        <v>79070</v>
+        <v>80210</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5907,19 +5907,24 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519383</v>
+        <v>519344</v>
       </c>
       <c r="R43" t="n">
-        <v>7055292</v>
+        <v>7055261</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5948,7 +5953,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5958,7 +5963,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På en lutande död sälg.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5977,22 +5987,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6010,7 +6020,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129307918</v>
+        <v>129309053</v>
       </c>
       <c r="B44" t="n">
         <v>79070</v>
@@ -6045,10 +6055,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519302</v>
+        <v>519383</v>
       </c>
       <c r="R44" t="n">
-        <v>7055219</v>
+        <v>7055292</v>
       </c>
       <c r="S44" t="n">
         <v>9</v>
@@ -6080,7 +6090,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6090,7 +6100,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6142,27 +6152,27 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129310002</v>
+        <v>129307918</v>
       </c>
       <c r="B45" t="n">
-        <v>80210</v>
+        <v>79070</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -6171,24 +6181,19 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519344</v>
+        <v>519302</v>
       </c>
       <c r="R45" t="n">
-        <v>7055261</v>
+        <v>7055219</v>
       </c>
       <c r="S45" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6217,7 +6222,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6227,12 +6232,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På en lutande död sälg.</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6251,22 +6251,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -2243,7 +2243,7 @@
         <v>122513932</v>
       </c>
       <c r="B15" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>129310773</v>
       </c>
       <c r="B21" t="n">
-        <v>92899</v>
+        <v>92905</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>129313853</v>
       </c>
       <c r="B22" t="n">
-        <v>92299</v>
+        <v>92305</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>129313937</v>
       </c>
       <c r="B23" t="n">
-        <v>91577</v>
+        <v>91583</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>129313980</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3502,43 +3502,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129311450</v>
+        <v>129310852</v>
       </c>
       <c r="B25" t="n">
-        <v>57730</v>
+        <v>92542</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3547,13 +3542,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519497</v>
+        <v>519479</v>
       </c>
       <c r="R25" t="n">
-        <v>7055786</v>
+        <v>7055528</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3582,7 +3577,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3592,12 +3587,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, längs flera meter på en gran vid åkanten.</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3611,27 +3601,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3649,10 +3619,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129310852</v>
+        <v>129309748</v>
       </c>
       <c r="B26" t="n">
-        <v>92536</v>
+        <v>92905</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3660,21 +3630,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3689,13 +3659,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519479</v>
+        <v>519381</v>
       </c>
       <c r="R26" t="n">
-        <v>7055528</v>
+        <v>7055220</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3724,7 +3694,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3734,7 +3704,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3748,7 +3718,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3766,53 +3736,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129309748</v>
+        <v>129314194</v>
       </c>
       <c r="B27" t="n">
-        <v>92899</v>
+        <v>79075</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519381</v>
+        <v>519427</v>
       </c>
       <c r="R27" t="n">
-        <v>7055220</v>
+        <v>7055741</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3841,7 +3806,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3851,7 +3816,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3865,7 +3830,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3883,45 +3868,55 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129314194</v>
+        <v>129309922</v>
       </c>
       <c r="B28" t="n">
-        <v>79070</v>
+        <v>98672</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519427</v>
+        <v>519372</v>
       </c>
       <c r="R28" t="n">
-        <v>7055741</v>
+        <v>7055266</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -3953,7 +3948,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3963,7 +3958,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Minst 1 fröställning inom 0,2 m2 yta.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3977,27 +3977,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4015,10 +3995,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129309922</v>
+        <v>129310986</v>
       </c>
       <c r="B29" t="n">
-        <v>98660</v>
+        <v>92542</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4026,32 +4006,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220093</v>
+        <v>4769</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4060,13 +4035,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519372</v>
+        <v>519482</v>
       </c>
       <c r="R29" t="n">
-        <v>7055266</v>
+        <v>7055550</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4095,7 +4070,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4105,12 +4080,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Minst 1 fröställning inom 0,2 m2 yta.</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4124,7 +4094,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4142,32 +4112,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129310986</v>
+        <v>129313884</v>
       </c>
       <c r="B30" t="n">
-        <v>92536</v>
+        <v>91583</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4769</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4182,13 +4152,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519482</v>
+        <v>519404</v>
       </c>
       <c r="R30" t="n">
-        <v>7055550</v>
+        <v>7055773</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4217,7 +4187,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4227,7 +4197,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4242,6 +4212,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4259,43 +4249,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129310410</v>
+        <v>129307276</v>
       </c>
       <c r="B31" t="n">
-        <v>57730</v>
+        <v>91360</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>3215</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4304,10 +4289,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519532</v>
+        <v>519259</v>
       </c>
       <c r="R31" t="n">
-        <v>7055358</v>
+        <v>7055075</v>
       </c>
       <c r="S31" t="n">
         <v>8</v>
@@ -4339,7 +4324,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4349,12 +4334,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4368,27 +4348,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Våtmark med barrträd</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4406,10 +4366,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129313884</v>
+        <v>129313586</v>
       </c>
       <c r="B32" t="n">
-        <v>91577</v>
+        <v>79075</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4417,42 +4377,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519404</v>
+        <v>519436</v>
       </c>
       <c r="R32" t="n">
-        <v>7055773</v>
+        <v>7055806</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4481,7 +4436,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4491,7 +4446,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4520,12 +4475,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4543,34 +4498,30 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129307276</v>
+        <v>129311001</v>
       </c>
       <c r="B33" t="n">
-        <v>91354</v>
+        <v>91607</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3215</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
@@ -4583,13 +4534,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519259</v>
+        <v>519493</v>
       </c>
       <c r="R33" t="n">
-        <v>7055075</v>
+        <v>7055555</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4618,7 +4569,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4628,7 +4579,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4642,7 +4593,27 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Våtmark med barrträd</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4660,10 +4631,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129313586</v>
+        <v>129308557</v>
       </c>
       <c r="B34" t="n">
-        <v>79070</v>
+        <v>57895</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4671,37 +4642,56 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>519436</v>
+        <v>519390</v>
       </c>
       <c r="R34" t="n">
-        <v>7055806</v>
+        <v>7055229</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4730,7 +4720,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4740,7 +4730,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Synobservation av 4 livliga talltitor som nyfiket dök upp på nära håll.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4755,26 +4750,6 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4792,10 +4767,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129311001</v>
+        <v>129310923</v>
       </c>
       <c r="B35" t="n">
-        <v>91601</v>
+        <v>57895</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4803,23 +4778,36 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4828,10 +4816,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>519493</v>
+        <v>519476</v>
       </c>
       <c r="R35" t="n">
-        <v>7055555</v>
+        <v>7055536</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4863,7 +4851,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4873,7 +4861,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Minst 1 talltita i flerskiktad gammal granskog och gransumpskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4888,26 +4881,6 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4925,10 +4898,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129308557</v>
+        <v>129308765</v>
       </c>
       <c r="B36" t="n">
-        <v>57890</v>
+        <v>91607</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4936,41 +4909,23 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4979,13 +4934,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>519390</v>
+        <v>519386</v>
       </c>
       <c r="R36" t="n">
-        <v>7055229</v>
+        <v>7055265</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5014,7 +4969,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5024,12 +4979,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Synobservation av 4 livliga talltitor som nyfiket dök upp på nära håll.</t>
+          <t>Växer i en stubbe av en gran som knäckts i stambasen.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5043,7 +4998,27 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5061,47 +5036,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129310923</v>
+        <v>129306797</v>
       </c>
       <c r="B37" t="n">
-        <v>57890</v>
+        <v>92542</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>4769</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -5110,13 +5076,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519476</v>
+        <v>519293</v>
       </c>
       <c r="R37" t="n">
-        <v>7055536</v>
+        <v>7055067</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5145,7 +5111,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5155,12 +5121,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Minst 1 talltita i flerskiktad gammal granskog och gransumpskog.</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5174,7 +5135,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5192,34 +5153,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129308765</v>
+        <v>129308971</v>
       </c>
       <c r="B38" t="n">
-        <v>91601</v>
+        <v>80216</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5228,13 +5193,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519386</v>
+        <v>519353</v>
       </c>
       <c r="R38" t="n">
-        <v>7055265</v>
+        <v>7055274</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5263,7 +5228,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5273,12 +5238,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Växer i en stubbe av en gran som knäckts i stambasen.</t>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5297,22 +5262,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5330,10 +5295,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129316798</v>
+        <v>129309958</v>
       </c>
       <c r="B39" t="n">
-        <v>57730</v>
+        <v>80181</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5341,32 +5306,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5375,13 +5335,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519455</v>
+        <v>519366</v>
       </c>
       <c r="R39" t="n">
-        <v>7055533</v>
+        <v>7055274</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5410,7 +5370,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5420,12 +5380,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska, på stambasen av en gran.</t>
+          <t>På en lutande död sälg.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5444,22 +5404,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5477,53 +5437,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129306797</v>
+        <v>129309053</v>
       </c>
       <c r="B40" t="n">
-        <v>92536</v>
+        <v>79075</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519293</v>
+        <v>519383</v>
       </c>
       <c r="R40" t="n">
-        <v>7055067</v>
+        <v>7055292</v>
       </c>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5552,7 +5507,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5562,7 +5517,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5577,6 +5532,26 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5594,50 +5569,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129308971</v>
+        <v>129307918</v>
       </c>
       <c r="B41" t="n">
-        <v>80211</v>
+        <v>79075</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>519353</v>
+        <v>519302</v>
       </c>
       <c r="R41" t="n">
-        <v>7055274</v>
+        <v>7055219</v>
       </c>
       <c r="S41" t="n">
         <v>9</v>
@@ -5669,7 +5639,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5679,12 +5649,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5703,22 +5668,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5736,32 +5701,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129309958</v>
+        <v>129310002</v>
       </c>
       <c r="B42" t="n">
-        <v>80176</v>
+        <v>80215</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5776,13 +5741,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519366</v>
+        <v>519344</v>
       </c>
       <c r="R42" t="n">
-        <v>7055274</v>
+        <v>7055261</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5811,7 +5776,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5821,7 +5786,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -5878,10 +5843,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129310002</v>
+        <v>129309664</v>
       </c>
       <c r="B43" t="n">
-        <v>80210</v>
+        <v>97645</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5889,42 +5854,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>221941</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519344</v>
+        <v>519401</v>
       </c>
       <c r="R43" t="n">
-        <v>7055261</v>
+        <v>7055248</v>
       </c>
       <c r="S43" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5953,7 +5913,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5963,12 +5923,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På en lutande död sälg.</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5983,26 +5938,6 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6020,10 +5955,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129309053</v>
+        <v>129310040</v>
       </c>
       <c r="B44" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6055,13 +5990,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519383</v>
+        <v>519359</v>
       </c>
       <c r="R44" t="n">
-        <v>7055292</v>
+        <v>7055281</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6090,7 +6025,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6100,7 +6035,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6152,48 +6087,67 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129307918</v>
+        <v>129307091</v>
       </c>
       <c r="B45" t="n">
-        <v>79070</v>
+        <v>98674</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>504</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519302</v>
+        <v>519283</v>
       </c>
       <c r="R45" t="n">
-        <v>7055219</v>
+        <v>7055063</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6222,7 +6176,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6232,7 +6186,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>8 vissna plantor av guckusko i en liten sänka.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6247,26 +6206,6 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6284,48 +6223,58 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129309664</v>
+        <v>129311450</v>
       </c>
       <c r="B46" t="n">
-        <v>97633</v>
+        <v>57735</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519401</v>
+        <v>519497</v>
       </c>
       <c r="R46" t="n">
-        <v>7055248</v>
+        <v>7055786</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6354,7 +6303,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6364,7 +6313,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, längs flera meter på en gran vid åkanten.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6378,7 +6332,27 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6396,10 +6370,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129310040</v>
+        <v>129310410</v>
       </c>
       <c r="B47" t="n">
-        <v>79070</v>
+        <v>57735</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6407,37 +6381,47 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519359</v>
+        <v>519532</v>
       </c>
       <c r="R47" t="n">
-        <v>7055281</v>
+        <v>7055358</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6466,7 +6450,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6476,7 +6460,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6505,12 +6494,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6528,47 +6517,38 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129307091</v>
+        <v>129316798</v>
       </c>
       <c r="B48" t="n">
-        <v>98662</v>
+        <v>57735</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>504</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -6582,13 +6562,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519283</v>
+        <v>519455</v>
       </c>
       <c r="R48" t="n">
-        <v>7055063</v>
+        <v>7055533</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6617,7 +6597,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6627,12 +6607,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>8 vissna plantor av guckusko i en liten sänka.</t>
+          <t>Ringhack, äldre, på gränsen till färska, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6647,6 +6627,26 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6667,7 +6667,7 @@
         <v>129306721</v>
       </c>
       <c r="B49" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>129316769</v>
       </c>
       <c r="B50" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         <v>129313241</v>
       </c>
       <c r="B51" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -2243,7 +2243,7 @@
         <v>122513932</v>
       </c>
       <c r="B15" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>129310773</v>
       </c>
       <c r="B21" t="n">
-        <v>92905</v>
+        <v>92906</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>129313853</v>
       </c>
       <c r="B22" t="n">
-        <v>92305</v>
+        <v>92306</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>129313937</v>
       </c>
       <c r="B23" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>129313980</v>
       </c>
       <c r="B24" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>129310852</v>
       </c>
       <c r="B25" t="n">
-        <v>92542</v>
+        <v>92543</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3619,10 +3619,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129309748</v>
+        <v>129309922</v>
       </c>
       <c r="B26" t="n">
-        <v>92905</v>
+        <v>98673</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3630,27 +3630,32 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5964</v>
+        <v>220093</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3659,13 +3664,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519381</v>
+        <v>519372</v>
       </c>
       <c r="R26" t="n">
-        <v>7055220</v>
+        <v>7055266</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3694,7 +3699,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3704,7 +3709,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Minst 1 fröställning inom 0,2 m2 yta.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3736,48 +3746,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129314194</v>
+        <v>129309748</v>
       </c>
       <c r="B27" t="n">
-        <v>79075</v>
+        <v>92906</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519427</v>
+        <v>519381</v>
       </c>
       <c r="R27" t="n">
-        <v>7055741</v>
+        <v>7055220</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3806,7 +3821,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3816,7 +3831,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3830,27 +3845,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3868,55 +3863,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129309922</v>
+        <v>129314194</v>
       </c>
       <c r="B28" t="n">
-        <v>98672</v>
+        <v>79076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519372</v>
+        <v>519427</v>
       </c>
       <c r="R28" t="n">
-        <v>7055266</v>
+        <v>7055741</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -3948,7 +3933,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3958,12 +3943,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Minst 1 fröställning inom 0,2 m2 yta.</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3977,7 +3957,27 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3998,7 +3998,7 @@
         <v>129310986</v>
       </c>
       <c r="B29" t="n">
-        <v>92542</v>
+        <v>92543</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>129313884</v>
       </c>
       <c r="B30" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>129307276</v>
       </c>
       <c r="B31" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>129313586</v>
       </c>
       <c r="B32" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>129311001</v>
       </c>
       <c r="B33" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4634,7 +4634,7 @@
         <v>129308557</v>
       </c>
       <c r="B34" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>129310923</v>
       </c>
       <c r="B35" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
         <v>129308765</v>
       </c>
       <c r="B36" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>129306797</v>
       </c>
       <c r="B37" t="n">
-        <v>92542</v>
+        <v>92543</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>129308971</v>
       </c>
       <c r="B38" t="n">
-        <v>80216</v>
+        <v>80217</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>129309958</v>
       </c>
       <c r="B39" t="n">
-        <v>80181</v>
+        <v>80182</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5437,27 +5437,27 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129309053</v>
+        <v>129310002</v>
       </c>
       <c r="B40" t="n">
-        <v>79075</v>
+        <v>80216</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5466,19 +5466,24 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519383</v>
+        <v>519344</v>
       </c>
       <c r="R40" t="n">
-        <v>7055292</v>
+        <v>7055261</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5507,7 +5512,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5517,7 +5522,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På en lutande död sälg.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5536,22 +5546,22 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5569,10 +5579,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129307918</v>
+        <v>129309053</v>
       </c>
       <c r="B41" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5604,10 +5614,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>519302</v>
+        <v>519383</v>
       </c>
       <c r="R41" t="n">
-        <v>7055219</v>
+        <v>7055292</v>
       </c>
       <c r="S41" t="n">
         <v>9</v>
@@ -5639,7 +5649,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5649,7 +5659,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5701,27 +5711,27 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129310002</v>
+        <v>129307918</v>
       </c>
       <c r="B42" t="n">
-        <v>80215</v>
+        <v>79076</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5730,24 +5740,19 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519344</v>
+        <v>519302</v>
       </c>
       <c r="R42" t="n">
-        <v>7055261</v>
+        <v>7055219</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5776,7 +5781,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5786,12 +5791,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På en lutande död sälg.</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5810,22 +5810,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5846,7 +5846,7 @@
         <v>129309664</v>
       </c>
       <c r="B43" t="n">
-        <v>97645</v>
+        <v>97646</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>129310040</v>
       </c>
       <c r="B44" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>129307091</v>
       </c>
       <c r="B45" t="n">
-        <v>98674</v>
+        <v>98675</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>129311450</v>
       </c>
       <c r="B46" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>129310410</v>
       </c>
       <c r="B47" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>129316798</v>
       </c>
       <c r="B48" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>129306721</v>
       </c>
       <c r="B49" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6811,10 +6811,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129316769</v>
+        <v>129313241</v>
       </c>
       <c r="B50" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6856,13 +6856,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>519455</v>
+        <v>519454</v>
       </c>
       <c r="R50" t="n">
-        <v>7055526</v>
+        <v>7055805</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6901,12 +6901,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska, på en gran.</t>
+          <t>Ringhack, äldre, på gränsen till färska, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -6958,10 +6958,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129313241</v>
+        <v>129316769</v>
       </c>
       <c r="B51" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7003,13 +7003,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519454</v>
+        <v>519455</v>
       </c>
       <c r="R51" t="n">
-        <v>7055805</v>
+        <v>7055526</v>
       </c>
       <c r="S51" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska, längs flera meter på en gran.</t>
+          <t>Ringhack, äldre, på gränsen till färska, på en gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -5295,10 +5295,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129309958</v>
+        <v>129309053</v>
       </c>
       <c r="B39" t="n">
-        <v>80182</v>
+        <v>79076</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5306,42 +5306,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519366</v>
+        <v>519383</v>
       </c>
       <c r="R39" t="n">
-        <v>7055274</v>
+        <v>7055292</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5370,7 +5365,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5380,12 +5375,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På en lutande död sälg.</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5404,22 +5394,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5437,27 +5427,27 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129310002</v>
+        <v>129307918</v>
       </c>
       <c r="B40" t="n">
-        <v>80216</v>
+        <v>79076</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5466,24 +5456,19 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519344</v>
+        <v>519302</v>
       </c>
       <c r="R40" t="n">
-        <v>7055261</v>
+        <v>7055219</v>
       </c>
       <c r="S40" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5512,7 +5497,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5522,12 +5507,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På en lutande död sälg.</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5546,22 +5526,22 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5579,10 +5559,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129309053</v>
+        <v>129309958</v>
       </c>
       <c r="B41" t="n">
-        <v>79076</v>
+        <v>80182</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5590,37 +5570,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>519383</v>
+        <v>519366</v>
       </c>
       <c r="R41" t="n">
-        <v>7055292</v>
+        <v>7055274</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5649,7 +5634,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5659,7 +5644,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På en lutande död sälg.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5678,22 +5668,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5711,27 +5701,27 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129307918</v>
+        <v>129310002</v>
       </c>
       <c r="B42" t="n">
-        <v>79076</v>
+        <v>80216</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5740,19 +5730,24 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519302</v>
+        <v>519344</v>
       </c>
       <c r="R42" t="n">
-        <v>7055219</v>
+        <v>7055261</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5781,7 +5776,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5791,7 +5786,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På en lutande död sälg.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5810,22 +5810,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -2972,7 +2972,7 @@
         <v>129310773</v>
       </c>
       <c r="B21" t="n">
-        <v>92906</v>
+        <v>92911</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>129313853</v>
       </c>
       <c r="B22" t="n">
-        <v>92306</v>
+        <v>92311</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>129313937</v>
       </c>
       <c r="B23" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>129310852</v>
       </c>
       <c r="B25" t="n">
-        <v>92543</v>
+        <v>92548</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3619,10 +3619,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129309922</v>
+        <v>129309748</v>
       </c>
       <c r="B26" t="n">
-        <v>98673</v>
+        <v>92911</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3630,32 +3630,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220093</v>
+        <v>5964</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3664,13 +3659,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519372</v>
+        <v>519381</v>
       </c>
       <c r="R26" t="n">
-        <v>7055266</v>
+        <v>7055220</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3699,7 +3694,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3709,12 +3704,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Minst 1 fröställning inom 0,2 m2 yta.</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3746,53 +3736,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129309748</v>
+        <v>129314194</v>
       </c>
       <c r="B27" t="n">
-        <v>92906</v>
+        <v>79081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519381</v>
+        <v>519427</v>
       </c>
       <c r="R27" t="n">
-        <v>7055220</v>
+        <v>7055741</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3821,7 +3806,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3831,7 +3816,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3845,7 +3830,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3863,45 +3868,55 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129314194</v>
+        <v>129309922</v>
       </c>
       <c r="B28" t="n">
-        <v>79076</v>
+        <v>98678</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519427</v>
+        <v>519372</v>
       </c>
       <c r="R28" t="n">
-        <v>7055741</v>
+        <v>7055266</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -3933,7 +3948,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3943,7 +3958,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Minst 1 fröställning inom 0,2 m2 yta.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3957,27 +3977,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3998,7 +3998,7 @@
         <v>129310986</v>
       </c>
       <c r="B29" t="n">
-        <v>92543</v>
+        <v>92548</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4112,32 +4112,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129313884</v>
+        <v>129307276</v>
       </c>
       <c r="B30" t="n">
-        <v>91584</v>
+        <v>91366</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>3215</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519404</v>
+        <v>519259</v>
       </c>
       <c r="R30" t="n">
-        <v>7055773</v>
+        <v>7055075</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4211,27 +4211,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Våtmark med barrträd</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4249,32 +4229,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129307276</v>
+        <v>129313884</v>
       </c>
       <c r="B31" t="n">
-        <v>91361</v>
+        <v>91589</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3215</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4289,13 +4269,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519259</v>
+        <v>519404</v>
       </c>
       <c r="R31" t="n">
-        <v>7055075</v>
+        <v>7055773</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4324,7 +4304,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4334,7 +4314,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4348,7 +4328,27 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Våtmark med barrträd</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4369,7 +4369,7 @@
         <v>129313586</v>
       </c>
       <c r="B32" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>129311001</v>
       </c>
       <c r="B33" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
         <v>129308765</v>
       </c>
       <c r="B36" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>129306797</v>
       </c>
       <c r="B37" t="n">
-        <v>92543</v>
+        <v>92548</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>129308971</v>
       </c>
       <c r="B38" t="n">
-        <v>80217</v>
+        <v>80222</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5295,27 +5295,27 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129309053</v>
+        <v>129310002</v>
       </c>
       <c r="B39" t="n">
-        <v>79076</v>
+        <v>80221</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5324,19 +5324,24 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519383</v>
+        <v>519344</v>
       </c>
       <c r="R39" t="n">
-        <v>7055292</v>
+        <v>7055261</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5365,7 +5370,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5375,7 +5380,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På en lutande död sälg.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5394,22 +5404,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5427,10 +5437,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129307918</v>
+        <v>129309053</v>
       </c>
       <c r="B40" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5462,10 +5472,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519302</v>
+        <v>519383</v>
       </c>
       <c r="R40" t="n">
-        <v>7055219</v>
+        <v>7055292</v>
       </c>
       <c r="S40" t="n">
         <v>9</v>
@@ -5497,7 +5507,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5507,7 +5517,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5559,10 +5569,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129309958</v>
+        <v>129307918</v>
       </c>
       <c r="B41" t="n">
-        <v>80182</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5570,42 +5580,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>519366</v>
+        <v>519302</v>
       </c>
       <c r="R41" t="n">
-        <v>7055274</v>
+        <v>7055219</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5634,7 +5639,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5644,12 +5649,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På en lutande död sälg.</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5668,22 +5668,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5701,32 +5701,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129310002</v>
+        <v>129309958</v>
       </c>
       <c r="B42" t="n">
-        <v>80216</v>
+        <v>80187</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5741,13 +5741,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519344</v>
+        <v>519366</v>
       </c>
       <c r="R42" t="n">
-        <v>7055261</v>
+        <v>7055274</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -5846,7 +5846,7 @@
         <v>129309664</v>
       </c>
       <c r="B43" t="n">
-        <v>97646</v>
+        <v>97651</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>129310040</v>
       </c>
       <c r="B44" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>129307091</v>
       </c>
       <c r="B45" t="n">
-        <v>98675</v>
+        <v>98680</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129313241</v>
+        <v>129316769</v>
       </c>
       <c r="B50" t="n">
         <v>57736</v>
@@ -6856,13 +6856,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>519454</v>
+        <v>519455</v>
       </c>
       <c r="R50" t="n">
-        <v>7055805</v>
+        <v>7055526</v>
       </c>
       <c r="S50" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6901,12 +6901,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska, längs flera meter på en gran.</t>
+          <t>Ringhack, äldre, på gränsen till färska, på en gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -6958,7 +6958,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129316769</v>
+        <v>129313241</v>
       </c>
       <c r="B51" t="n">
         <v>57736</v>
@@ -7003,13 +7003,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519455</v>
+        <v>519454</v>
       </c>
       <c r="R51" t="n">
-        <v>7055526</v>
+        <v>7055805</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska, på en gran.</t>
+          <t>Ringhack, äldre, på gränsen till färska, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -3736,45 +3736,55 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129314194</v>
+        <v>129309922</v>
       </c>
       <c r="B27" t="n">
-        <v>79081</v>
+        <v>98678</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519427</v>
+        <v>519372</v>
       </c>
       <c r="R27" t="n">
-        <v>7055741</v>
+        <v>7055266</v>
       </c>
       <c r="S27" t="n">
         <v>9</v>
@@ -3806,7 +3816,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3816,7 +3826,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Minst 1 fröställning inom 0,2 m2 yta.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3830,27 +3845,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3868,55 +3863,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129309922</v>
+        <v>129314194</v>
       </c>
       <c r="B28" t="n">
-        <v>98678</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519372</v>
+        <v>519427</v>
       </c>
       <c r="R28" t="n">
-        <v>7055266</v>
+        <v>7055741</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -3948,7 +3933,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3958,12 +3943,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Minst 1 fröställning inom 0,2 m2 yta.</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3977,7 +3957,27 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -3736,55 +3736,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129309922</v>
+        <v>129314194</v>
       </c>
       <c r="B27" t="n">
-        <v>98678</v>
+        <v>79081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519372</v>
+        <v>519427</v>
       </c>
       <c r="R27" t="n">
-        <v>7055266</v>
+        <v>7055741</v>
       </c>
       <c r="S27" t="n">
         <v>9</v>
@@ -3816,7 +3806,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3826,12 +3816,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Minst 1 fröställning inom 0,2 m2 yta.</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3845,7 +3830,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3863,45 +3868,55 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129314194</v>
+        <v>129309922</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>98678</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519427</v>
+        <v>519372</v>
       </c>
       <c r="R28" t="n">
-        <v>7055741</v>
+        <v>7055266</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -3933,7 +3948,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3943,7 +3958,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Minst 1 fröställning inom 0,2 m2 yta.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3957,27 +3977,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4112,32 +4112,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129307276</v>
+        <v>129313884</v>
       </c>
       <c r="B30" t="n">
-        <v>91366</v>
+        <v>91589</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3215</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519259</v>
+        <v>519404</v>
       </c>
       <c r="R30" t="n">
-        <v>7055075</v>
+        <v>7055773</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4211,7 +4211,27 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Våtmark med barrträd</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4229,32 +4249,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129313884</v>
+        <v>129307276</v>
       </c>
       <c r="B31" t="n">
-        <v>91589</v>
+        <v>91366</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>3215</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4269,13 +4289,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519404</v>
+        <v>519259</v>
       </c>
       <c r="R31" t="n">
-        <v>7055773</v>
+        <v>7055075</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4304,7 +4324,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4314,7 +4334,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4328,27 +4348,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Våtmark med barrträd</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -5295,32 +5295,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129310002</v>
+        <v>129309958</v>
       </c>
       <c r="B39" t="n">
-        <v>80221</v>
+        <v>80187</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5335,13 +5335,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519344</v>
+        <v>519366</v>
       </c>
       <c r="R39" t="n">
-        <v>7055261</v>
+        <v>7055274</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5437,27 +5437,27 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129309053</v>
+        <v>129310002</v>
       </c>
       <c r="B40" t="n">
-        <v>79081</v>
+        <v>80221</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5466,19 +5466,24 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519383</v>
+        <v>519344</v>
       </c>
       <c r="R40" t="n">
-        <v>7055292</v>
+        <v>7055261</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5507,7 +5512,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5517,7 +5522,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På en lutande död sälg.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5536,22 +5546,22 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5569,7 +5579,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129307918</v>
+        <v>129309053</v>
       </c>
       <c r="B41" t="n">
         <v>79081</v>
@@ -5604,10 +5614,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>519302</v>
+        <v>519383</v>
       </c>
       <c r="R41" t="n">
-        <v>7055219</v>
+        <v>7055292</v>
       </c>
       <c r="S41" t="n">
         <v>9</v>
@@ -5639,7 +5649,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5649,7 +5659,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5701,10 +5711,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129309958</v>
+        <v>129307918</v>
       </c>
       <c r="B42" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5712,42 +5722,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519366</v>
+        <v>519302</v>
       </c>
       <c r="R42" t="n">
-        <v>7055274</v>
+        <v>7055219</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5776,7 +5781,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5786,12 +5791,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På en lutande död sälg.</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5810,22 +5810,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -5579,7 +5579,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129309053</v>
+        <v>129307918</v>
       </c>
       <c r="B41" t="n">
         <v>79081</v>
@@ -5614,10 +5614,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>519383</v>
+        <v>519302</v>
       </c>
       <c r="R41" t="n">
-        <v>7055292</v>
+        <v>7055219</v>
       </c>
       <c r="S41" t="n">
         <v>9</v>
@@ -5649,7 +5649,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5711,7 +5711,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129307918</v>
+        <v>129309053</v>
       </c>
       <c r="B42" t="n">
         <v>79081</v>
@@ -5746,10 +5746,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519302</v>
+        <v>519383</v>
       </c>
       <c r="R42" t="n">
-        <v>7055219</v>
+        <v>7055292</v>
       </c>
       <c r="S42" t="n">
         <v>9</v>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6811,7 +6811,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129316769</v>
+        <v>129313241</v>
       </c>
       <c r="B50" t="n">
         <v>57736</v>
@@ -6856,13 +6856,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>519455</v>
+        <v>519454</v>
       </c>
       <c r="R50" t="n">
-        <v>7055526</v>
+        <v>7055805</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6901,12 +6901,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska, på en gran.</t>
+          <t>Ringhack, äldre, på gränsen till färska, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -6958,7 +6958,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129313241</v>
+        <v>129316769</v>
       </c>
       <c r="B51" t="n">
         <v>57736</v>
@@ -7003,13 +7003,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519454</v>
+        <v>519455</v>
       </c>
       <c r="R51" t="n">
-        <v>7055805</v>
+        <v>7055526</v>
       </c>
       <c r="S51" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska, längs flera meter på en gran.</t>
+          <t>Ringhack, äldre, på gränsen till färska, på en gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -2972,7 +2972,7 @@
         <v>129310773</v>
       </c>
       <c r="B21" t="n">
-        <v>92911</v>
+        <v>92915</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>129313853</v>
       </c>
       <c r="B22" t="n">
-        <v>92311</v>
+        <v>92315</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>129313937</v>
       </c>
       <c r="B23" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>129310852</v>
       </c>
       <c r="B25" t="n">
-        <v>92548</v>
+        <v>92552</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3619,53 +3619,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129309748</v>
+        <v>129314194</v>
       </c>
       <c r="B26" t="n">
-        <v>92911</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519381</v>
+        <v>519427</v>
       </c>
       <c r="R26" t="n">
-        <v>7055220</v>
+        <v>7055741</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3694,7 +3689,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3704,7 +3699,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3718,7 +3713,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3736,48 +3751,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129314194</v>
+        <v>129309748</v>
       </c>
       <c r="B27" t="n">
-        <v>79081</v>
+        <v>92915</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519427</v>
+        <v>519381</v>
       </c>
       <c r="R27" t="n">
-        <v>7055741</v>
+        <v>7055220</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3806,7 +3826,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3816,7 +3836,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3830,27 +3850,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3871,7 +3871,7 @@
         <v>129309922</v>
       </c>
       <c r="B28" t="n">
-        <v>98678</v>
+        <v>98682</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>129310986</v>
       </c>
       <c r="B29" t="n">
-        <v>92548</v>
+        <v>92552</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4112,32 +4112,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129313884</v>
+        <v>129307276</v>
       </c>
       <c r="B30" t="n">
-        <v>91589</v>
+        <v>91370</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>3215</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519404</v>
+        <v>519259</v>
       </c>
       <c r="R30" t="n">
-        <v>7055773</v>
+        <v>7055075</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4211,27 +4211,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Våtmark med barrträd</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4249,32 +4229,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129307276</v>
+        <v>129313884</v>
       </c>
       <c r="B31" t="n">
-        <v>91366</v>
+        <v>91593</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3215</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4289,13 +4269,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519259</v>
+        <v>519404</v>
       </c>
       <c r="R31" t="n">
-        <v>7055075</v>
+        <v>7055773</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4324,7 +4304,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4334,7 +4314,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4348,7 +4328,27 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Våtmark med barrträd</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4501,7 +4501,7 @@
         <v>129311001</v>
       </c>
       <c r="B33" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4898,30 +4898,34 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129308765</v>
+        <v>129306797</v>
       </c>
       <c r="B36" t="n">
-        <v>91613</v>
+        <v>92552</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>4769</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
@@ -4934,13 +4938,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>519386</v>
+        <v>519293</v>
       </c>
       <c r="R36" t="n">
-        <v>7055265</v>
+        <v>7055067</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4969,7 +4973,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4979,12 +4983,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Växer i en stubbe av en gran som knäckts i stambasen.</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4999,26 +4998,6 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5036,34 +5015,30 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129306797</v>
+        <v>129308765</v>
       </c>
       <c r="B37" t="n">
-        <v>92548</v>
+        <v>91617</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4769</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
@@ -5076,13 +5051,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519293</v>
+        <v>519386</v>
       </c>
       <c r="R37" t="n">
-        <v>7055067</v>
+        <v>7055265</v>
       </c>
       <c r="S37" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5111,7 +5086,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5121,7 +5096,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Växer i en stubbe av en gran som knäckts i stambasen.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5136,6 +5116,26 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5846,7 +5846,7 @@
         <v>129309664</v>
       </c>
       <c r="B43" t="n">
-        <v>97651</v>
+        <v>97655</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>129307091</v>
       </c>
       <c r="B45" t="n">
-        <v>98680</v>
+        <v>98684</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129313241</v>
+        <v>129316769</v>
       </c>
       <c r="B50" t="n">
         <v>57736</v>
@@ -6856,13 +6856,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>519454</v>
+        <v>519455</v>
       </c>
       <c r="R50" t="n">
-        <v>7055805</v>
+        <v>7055526</v>
       </c>
       <c r="S50" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6901,12 +6901,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska, längs flera meter på en gran.</t>
+          <t>Ringhack, äldre, på gränsen till färska, på en gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -6958,7 +6958,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129316769</v>
+        <v>129313241</v>
       </c>
       <c r="B51" t="n">
         <v>57736</v>
@@ -7003,13 +7003,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519455</v>
+        <v>519454</v>
       </c>
       <c r="R51" t="n">
-        <v>7055526</v>
+        <v>7055805</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska, på en gran.</t>
+          <t>Ringhack, äldre, på gränsen till färska, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -6090,7 +6090,7 @@
         <v>129307091</v>
       </c>
       <c r="B45" t="n">
-        <v>98684</v>
+        <v>98686</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -6090,7 +6090,7 @@
         <v>129307091</v>
       </c>
       <c r="B45" t="n">
-        <v>98686</v>
+        <v>98696</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -2243,7 +2243,7 @@
         <v>122513932</v>
       </c>
       <c r="B15" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>129307091</v>
       </c>
       <c r="B45" t="n">
-        <v>98696</v>
+        <v>98700</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>129311450</v>
       </c>
       <c r="B46" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>129310410</v>
       </c>
       <c r="B47" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>129316798</v>
       </c>
       <c r="B48" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>129306721</v>
       </c>
       <c r="B49" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6811,10 +6811,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129316769</v>
+        <v>129313241</v>
       </c>
       <c r="B50" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6856,13 +6856,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>519455</v>
+        <v>519454</v>
       </c>
       <c r="R50" t="n">
-        <v>7055526</v>
+        <v>7055805</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6901,12 +6901,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska, på en gran.</t>
+          <t>Ringhack, äldre, på gränsen till färska, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -6958,10 +6958,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129313241</v>
+        <v>129316769</v>
       </c>
       <c r="B51" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7003,13 +7003,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519454</v>
+        <v>519455</v>
       </c>
       <c r="R51" t="n">
-        <v>7055805</v>
+        <v>7055526</v>
       </c>
       <c r="S51" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska, längs flera meter på en gran.</t>
+          <t>Ringhack, äldre, på gränsen till färska, på en gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -6226,7 +6226,7 @@
         <v>129311450</v>
       </c>
       <c r="B46" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>129310410</v>
       </c>
       <c r="B47" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>129316798</v>
       </c>
       <c r="B48" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>129306721</v>
       </c>
       <c r="B49" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6811,10 +6811,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129313241</v>
+        <v>129316769</v>
       </c>
       <c r="B50" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6856,13 +6856,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>519454</v>
+        <v>519455</v>
       </c>
       <c r="R50" t="n">
-        <v>7055805</v>
+        <v>7055526</v>
       </c>
       <c r="S50" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6901,12 +6901,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska, längs flera meter på en gran.</t>
+          <t>Ringhack, äldre, på gränsen till färska, på en gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -6958,10 +6958,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129316769</v>
+        <v>129313241</v>
       </c>
       <c r="B51" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7003,13 +7003,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519455</v>
+        <v>519454</v>
       </c>
       <c r="R51" t="n">
-        <v>7055526</v>
+        <v>7055805</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska, på en gran.</t>
+          <t>Ringhack, äldre, på gränsen till färska, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,67 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122514485</v>
+        <v>129306617</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519340</v>
+        <v>519307</v>
       </c>
       <c r="R2" t="n">
-        <v>7055482</v>
+        <v>7055051</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +759,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Minst 3 vissna plantor av guckusko inom ca 7 meter från gränsen till en avverkningsanmäld yta.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,26 +794,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,43 +811,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122513607</v>
+        <v>129307091</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -847,10 +865,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519387</v>
+        <v>519283</v>
       </c>
       <c r="R3" t="n">
-        <v>7055266</v>
+        <v>7055063</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,17 +895,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>8 vissna plantor av guckusko i en liten sänka.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,6 +926,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -914,15 +947,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122513788</v>
+        <v>129313884</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,27 +958,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -959,13 +987,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519313</v>
+        <v>519404</v>
       </c>
       <c r="R4" t="n">
-        <v>7055191</v>
+        <v>7055773</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,17 +1017,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1051,15 +1084,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122513843</v>
+        <v>129313937</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,37 +1095,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519326</v>
+        <v>519405</v>
       </c>
       <c r="R5" t="n">
-        <v>7055234</v>
+        <v>7055762</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1121,12 +1154,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,7 +1183,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1155,12 +1198,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1178,15 +1221,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122513257</v>
+        <v>129309958</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,27 +1232,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1223,10 +1261,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519274</v>
+        <v>519366</v>
       </c>
       <c r="R6" t="n">
-        <v>7055087</v>
+        <v>7055274</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1253,17 +1291,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På en lutande död sälg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,6 +1322,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1290,53 +1363,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122513561</v>
+        <v>129307276</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>3215</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519272</v>
+        <v>519259</v>
       </c>
       <c r="R7" t="n">
-        <v>7055091</v>
+        <v>7055075</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1360,12 +1433,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,27 +1462,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Våtmark med barrträd</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1417,43 +1480,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122514475</v>
+        <v>129313853</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1462,13 +1520,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519424</v>
+        <v>519415</v>
       </c>
       <c r="R8" t="n">
-        <v>7055785</v>
+        <v>7055795</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1492,17 +1550,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1513,6 +1576,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1529,53 +1617,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122513696</v>
+        <v>129306797</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519306</v>
+        <v>519293</v>
       </c>
       <c r="R9" t="n">
-        <v>7055165</v>
+        <v>7055067</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1599,17 +1687,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ymnigt med långväxta bålar.</t>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1623,27 +1716,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1661,43 +1734,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122513395</v>
+        <v>129310852</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1706,10 +1774,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519278</v>
+        <v>519479</v>
       </c>
       <c r="R10" t="n">
-        <v>7055044</v>
+        <v>7055528</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1736,17 +1804,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1760,27 +1833,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1798,53 +1851,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122514293</v>
+        <v>129310986</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519526</v>
+        <v>519482</v>
       </c>
       <c r="R11" t="n">
-        <v>7055378</v>
+        <v>7055550</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1868,12 +1921,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1887,27 +1950,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1928,12 +1971,7 @@
         <v>122513573</v>
       </c>
       <c r="B12" t="n">
-        <v>90964</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2027,47 +2065,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122513620</v>
+        <v>129309748</v>
       </c>
       <c r="B13" t="n">
-        <v>57460</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100136</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>rastande</t>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2076,13 +2105,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519384</v>
+        <v>519381</v>
       </c>
       <c r="R13" t="n">
-        <v>7055266</v>
+        <v>7055220</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2106,12 +2135,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2122,6 +2161,11 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2138,15 +2182,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122513924</v>
+        <v>129310383</v>
       </c>
       <c r="B14" t="n">
-        <v>90962</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2154,37 +2193,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519411</v>
+        <v>519544</v>
       </c>
       <c r="R14" t="n">
-        <v>7055518</v>
+        <v>7055366</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2208,12 +2252,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2224,6 +2278,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2240,10 +2299,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122513932</v>
+        <v>129310773</v>
       </c>
       <c r="B15" t="n">
-        <v>57737</v>
+        <v>93233</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,42 +2310,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519417</v>
+        <v>519497</v>
       </c>
       <c r="R15" t="n">
-        <v>7055533</v>
+        <v>7055506</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2313,17 +2369,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på tall.</t>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2337,27 +2398,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2375,43 +2416,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122514218</v>
+        <v>122513395</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2420,10 +2456,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519487</v>
+        <v>519278</v>
       </c>
       <c r="R16" t="n">
-        <v>7055674</v>
+        <v>7055044</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2460,7 +2496,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2471,6 +2507,31 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2487,55 +2548,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122513469</v>
+        <v>122513561</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519319</v>
+        <v>519272</v>
       </c>
       <c r="R17" t="n">
-        <v>7055189</v>
+        <v>7055091</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2570,11 +2621,6 @@
           <t>2025-02-08</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2583,6 +2629,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2599,19 +2670,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122513793</v>
+        <v>122513696</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2639,10 +2705,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519310</v>
+        <v>519306</v>
       </c>
       <c r="R18" t="n">
-        <v>7055186</v>
+        <v>7055165</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2675,6 +2741,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ymnigt med långväxta bålar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2726,19 +2797,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122513926</v>
+        <v>122513793</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2766,13 +2832,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519405</v>
+        <v>519310</v>
       </c>
       <c r="R19" t="n">
-        <v>7055243</v>
+        <v>7055186</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2853,57 +2919,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123542918</v>
+        <v>122513843</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Öjån, Jmt</t>
+          <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519406</v>
+        <v>519326</v>
       </c>
       <c r="R20" t="n">
-        <v>7055512</v>
+        <v>7055234</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2927,22 +2984,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:44</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:44</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2953,69 +3000,89 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linda  Höglund</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linda  Höglund</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129310773</v>
+        <v>122513926</v>
       </c>
       <c r="B21" t="n">
-        <v>92915</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519497</v>
+        <v>519405</v>
       </c>
       <c r="R21" t="n">
-        <v>7055506</v>
+        <v>7055243</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3039,22 +3106,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:48</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:48</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3069,6 +3126,26 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3086,53 +3163,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129313853</v>
+        <v>122514293</v>
       </c>
       <c r="B22" t="n">
-        <v>92315</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519415</v>
+        <v>519526</v>
       </c>
       <c r="R22" t="n">
-        <v>7055795</v>
+        <v>7055378</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3156,22 +3228,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>15:57</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>15:57</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3185,7 +3247,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -3200,12 +3262,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3223,53 +3285,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129313937</v>
+        <v>122514485</v>
       </c>
       <c r="B23" t="n">
-        <v>91593</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>519405</v>
+        <v>519340</v>
       </c>
       <c r="R23" t="n">
-        <v>7055762</v>
+        <v>7055482</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3293,22 +3350,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>16:01</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>16:01</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3322,7 +3369,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -3337,12 +3384,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3360,53 +3407,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129313980</v>
+        <v>129307918</v>
       </c>
       <c r="B24" t="n">
-        <v>57733</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>519421</v>
+        <v>519302</v>
       </c>
       <c r="R24" t="n">
-        <v>7055771</v>
+        <v>7055219</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3435,7 +3477,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3445,12 +3487,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i en gran.</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3464,7 +3501,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -3479,12 +3516,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3502,53 +3539,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129310852</v>
+        <v>129309053</v>
       </c>
       <c r="B25" t="n">
-        <v>92552</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519479</v>
+        <v>519383</v>
       </c>
       <c r="R25" t="n">
-        <v>7055528</v>
+        <v>7055292</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3577,7 +3609,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3587,7 +3619,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3601,7 +3633,27 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3619,14 +3671,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129314194</v>
+        <v>129310040</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3654,13 +3706,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519427</v>
+        <v>519359</v>
       </c>
       <c r="R26" t="n">
-        <v>7055741</v>
+        <v>7055281</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3689,7 +3741,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3699,7 +3751,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3713,7 +3765,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -3751,50 +3803,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129309748</v>
+        <v>129313586</v>
       </c>
       <c r="B27" t="n">
-        <v>92915</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519381</v>
+        <v>519436</v>
       </c>
       <c r="R27" t="n">
-        <v>7055220</v>
+        <v>7055806</v>
       </c>
       <c r="S27" t="n">
         <v>8</v>
@@ -3826,7 +3873,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3836,7 +3883,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3850,7 +3897,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3868,55 +3935,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129309922</v>
+        <v>129314194</v>
       </c>
       <c r="B28" t="n">
-        <v>98682</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519372</v>
+        <v>519427</v>
       </c>
       <c r="R28" t="n">
-        <v>7055266</v>
+        <v>7055741</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -3948,7 +4005,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3958,12 +4015,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Minst 1 fröställning inom 0,2 m2 yta.</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3977,7 +4029,27 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3995,10 +4067,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129310986</v>
+        <v>129310002</v>
       </c>
       <c r="B29" t="n">
-        <v>92552</v>
+        <v>80467</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4006,27 +4078,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4769</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4035,10 +4107,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519482</v>
+        <v>519344</v>
       </c>
       <c r="R29" t="n">
-        <v>7055550</v>
+        <v>7055261</v>
       </c>
       <c r="S29" t="n">
         <v>11</v>
@@ -4070,7 +4142,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4080,7 +4152,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På en lutande död sälg.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4094,7 +4171,27 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4112,10 +4209,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129307276</v>
+        <v>129308971</v>
       </c>
       <c r="B30" t="n">
-        <v>91370</v>
+        <v>80468</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4123,27 +4220,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3215</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4152,13 +4249,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519259</v>
+        <v>519353</v>
       </c>
       <c r="R30" t="n">
-        <v>7055075</v>
+        <v>7055274</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4187,7 +4284,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4197,7 +4294,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4211,7 +4313,27 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Våtmark med barrträd</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4229,38 +4351,43 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129313884</v>
+        <v>129310609</v>
       </c>
       <c r="B31" t="n">
-        <v>91593</v>
+        <v>57950</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4269,13 +4396,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519404</v>
+        <v>519530</v>
       </c>
       <c r="R31" t="n">
-        <v>7055773</v>
+        <v>7055428</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4304,7 +4431,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4314,7 +4441,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rejäla färska hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4366,45 +4498,55 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129313586</v>
+        <v>129310744</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>57950</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519436</v>
+        <v>519498</v>
       </c>
       <c r="R32" t="n">
-        <v>7055806</v>
+        <v>7055493</v>
       </c>
       <c r="S32" t="n">
         <v>8</v>
@@ -4436,7 +4578,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4446,7 +4588,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i stambasen av en grov gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4475,12 +4622,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4498,34 +4645,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129311001</v>
+        <v>129313980</v>
       </c>
       <c r="B33" t="n">
-        <v>91617</v>
+        <v>57950</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4534,10 +4685,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519493</v>
+        <v>519421</v>
       </c>
       <c r="R33" t="n">
-        <v>7055555</v>
+        <v>7055771</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4569,7 +4720,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4579,7 +4730,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i en gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4608,12 +4764,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4631,10 +4787,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129308557</v>
+        <v>122513257</v>
       </c>
       <c r="B34" t="n">
-        <v>57896</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4642,41 +4798,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4685,13 +4827,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>519390</v>
+        <v>519274</v>
       </c>
       <c r="R34" t="n">
-        <v>7055229</v>
+        <v>7055087</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4715,27 +4857,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>12:44</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>12:44</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Synobservation av 4 livliga talltitor som nyfiket dök upp på nära håll.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4746,11 +4878,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4767,10 +4894,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129310923</v>
+        <v>122513469</v>
       </c>
       <c r="B35" t="n">
-        <v>57896</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4778,36 +4905,27 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4816,10 +4934,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>519476</v>
+        <v>519319</v>
       </c>
       <c r="R35" t="n">
-        <v>7055536</v>
+        <v>7055189</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4846,27 +4964,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>14:56</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>14:56</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Minst 1 talltita i flerskiktad gammal granskog och gransumpskog.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4877,11 +4985,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4898,38 +5001,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129306797</v>
+        <v>122513607</v>
       </c>
       <c r="B36" t="n">
-        <v>92552</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4938,13 +5041,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>519293</v>
+        <v>519387</v>
       </c>
       <c r="R36" t="n">
-        <v>7055067</v>
+        <v>7055266</v>
       </c>
       <c r="S36" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4968,22 +5071,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:26</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:26</t>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4994,11 +5092,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5015,10 +5108,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129308765</v>
+        <v>122513788</v>
       </c>
       <c r="B37" t="n">
-        <v>91617</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5026,23 +5119,27 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -5051,13 +5148,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519386</v>
+        <v>519313</v>
       </c>
       <c r="R37" t="n">
-        <v>7055265</v>
+        <v>7055191</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5081,27 +5178,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>12:53</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>12:53</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Växer i en stubbe av en gran som knäckts i stambasen.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5115,7 +5202,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -5130,12 +5217,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5153,53 +5240,56 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129308971</v>
+        <v>122513932</v>
       </c>
       <c r="B38" t="n">
-        <v>80222</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519353</v>
+        <v>519417</v>
       </c>
       <c r="R38" t="n">
-        <v>7055274</v>
+        <v>7055533</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5223,27 +5313,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:05</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:05</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På en sälglåga.</t>
+          <t>Ringhack, äldre, på tall.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5262,22 +5342,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5295,10 +5375,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129309958</v>
+        <v>122514218</v>
       </c>
       <c r="B39" t="n">
-        <v>80187</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5306,27 +5386,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5335,10 +5415,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519366</v>
+        <v>519487</v>
       </c>
       <c r="R39" t="n">
-        <v>7055274</v>
+        <v>7055674</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5365,27 +5445,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:44</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:44</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På en lutande död sälg.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5396,31 +5466,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5437,38 +5482,43 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129310002</v>
+        <v>122514422</v>
       </c>
       <c r="B40" t="n">
-        <v>80221</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5477,13 +5527,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519344</v>
+        <v>519397</v>
       </c>
       <c r="R40" t="n">
-        <v>7055261</v>
+        <v>7055470</v>
       </c>
       <c r="S40" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5507,27 +5557,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På en lutande död sälg.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5541,27 +5581,27 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5579,10 +5619,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129307918</v>
+        <v>122514475</v>
       </c>
       <c r="B41" t="n">
-        <v>79081</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5590,37 +5630,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>519302</v>
+        <v>519424</v>
       </c>
       <c r="R41" t="n">
-        <v>7055219</v>
+        <v>7055785</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5644,22 +5689,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>12:28</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>12:28</t>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5670,31 +5710,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5711,10 +5726,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129309053</v>
+        <v>123542918</v>
       </c>
       <c r="B42" t="n">
-        <v>79081</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5722,37 +5737,41 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Flärknäset, Flärknäset, Jmt</t>
+          <t>Öjån, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519383</v>
+        <v>519406</v>
       </c>
       <c r="R42" t="n">
-        <v>7055292</v>
+        <v>7055512</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5776,22 +5795,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5802,89 +5821,74 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Linda  Höglund</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Linda  Höglund</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129309664</v>
+        <v>129306721</v>
       </c>
       <c r="B43" t="n">
-        <v>97655</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519401</v>
+        <v>519304</v>
       </c>
       <c r="R43" t="n">
-        <v>7055248</v>
+        <v>7055061</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5913,7 +5917,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5923,7 +5927,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, påtagligt och tydligt på stambasen av en gammal gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5938,6 +5947,26 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5955,10 +5984,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129310040</v>
+        <v>129310410</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5966,37 +5995,47 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Flärknäset, Flärknäset, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519359</v>
+        <v>519532</v>
       </c>
       <c r="R44" t="n">
-        <v>7055281</v>
+        <v>7055358</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6025,7 +6064,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6035,7 +6074,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6064,12 +6108,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6087,47 +6131,38 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129307091</v>
+        <v>129310759</v>
       </c>
       <c r="B45" t="n">
-        <v>98700</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>504</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6141,13 +6176,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519283</v>
+        <v>519497</v>
       </c>
       <c r="R45" t="n">
-        <v>7055063</v>
+        <v>7055497</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6176,7 +6211,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6186,12 +6221,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>8 vissna plantor av guckusko i en liten sänka.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6205,7 +6240,27 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6226,7 +6281,7 @@
         <v>129311450</v>
       </c>
       <c r="B46" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6370,10 +6425,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129310410</v>
+        <v>129313241</v>
       </c>
       <c r="B47" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6401,7 +6456,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -6415,13 +6470,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519532</v>
+        <v>519454</v>
       </c>
       <c r="R47" t="n">
-        <v>7055358</v>
+        <v>7055805</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6450,7 +6505,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6460,12 +6515,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Ringhack, äldre, på gränsen till färska, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6479,7 +6534,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -6517,10 +6572,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129316798</v>
+        <v>129313610</v>
       </c>
       <c r="B48" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6562,13 +6617,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519455</v>
+        <v>519404</v>
       </c>
       <c r="R48" t="n">
-        <v>7055533</v>
+        <v>7055812</v>
       </c>
       <c r="S48" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6597,7 +6652,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6607,12 +6662,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska, på stambasen av en gran.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6626,7 +6681,7 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -6664,10 +6719,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129306721</v>
+        <v>129313810</v>
       </c>
       <c r="B49" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6709,13 +6764,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519304</v>
+        <v>519391</v>
       </c>
       <c r="R49" t="n">
-        <v>7055061</v>
+        <v>7055805</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6744,7 +6799,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6754,12 +6809,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, påtagligt och tydligt på stambasen av en gammal gran.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6773,7 +6828,7 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -6814,7 +6869,7 @@
         <v>129316769</v>
       </c>
       <c r="B50" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6958,10 +7013,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129313241</v>
+        <v>129316798</v>
       </c>
       <c r="B51" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7003,10 +7058,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519454</v>
+        <v>519455</v>
       </c>
       <c r="R51" t="n">
-        <v>7055805</v>
+        <v>7055533</v>
       </c>
       <c r="S51" t="n">
         <v>11</v>
@@ -7038,7 +7093,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7048,12 +7103,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska, längs flera meter på en gran.</t>
+          <t>Ringhack, äldre, på gränsen till färska, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7067,7 +7122,7 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -7102,6 +7157,744 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>122513620</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57813</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100136</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Lappuggla</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Strix nebulosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>519384</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7055266</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129308557</v>
+      </c>
+      <c r="B53" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>519390</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7055229</v>
+      </c>
+      <c r="S53" t="n">
+        <v>9</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Synobservation av 4 livliga talltitor som nyfiket dök upp på nära håll.</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129310923</v>
+      </c>
+      <c r="B54" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>519476</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7055536</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Minst 1 talltita i flerskiktad gammal granskog och gransumpskog.</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129310223</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>519455</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7055312</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Rikkärr</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129309922</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>519372</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7055266</v>
+      </c>
+      <c r="S56" t="n">
+        <v>9</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Minst 1 fröställning inom 0,2 m2 yta.</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129309664</v>
+      </c>
+      <c r="B57" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Flärknäset, Flärknäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>519401</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7055248</v>
+      </c>
+      <c r="S57" t="n">
+        <v>9</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40673-2024 artfynd.xlsx
+++ b/artfynd/A 40673-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AZ57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -808,6 +813,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129306617</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -944,6 +954,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129307091</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1086,6 +1101,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129309958</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1203,6 +1223,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129307276</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1320,6 +1345,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129306797</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1452,6 +1482,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122513395</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1574,6 +1609,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122513561</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1701,6 +1741,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122513696</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1823,6 +1868,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122513793</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1945,6 +1995,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122513843</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2067,6 +2122,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122514485</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2199,6 +2259,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129307918</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2331,6 +2396,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310040</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2473,6 +2543,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310002</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2615,6 +2690,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129308971</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2722,6 +2802,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122513257</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2829,6 +2914,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122513469</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2961,6 +3051,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122513788</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3108,6 +3203,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129306721</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3245,6 +3345,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129313884</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3382,6 +3487,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129313937</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3519,6 +3629,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129313853</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3636,6 +3751,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310852</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3753,6 +3873,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310986</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3850,6 +3975,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122513573</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3967,6 +4097,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129309748</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4084,6 +4219,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310383</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4201,6 +4341,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310773</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4323,6 +4468,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122513926</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4445,6 +4595,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122514293</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4577,6 +4732,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129309053</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4709,6 +4869,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129313586</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4841,6 +5006,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129314194</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4988,6 +5158,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310609</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5135,6 +5310,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310744</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5277,6 +5457,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129313980</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5384,6 +5569,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122513607</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5519,6 +5709,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122513932</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5626,6 +5821,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122514218</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5763,6 +5963,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122514422</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5870,6 +6075,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122514475</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5981,6 +6191,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123542918</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6128,6 +6343,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310410</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6275,6 +6495,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310759</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6422,6 +6647,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129311450</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6569,6 +6799,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129313241</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6716,6 +6951,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129313610</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6863,6 +7103,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129313810</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -7010,6 +7255,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129316769</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -7157,6 +7407,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129316798</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7263,6 +7518,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122513620</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7399,6 +7659,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129308557</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7530,6 +7795,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310923</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7656,6 +7926,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310223</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7783,6 +8058,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129309922</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7895,8 +8175,71 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129309664</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>